--- a/report_2504.xlsx
+++ b/report_2504.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.06</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>-0.5</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>-1.28</v>
+        <v>-0.95</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>-1.28</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>-0.83</v>
+        <v>0.09</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>-0.83</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>46.81</v>
+        <v>46.09</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>46.81</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>-10.42</v>
+        <v>-9.5</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>-10.42</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>-4.62</v>
+        <v>-2.64</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>-4.62</v>
@@ -9531,13 +9531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="96" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>5.77</v>
+        <v>48.94</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>5.77</v>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="B35" s="94" t="n">
-        <v>3.39</v>
+        <v>3.56</v>
       </c>
       <c r="C35" s="94" t="n">
         <v>2.49</v>
@@ -10336,7 +10336,7 @@
         </is>
       </c>
       <c r="B36" s="94" t="n">
-        <v>3.56</v>
+        <v>3.73</v>
       </c>
       <c r="C36" s="94" t="n">
         <v>2.85</v>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="B37" s="94" t="n">
-        <v>43.63</v>
+        <v>48.76</v>
       </c>
       <c r="C37" s="94" t="n">
         <v>8.33</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-3.93</v>
+        <v>-4.04</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-3.16</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-6.77</v>
+        <v>-6.87</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-4.48</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>49.89</v>
+        <v>49.08</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>66.64</v>
@@ -10977,9 +10977,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C42" s="92" t="inlineStr">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>4.63</v>
+        <v>5.17</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>4.63</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>3.05</v>
+        <v>4.44</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>3.05</v>
@@ -11323,13 +11323,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="96" t="inlineStr">
+      <c r="A45" s="76" t="inlineStr">
         <is>
           <t>fr40:RS5</t>
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>18.86</v>
+        <v>36.94</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>18.86</v>
@@ -11425,165 +11425,165 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="92" t="inlineStr">
+      <c r="B46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C46" s="92" t="inlineStr">
+      <c r="D46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D46" s="92" t="inlineStr">
+      <c r="E46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E46" s="92" t="inlineStr">
+      <c r="F46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F46" s="92" t="inlineStr">
+      <c r="G46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G46" s="93" t="inlineStr">
+      <c r="I46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H46" s="92" t="inlineStr">
+      <c r="M46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I46" s="92" t="inlineStr">
+      <c r="R46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J46" s="92" t="inlineStr">
+      <c r="T46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K46" s="91" t="inlineStr">
+      <c r="U46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L46" s="93" t="inlineStr">
+      <c r="V46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M46" s="93" t="inlineStr">
+      <c r="X46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N46" s="93" t="inlineStr">
+      <c r="Y46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O46" s="93" t="inlineStr">
+      <c r="AA46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AD46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="R46" s="91" t="inlineStr">
+      <c r="AE46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="T46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="U46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" s="76" t="inlineStr">
+      <c r="A47" s="95" t="inlineStr">
         <is>
           <t>dax30:RNG60</t>
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>9.630000000000001</v>
+        <v>10.79</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>9.630000000000001</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>16.01</v>
+        <v>18.19</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>16.01</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>25.84</v>
+        <v>44</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>25.84</v>
@@ -11870,14 +11870,14 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：ixic:RS2:5.77&lt;=38;jp225:RNG60:-10.7&lt;=-10;jp225:RS9:23.21&lt;=28;fr40:RS5:18.86&lt;=20</t>
+          <t>今日买报：jp225:RNG60:-10.7&lt;=-10;jp225:RS9:23.21&lt;=28</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：kc:RNG120:38.43&gt;=30;hk50:RNG60:18.26&gt;=15</t>
+          <t>今日卖报：kc:RNG120:38.43&gt;=30;hk50:RNG60:18.26&gt;=15;dax30:RNG60:10.79&gt;=10</t>
         </is>
       </c>
     </row>

--- a/report_2504.xlsx
+++ b/report_2504.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.28</v>
+        <v>7.3</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.28</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.02</v>
+        <v>0.22</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.18</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.58</v>
+        <v>0.82</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.37</v>
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C18" s="92" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>-4.01</v>
+        <v>-4.57</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>-4.01</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>-1.1</v>
+        <v>-1.39</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>-1.1</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>52.81</v>
+        <v>76.8</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>52.81</v>
@@ -8737,9 +8737,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B22" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C22" s="92" t="inlineStr">
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>-0.95</v>
+        <v>-1.19</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>-0.95</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>0.09</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>46.09</v>
+        <v>63.09</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>46.09</v>
@@ -9185,9 +9185,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C26" s="92" t="inlineStr">
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>-9.5</v>
+        <v>-10.3</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>-9.5</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>-2.64</v>
+        <v>-3.2</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>-2.64</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>48.94</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>48.94</v>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-1.89</v>
+        <v>-1.73</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-4.04</v>
@@ -10782,7 +10782,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-6.11</v>
+        <v>-5.95</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-6.87</v>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>53.64</v>
+        <v>54.73</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>49.08</v>
@@ -11133,7 +11133,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>5.17</v>
+        <v>5.45</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>5.17</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>4.44</v>
+        <v>3.71</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>4.44</v>
@@ -11327,7 +11327,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>36.94</v>
+        <v>34.95</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>36.94</v>
@@ -11423,165 +11423,165 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="92" t="inlineStr">
+      <c r="B46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C46" s="91" t="inlineStr">
+      <c r="E46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D46" s="92" t="inlineStr">
+      <c r="M46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E46" s="92" t="inlineStr">
+      <c r="S46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F46" s="92" t="inlineStr">
+      <c r="U46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G46" s="92" t="inlineStr">
+      <c r="V46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H46" s="93" t="inlineStr">
+      <c r="AA46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="J46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="K46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="L46" s="91" t="inlineStr">
+      <c r="AB46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M46" s="93" t="inlineStr">
+      <c r="AC46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AD46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AE46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="S46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="U46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" s="76" t="inlineStr">
+      <c r="A47" s="95" t="inlineStr">
         <is>
           <t>dax30:RNG60</t>
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>9.56</v>
+        <v>10.14</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>10.81</v>
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>15.67</v>
+        <v>16.29</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>18.22</v>
@@ -11775,7 +11775,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>36.5</v>
+        <v>39.55</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>44.2</v>
@@ -11875,7 +11875,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：hk50:RNG60:17.42&gt;=15</t>
+          <t>今日卖报：hk50:RNG60:17.42&gt;=15;dax30:RNG60:10.14&gt;=10</t>
         </is>
       </c>
     </row>

--- a/report_2504.xlsx
+++ b/report_2504.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.31</v>
+        <v>7.28</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.3</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.22</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.82</v>
@@ -8737,9 +8737,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B22" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C22" s="93" t="inlineStr">
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>-1.19</v>
+        <v>-5.06</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>-1.19</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>0.34</v>
+        <v>-4.62</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>0.34</v>
@@ -9083,13 +9083,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="76" t="inlineStr">
+      <c r="A25" s="96" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>63.09</v>
+        <v>14.42</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>63.09</v>
@@ -9185,9 +9185,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B26" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C26" s="91" t="inlineStr">
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>-10.3</v>
+        <v>-16.68</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>-10.3</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>-3.2</v>
+        <v>-9.52</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>-3.2</v>
@@ -9531,13 +9531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="76" t="inlineStr">
+      <c r="A29" s="96" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>73.40000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>73.40000000000001</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-2.42</v>
+        <v>-2.43</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-1.73</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-6.5</v>
+        <v>-6.51</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-5.95</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>51.43</v>
+        <v>51.3</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>54.73</v>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>2.95</v>
+        <v>1.45</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>5.45</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>1.44</v>
+        <v>-0.04</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>3.71</v>
@@ -11323,13 +11323,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="76" t="inlineStr">
+      <c r="A45" s="96" t="inlineStr">
         <is>
           <t>fr40:RS5</t>
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>22.29</v>
+        <v>17.48</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>34.95</v>
@@ -11425,165 +11425,165 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="91" t="inlineStr">
+      <c r="B46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C46" s="91" t="inlineStr">
+      <c r="D46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D46" s="91" t="inlineStr">
+      <c r="E46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E46" s="92" t="inlineStr">
+      <c r="N46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F46" s="92" t="inlineStr">
+      <c r="T46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G46" s="92" t="inlineStr">
+      <c r="V46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H46" s="92" t="inlineStr">
+      <c r="W46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I46" s="93" t="inlineStr">
+      <c r="AB46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="K46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="L46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="M46" s="91" t="inlineStr">
+      <c r="AC46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="T46" s="91" t="inlineStr">
+      <c r="AD46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W46" s="91" t="inlineStr">
+      <c r="AE46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" s="95" t="inlineStr">
+      <c r="A47" s="76" t="inlineStr">
         <is>
           <t>dax30:RNG60</t>
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>10.14</v>
+        <v>6.89</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>10.14</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>16.29</v>
+        <v>13.05</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>16.29</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>39.55</v>
+        <v>25.18</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>39.55</v>
@@ -11870,14 +11870,14 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RS4:18.53&lt;=22;jp225:RNG60:-13.34&lt;=-10;jp225:RS9:18.88&lt;=28;vn:RS3:5.54&lt;=25</t>
+          <t>今日买报：hk50:RS4:18.53&lt;=22;us30:RS3:14.42&lt;=25;ixic:RS2:9.58&lt;=38;jp225:RNG60:-13.34&lt;=-10;jp225:RS9:18.88&lt;=28;vn:RS3:5.54&lt;=25;fr40:RS5:17.48&lt;=20</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：hk50:RNG60:16.06&gt;=15;dax30:RNG60:10.14&gt;=10</t>
+          <t>今日卖报：hk50:RNG60:16.06&gt;=15</t>
         </is>
       </c>
     </row>

--- a/report_2504.xlsx
+++ b/report_2504.xlsx
@@ -6342,152 +6342,152 @@
       </c>
       <c r="B1" s="77" t="inlineStr">
         <is>
+          <t>250404</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
           <t>250403</t>
         </is>
       </c>
-      <c r="C1" s="77" t="inlineStr">
+      <c r="D1" s="77" t="inlineStr">
         <is>
           <t>250402</t>
         </is>
       </c>
-      <c r="D1" s="77" t="inlineStr">
+      <c r="E1" s="77" t="inlineStr">
         <is>
           <t>250401</t>
         </is>
       </c>
-      <c r="E1" s="77" t="inlineStr">
+      <c r="F1" s="77" t="inlineStr">
         <is>
           <t>250331</t>
         </is>
       </c>
-      <c r="F1" s="77" t="inlineStr">
+      <c r="G1" s="77" t="inlineStr">
         <is>
           <t>250328</t>
         </is>
       </c>
-      <c r="G1" s="77" t="inlineStr">
+      <c r="H1" s="77" t="inlineStr">
         <is>
           <t>250327</t>
         </is>
       </c>
-      <c r="H1" s="77" t="inlineStr">
+      <c r="I1" s="77" t="inlineStr">
         <is>
           <t>250326</t>
         </is>
       </c>
-      <c r="I1" s="77" t="inlineStr">
+      <c r="J1" s="77" t="inlineStr">
         <is>
           <t>250325</t>
         </is>
       </c>
-      <c r="J1" s="77" t="inlineStr">
+      <c r="K1" s="77" t="inlineStr">
         <is>
           <t>250324</t>
         </is>
       </c>
-      <c r="K1" s="77" t="inlineStr">
+      <c r="L1" s="77" t="inlineStr">
         <is>
           <t>250323</t>
         </is>
       </c>
-      <c r="L1" s="77" t="inlineStr">
+      <c r="M1" s="77" t="inlineStr">
         <is>
           <t>250321</t>
         </is>
       </c>
-      <c r="M1" s="77" t="inlineStr">
+      <c r="N1" s="77" t="inlineStr">
         <is>
           <t>250320</t>
         </is>
       </c>
-      <c r="N1" s="77" t="inlineStr">
+      <c r="O1" s="77" t="inlineStr">
         <is>
           <t>250319</t>
         </is>
       </c>
-      <c r="O1" s="77" t="inlineStr">
+      <c r="P1" s="77" t="inlineStr">
         <is>
           <t>250318</t>
         </is>
       </c>
-      <c r="P1" s="77" t="inlineStr">
+      <c r="Q1" s="77" t="inlineStr">
         <is>
           <t>250317</t>
         </is>
       </c>
-      <c r="Q1" s="77" t="inlineStr">
+      <c r="R1" s="77" t="inlineStr">
         <is>
           <t>250316</t>
         </is>
       </c>
-      <c r="R1" s="77" t="inlineStr">
+      <c r="S1" s="77" t="inlineStr">
         <is>
           <t>250314</t>
         </is>
       </c>
-      <c r="S1" s="77" t="inlineStr">
+      <c r="T1" s="77" t="inlineStr">
         <is>
           <t>250313</t>
         </is>
       </c>
-      <c r="T1" s="77" t="inlineStr">
+      <c r="U1" s="77" t="inlineStr">
         <is>
           <t>250312</t>
         </is>
       </c>
-      <c r="U1" s="77" t="inlineStr">
+      <c r="V1" s="77" t="inlineStr">
         <is>
           <t>250311</t>
         </is>
       </c>
-      <c r="V1" s="77" t="inlineStr">
+      <c r="W1" s="77" t="inlineStr">
         <is>
           <t>250310</t>
         </is>
       </c>
-      <c r="W1" s="77" t="inlineStr">
+      <c r="X1" s="77" t="inlineStr">
         <is>
           <t>250309</t>
         </is>
       </c>
-      <c r="X1" s="77" t="inlineStr">
+      <c r="Y1" s="77" t="inlineStr">
         <is>
           <t>250307</t>
         </is>
       </c>
-      <c r="Y1" s="77" t="inlineStr">
+      <c r="Z1" s="77" t="inlineStr">
         <is>
           <t>250306</t>
         </is>
       </c>
-      <c r="Z1" s="77" t="inlineStr">
+      <c r="AA1" s="77" t="inlineStr">
         <is>
           <t>250305</t>
         </is>
       </c>
-      <c r="AA1" s="77" t="inlineStr">
+      <c r="AB1" s="77" t="inlineStr">
         <is>
           <t>250304</t>
         </is>
       </c>
-      <c r="AB1" s="77" t="inlineStr">
+      <c r="AC1" s="77" t="inlineStr">
         <is>
           <t>250303</t>
         </is>
       </c>
-      <c r="AC1" s="77" t="inlineStr">
+      <c r="AD1" s="77" t="inlineStr">
         <is>
           <t>250302</t>
         </is>
       </c>
-      <c r="AD1" s="77" t="inlineStr">
+      <c r="AE1" s="77" t="inlineStr">
         <is>
           <t>250228</t>
-        </is>
-      </c>
-      <c r="AE1" s="77" t="inlineStr">
-        <is>
-          <t>250227</t>
         </is>
       </c>
     </row>
@@ -6512,139 +6512,139 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="E2" s="92" t="inlineStr">
+      <c r="E2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F2" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F2" s="92" t="inlineStr">
+      <c r="G2" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G2" s="92" t="inlineStr">
+      <c r="H2" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H2" s="92" t="inlineStr">
+      <c r="I2" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I2" s="92" t="inlineStr">
+      <c r="J2" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J2" s="92" t="inlineStr">
+      <c r="K2" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K2" s="92" t="inlineStr">
+      <c r="L2" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L2" s="92" t="inlineStr">
+      <c r="M2" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M2" s="91" t="inlineStr">
+      <c r="N2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N2" s="93" t="inlineStr">
+      <c r="O2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O2" s="93" t="inlineStr">
+      <c r="P2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P2" s="93" t="inlineStr">
+      <c r="Q2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q2" s="93" t="inlineStr">
+      <c r="R2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R2" s="93" t="inlineStr">
+      <c r="S2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S2" s="91" t="inlineStr">
+      <c r="T2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T2" s="91" t="inlineStr">
+      <c r="U2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U2" s="93" t="inlineStr">
+      <c r="V2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V2" s="93" t="inlineStr">
+      <c r="W2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W2" s="93" t="inlineStr">
+      <c r="X2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X2" s="93" t="inlineStr">
+      <c r="Y2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y2" s="93" t="inlineStr">
+      <c r="Z2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z2" s="91" t="inlineStr">
+      <c r="AA2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA2" s="92" t="inlineStr">
+      <c r="AB2" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB2" s="92" t="inlineStr">
+      <c r="AC2" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC2" s="92" t="inlineStr">
+      <c r="AD2" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD2" s="92" t="inlineStr">
+      <c r="AE2" s="92" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AE2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -6658,91 +6658,91 @@
         <v>-0.29</v>
       </c>
       <c r="C3" s="94" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="D3" s="94" t="n">
         <v>-1.68</v>
       </c>
-      <c r="D3" s="94" t="n">
+      <c r="E3" s="94" t="n">
         <v>-1.52</v>
       </c>
-      <c r="E3" s="94" t="n">
+      <c r="F3" s="94" t="n">
         <v>-1.83</v>
       </c>
-      <c r="F3" s="94" t="n">
+      <c r="G3" s="94" t="n">
         <v>-1.24</v>
       </c>
-      <c r="G3" s="94" t="n">
+      <c r="H3" s="94" t="n">
         <v>-0.58</v>
       </c>
-      <c r="H3" s="94" t="n">
+      <c r="I3" s="94" t="n">
         <v>0.52</v>
       </c>
-      <c r="I3" s="94" t="n">
+      <c r="J3" s="94" t="n">
         <v>0.06</v>
       </c>
-      <c r="J3" s="94" t="n">
+      <c r="K3" s="94" t="n">
         <v>0</v>
-      </c>
-      <c r="K3" s="94" t="n">
-        <v>-0.51</v>
       </c>
       <c r="L3" s="94" t="n">
         <v>-0.51</v>
       </c>
       <c r="M3" s="94" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="N3" s="94" t="n">
         <v>1.41</v>
       </c>
-      <c r="N3" s="94" t="n">
+      <c r="O3" s="94" t="n">
         <v>1.18</v>
       </c>
-      <c r="O3" s="94" t="n">
+      <c r="P3" s="94" t="n">
         <v>1.12</v>
       </c>
-      <c r="P3" s="94" t="n">
+      <c r="Q3" s="94" t="n">
         <v>-1.02</v>
-      </c>
-      <c r="Q3" s="94" t="n">
-        <v>-0.38</v>
       </c>
       <c r="R3" s="94" t="n">
         <v>-0.38</v>
       </c>
       <c r="S3" s="94" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="T3" s="94" t="n">
         <v>-1.87</v>
       </c>
-      <c r="T3" s="94" t="n">
+      <c r="U3" s="94" t="n">
         <v>-0.9</v>
       </c>
-      <c r="U3" s="94" t="n">
+      <c r="V3" s="94" t="n">
         <v>-0.71</v>
       </c>
-      <c r="V3" s="94" t="n">
+      <c r="W3" s="94" t="n">
         <v>-0.08</v>
-      </c>
-      <c r="W3" s="94" t="n">
-        <v>0.23</v>
       </c>
       <c r="X3" s="94" t="n">
         <v>0.23</v>
       </c>
       <c r="Y3" s="94" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Z3" s="94" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="Z3" s="94" t="n">
+      <c r="AA3" s="94" t="n">
         <v>-0.65</v>
       </c>
-      <c r="AA3" s="94" t="n">
+      <c r="AB3" s="94" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AB3" s="94" t="n">
+      <c r="AC3" s="94" t="n">
         <v>0.64</v>
-      </c>
-      <c r="AC3" s="94" t="n">
-        <v>0.34</v>
       </c>
       <c r="AD3" s="94" t="n">
         <v>0.34</v>
       </c>
       <c r="AE3" s="94" t="n">
-        <v>3.94</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="4">
@@ -6755,91 +6755,91 @@
         <v>-4.23</v>
       </c>
       <c r="C4" s="94" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="D4" s="94" t="n">
         <v>0.41</v>
       </c>
-      <c r="D4" s="94" t="n">
+      <c r="E4" s="94" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="E4" s="94" t="n">
+      <c r="F4" s="94" t="n">
         <v>11.16</v>
       </c>
-      <c r="F4" s="94" t="n">
+      <c r="G4" s="94" t="n">
         <v>15.71</v>
       </c>
-      <c r="G4" s="94" t="n">
+      <c r="H4" s="94" t="n">
         <v>17.83</v>
       </c>
-      <c r="H4" s="94" t="n">
+      <c r="I4" s="94" t="n">
         <v>22.55</v>
       </c>
-      <c r="I4" s="94" t="n">
+      <c r="J4" s="94" t="n">
         <v>23.14</v>
       </c>
-      <c r="J4" s="94" t="n">
+      <c r="K4" s="94" t="n">
         <v>23.17</v>
-      </c>
-      <c r="K4" s="94" t="n">
-        <v>23.83</v>
       </c>
       <c r="L4" s="94" t="n">
         <v>23.83</v>
       </c>
       <c r="M4" s="94" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="N4" s="94" t="n">
         <v>26.07</v>
       </c>
-      <c r="N4" s="94" t="n">
+      <c r="O4" s="94" t="n">
         <v>26.11</v>
       </c>
-      <c r="O4" s="94" t="n">
+      <c r="P4" s="94" t="n">
         <v>26.01</v>
       </c>
-      <c r="P4" s="94" t="n">
+      <c r="Q4" s="94" t="n">
         <v>24.85</v>
-      </c>
-      <c r="Q4" s="94" t="n">
-        <v>24.96</v>
       </c>
       <c r="R4" s="94" t="n">
         <v>24.96</v>
       </c>
       <c r="S4" s="94" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="T4" s="94" t="n">
         <v>21.44</v>
       </c>
-      <c r="T4" s="94" t="n">
+      <c r="U4" s="94" t="n">
         <v>20.93</v>
       </c>
-      <c r="U4" s="94" t="n">
+      <c r="V4" s="94" t="n">
         <v>21.39</v>
       </c>
-      <c r="V4" s="94" t="n">
+      <c r="W4" s="94" t="n">
         <v>20.09</v>
-      </c>
-      <c r="W4" s="94" t="n">
-        <v>19.98</v>
       </c>
       <c r="X4" s="94" t="n">
         <v>19.98</v>
       </c>
       <c r="Y4" s="94" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="Z4" s="94" t="n">
         <v>18.96</v>
       </c>
-      <c r="Z4" s="94" t="n">
+      <c r="AA4" s="94" t="n">
         <v>18.38</v>
       </c>
-      <c r="AA4" s="94" t="n">
+      <c r="AB4" s="94" t="n">
         <v>17.16</v>
       </c>
-      <c r="AB4" s="94" t="n">
+      <c r="AC4" s="94" t="n">
         <v>16.44</v>
-      </c>
-      <c r="AC4" s="94" t="n">
-        <v>16.3</v>
       </c>
       <c r="AD4" s="94" t="n">
         <v>16.3</v>
       </c>
       <c r="AE4" s="94" t="n">
-        <v>18.7</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="5">
@@ -6852,91 +6852,91 @@
         <v>29.66</v>
       </c>
       <c r="C5" s="94" t="n">
+        <v>29.66</v>
+      </c>
+      <c r="D5" s="94" t="n">
         <v>42.58</v>
       </c>
-      <c r="D5" s="94" t="n">
+      <c r="E5" s="94" t="n">
         <v>38.88</v>
       </c>
-      <c r="E5" s="94" t="n">
+      <c r="F5" s="94" t="n">
         <v>9.85</v>
       </c>
-      <c r="F5" s="94" t="n">
+      <c r="G5" s="94" t="n">
         <v>16.11</v>
       </c>
-      <c r="G5" s="94" t="n">
+      <c r="H5" s="94" t="n">
         <v>41.34</v>
       </c>
-      <c r="H5" s="94" t="n">
+      <c r="I5" s="94" t="n">
         <v>23.32</v>
       </c>
-      <c r="I5" s="94" t="n">
+      <c r="J5" s="94" t="n">
         <v>24.6</v>
       </c>
-      <c r="J5" s="94" t="n">
+      <c r="K5" s="94" t="n">
         <v>24.63</v>
-      </c>
-      <c r="K5" s="94" t="n">
-        <v>16.35</v>
       </c>
       <c r="L5" s="94" t="n">
         <v>16.35</v>
       </c>
       <c r="M5" s="94" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="N5" s="94" t="n">
         <v>43.2</v>
       </c>
-      <c r="N5" s="94" t="n">
+      <c r="O5" s="94" t="n">
         <v>76.29000000000001</v>
       </c>
-      <c r="O5" s="94" t="n">
+      <c r="P5" s="94" t="n">
         <v>84.51000000000001</v>
       </c>
-      <c r="P5" s="94" t="n">
+      <c r="Q5" s="94" t="n">
         <v>83.2</v>
-      </c>
-      <c r="Q5" s="94" t="n">
-        <v>81.28</v>
       </c>
       <c r="R5" s="94" t="n">
         <v>81.28</v>
       </c>
       <c r="S5" s="94" t="n">
+        <v>81.28</v>
+      </c>
+      <c r="T5" s="94" t="n">
         <v>36.47</v>
       </c>
-      <c r="T5" s="94" t="n">
+      <c r="U5" s="94" t="n">
         <v>55.76</v>
       </c>
-      <c r="U5" s="94" t="n">
+      <c r="V5" s="94" t="n">
         <v>70.7</v>
       </c>
-      <c r="V5" s="94" t="n">
+      <c r="W5" s="94" t="n">
         <v>57.61</v>
-      </c>
-      <c r="W5" s="94" t="n">
-        <v>66.93000000000001</v>
       </c>
       <c r="X5" s="94" t="n">
         <v>66.93000000000001</v>
       </c>
       <c r="Y5" s="94" t="n">
+        <v>66.93000000000001</v>
+      </c>
+      <c r="Z5" s="94" t="n">
         <v>78.22</v>
       </c>
-      <c r="Z5" s="94" t="n">
+      <c r="AA5" s="94" t="n">
         <v>55.12</v>
       </c>
-      <c r="AA5" s="94" t="n">
+      <c r="AB5" s="94" t="n">
         <v>33.93</v>
       </c>
-      <c r="AB5" s="94" t="n">
+      <c r="AC5" s="94" t="n">
         <v>24.13</v>
-      </c>
-      <c r="AC5" s="94" t="n">
-        <v>25.5</v>
       </c>
       <c r="AD5" s="94" t="n">
         <v>25.5</v>
       </c>
       <c r="AE5" s="94" t="n">
-        <v>71.36</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="6">
@@ -6975,124 +6975,124 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="H6" s="92" t="inlineStr">
+      <c r="H6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I6" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I6" s="92" t="inlineStr">
+      <c r="J6" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J6" s="92" t="inlineStr">
+      <c r="K6" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K6" s="92" t="inlineStr">
+      <c r="L6" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L6" s="92" t="inlineStr">
+      <c r="M6" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M6" s="92" t="inlineStr">
+      <c r="N6" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N6" s="92" t="inlineStr">
+      <c r="O6" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O6" s="93" t="inlineStr">
+      <c r="P6" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P6" s="92" t="inlineStr">
+      <c r="Q6" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q6" s="91" t="inlineStr">
+      <c r="R6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R6" s="91" t="inlineStr">
+      <c r="S6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S6" s="92" t="inlineStr">
+      <c r="T6" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T6" s="91" t="inlineStr">
+      <c r="U6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U6" s="91" t="inlineStr">
+      <c r="V6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V6" s="91" t="inlineStr">
+      <c r="W6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W6" s="91" t="inlineStr">
+      <c r="X6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X6" s="91" t="inlineStr">
+      <c r="Y6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y6" s="93" t="inlineStr">
+      <c r="Z6" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z6" s="91" t="inlineStr">
+      <c r="AA6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA6" s="91" t="inlineStr">
+      <c r="AB6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB6" s="92" t="inlineStr">
+      <c r="AC6" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC6" s="91" t="inlineStr">
+      <c r="AD6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD6" s="91" t="inlineStr">
+      <c r="AE6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE6" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -7106,91 +7106,91 @@
         <v>2.95</v>
       </c>
       <c r="C7" s="94" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D7" s="94" t="n">
         <v>0.21</v>
       </c>
-      <c r="D7" s="94" t="n">
+      <c r="E7" s="94" t="n">
         <v>0.57</v>
       </c>
-      <c r="E7" s="94" t="n">
+      <c r="F7" s="94" t="n">
         <v>-0.42</v>
       </c>
-      <c r="F7" s="94" t="n">
+      <c r="G7" s="94" t="n">
         <v>1.19</v>
       </c>
-      <c r="G7" s="94" t="n">
+      <c r="H7" s="94" t="n">
         <v>2.62</v>
       </c>
-      <c r="H7" s="94" t="n">
+      <c r="I7" s="94" t="n">
         <v>3.05</v>
       </c>
-      <c r="I7" s="94" t="n">
+      <c r="J7" s="94" t="n">
         <v>2.03</v>
       </c>
-      <c r="J7" s="94" t="n">
+      <c r="K7" s="94" t="n">
         <v>5.33</v>
-      </c>
-      <c r="K7" s="94" t="n">
-        <v>6.25</v>
       </c>
       <c r="L7" s="94" t="n">
         <v>6.25</v>
       </c>
       <c r="M7" s="94" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="N7" s="94" t="n">
         <v>10.08</v>
       </c>
-      <c r="N7" s="94" t="n">
+      <c r="O7" s="94" t="n">
         <v>10.42</v>
       </c>
-      <c r="O7" s="94" t="n">
+      <c r="P7" s="94" t="n">
         <v>10.11</v>
       </c>
-      <c r="P7" s="94" t="n">
+      <c r="Q7" s="94" t="n">
         <v>7.15</v>
-      </c>
-      <c r="Q7" s="94" t="n">
-        <v>8.029999999999999</v>
       </c>
       <c r="R7" s="94" t="n">
         <v>8.029999999999999</v>
       </c>
       <c r="S7" s="94" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="T7" s="94" t="n">
         <v>5.82</v>
       </c>
-      <c r="T7" s="94" t="n">
+      <c r="U7" s="94" t="n">
         <v>8.9</v>
       </c>
-      <c r="U7" s="94" t="n">
+      <c r="V7" s="94" t="n">
         <v>8.51</v>
       </c>
-      <c r="V7" s="94" t="n">
+      <c r="W7" s="94" t="n">
         <v>10.31</v>
-      </c>
-      <c r="W7" s="94" t="n">
-        <v>10.83</v>
       </c>
       <c r="X7" s="94" t="n">
         <v>10.83</v>
       </c>
       <c r="Y7" s="94" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="Z7" s="94" t="n">
         <v>11.57</v>
       </c>
-      <c r="Z7" s="94" t="n">
+      <c r="AA7" s="94" t="n">
         <v>6.7</v>
       </c>
-      <c r="AA7" s="94" t="n">
+      <c r="AB7" s="94" t="n">
         <v>7.27</v>
       </c>
-      <c r="AB7" s="94" t="n">
+      <c r="AC7" s="94" t="n">
         <v>8</v>
-      </c>
-      <c r="AC7" s="94" t="n">
-        <v>9.42</v>
       </c>
       <c r="AD7" s="94" t="n">
         <v>9.42</v>
       </c>
       <c r="AE7" s="94" t="n">
-        <v>18.36</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="8">
@@ -7203,91 +7203,91 @@
         <v>-0.58</v>
       </c>
       <c r="C8" s="94" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="D8" s="94" t="n">
         <v>17.24</v>
       </c>
-      <c r="D8" s="94" t="n">
+      <c r="E8" s="94" t="n">
         <v>38.43</v>
       </c>
-      <c r="E8" s="94" t="n">
+      <c r="F8" s="94" t="n">
         <v>47.55</v>
       </c>
-      <c r="F8" s="94" t="n">
+      <c r="G8" s="94" t="n">
         <v>54.27</v>
       </c>
-      <c r="G8" s="94" t="n">
+      <c r="H8" s="94" t="n">
         <v>56</v>
       </c>
-      <c r="H8" s="94" t="n">
+      <c r="I8" s="94" t="n">
         <v>60.03</v>
       </c>
-      <c r="I8" s="94" t="n">
+      <c r="J8" s="94" t="n">
         <v>59.12</v>
       </c>
-      <c r="J8" s="94" t="n">
+      <c r="K8" s="94" t="n">
         <v>60.55</v>
-      </c>
-      <c r="K8" s="94" t="n">
-        <v>61.09</v>
       </c>
       <c r="L8" s="94" t="n">
         <v>61.09</v>
       </c>
       <c r="M8" s="94" t="n">
+        <v>61.09</v>
+      </c>
+      <c r="N8" s="94" t="n">
         <v>62.55</v>
       </c>
-      <c r="N8" s="94" t="n">
+      <c r="O8" s="94" t="n">
         <v>63.46</v>
       </c>
-      <c r="O8" s="94" t="n">
+      <c r="P8" s="94" t="n">
         <v>64.05</v>
       </c>
-      <c r="P8" s="94" t="n">
+      <c r="Q8" s="94" t="n">
         <v>64.12</v>
-      </c>
-      <c r="Q8" s="94" t="n">
-        <v>66.14</v>
       </c>
       <c r="R8" s="94" t="n">
         <v>66.14</v>
       </c>
       <c r="S8" s="94" t="n">
+        <v>66.14</v>
+      </c>
+      <c r="T8" s="94" t="n">
         <v>61.5</v>
       </c>
-      <c r="T8" s="94" t="n">
+      <c r="U8" s="94" t="n">
         <v>62.78</v>
       </c>
-      <c r="U8" s="94" t="n">
+      <c r="V8" s="94" t="n">
         <v>63.73</v>
       </c>
-      <c r="V8" s="94" t="n">
+      <c r="W8" s="94" t="n">
         <v>63.74</v>
-      </c>
-      <c r="W8" s="94" t="n">
-        <v>65.31</v>
       </c>
       <c r="X8" s="94" t="n">
         <v>65.31</v>
       </c>
       <c r="Y8" s="94" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="Z8" s="94" t="n">
         <v>61.57</v>
       </c>
-      <c r="Z8" s="94" t="n">
+      <c r="AA8" s="94" t="n">
         <v>59.48</v>
       </c>
-      <c r="AA8" s="94" t="n">
+      <c r="AB8" s="94" t="n">
         <v>61</v>
       </c>
-      <c r="AB8" s="94" t="n">
+      <c r="AC8" s="94" t="n">
         <v>57.54</v>
-      </c>
-      <c r="AC8" s="94" t="n">
-        <v>58.07</v>
       </c>
       <c r="AD8" s="94" t="n">
         <v>58.07</v>
       </c>
       <c r="AE8" s="94" t="n">
-        <v>64.23999999999999</v>
+        <v>58.07</v>
       </c>
     </row>
     <row r="9">
@@ -7300,91 +7300,91 @@
         <v>22.95</v>
       </c>
       <c r="C9" s="94" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="D9" s="94" t="n">
         <v>26.81</v>
       </c>
-      <c r="D9" s="94" t="n">
+      <c r="E9" s="94" t="n">
         <v>28.13</v>
       </c>
-      <c r="E9" s="94" t="n">
+      <c r="F9" s="94" t="n">
         <v>25.11</v>
       </c>
-      <c r="F9" s="94" t="n">
+      <c r="G9" s="94" t="n">
         <v>29.08</v>
       </c>
-      <c r="G9" s="94" t="n">
+      <c r="H9" s="94" t="n">
         <v>36.65</v>
       </c>
-      <c r="H9" s="94" t="n">
+      <c r="I9" s="94" t="n">
         <v>19.14</v>
       </c>
-      <c r="I9" s="94" t="n">
+      <c r="J9" s="94" t="n">
         <v>20.17</v>
       </c>
-      <c r="J9" s="94" t="n">
+      <c r="K9" s="94" t="n">
         <v>26.21</v>
-      </c>
-      <c r="K9" s="94" t="n">
-        <v>22.22</v>
       </c>
       <c r="L9" s="94" t="n">
         <v>22.22</v>
       </c>
       <c r="M9" s="94" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="N9" s="94" t="n">
         <v>32.22</v>
       </c>
-      <c r="N9" s="94" t="n">
+      <c r="O9" s="94" t="n">
         <v>40.27</v>
       </c>
-      <c r="O9" s="94" t="n">
+      <c r="P9" s="94" t="n">
         <v>51.11</v>
       </c>
-      <c r="P9" s="94" t="n">
+      <c r="Q9" s="94" t="n">
         <v>45.03</v>
-      </c>
-      <c r="Q9" s="94" t="n">
-        <v>48.61</v>
       </c>
       <c r="R9" s="94" t="n">
         <v>48.61</v>
       </c>
       <c r="S9" s="94" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="T9" s="94" t="n">
         <v>32.49</v>
       </c>
-      <c r="T9" s="94" t="n">
+      <c r="U9" s="94" t="n">
         <v>47.34</v>
       </c>
-      <c r="U9" s="94" t="n">
+      <c r="V9" s="94" t="n">
         <v>54.26</v>
       </c>
-      <c r="V9" s="94" t="n">
+      <c r="W9" s="94" t="n">
         <v>58</v>
-      </c>
-      <c r="W9" s="94" t="n">
-        <v>59.83</v>
       </c>
       <c r="X9" s="94" t="n">
         <v>59.83</v>
       </c>
       <c r="Y9" s="94" t="n">
+        <v>59.83</v>
+      </c>
+      <c r="Z9" s="94" t="n">
         <v>69.86</v>
       </c>
-      <c r="Z9" s="94" t="n">
+      <c r="AA9" s="94" t="n">
         <v>52.7</v>
       </c>
-      <c r="AA9" s="94" t="n">
+      <c r="AB9" s="94" t="n">
         <v>50.83</v>
       </c>
-      <c r="AB9" s="94" t="n">
+      <c r="AC9" s="94" t="n">
         <v>39.77</v>
-      </c>
-      <c r="AC9" s="94" t="n">
-        <v>47.44</v>
       </c>
       <c r="AD9" s="94" t="n">
         <v>47.44</v>
       </c>
       <c r="AE9" s="94" t="n">
-        <v>85.52</v>
+        <v>47.44</v>
       </c>
     </row>
     <row r="10">
@@ -7398,149 +7398,149 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C10" s="91" t="inlineStr">
+      <c r="C10" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D10" s="92" t="inlineStr">
+      <c r="E10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E10" s="92" t="inlineStr">
+      <c r="F10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F10" s="92" t="inlineStr">
+      <c r="G10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G10" s="91" t="inlineStr">
+      <c r="H10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H10" s="92" t="inlineStr">
+      <c r="I10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I10" s="92" t="inlineStr">
+      <c r="J10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J10" s="92" t="inlineStr">
+      <c r="K10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K10" s="92" t="inlineStr">
+      <c r="L10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L10" s="92" t="inlineStr">
+      <c r="M10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M10" s="92" t="inlineStr">
+      <c r="N10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N10" s="93" t="inlineStr">
+      <c r="O10" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O10" s="93" t="inlineStr">
+      <c r="P10" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P10" s="93" t="inlineStr">
+      <c r="Q10" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q10" s="93" t="inlineStr">
+      <c r="R10" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R10" s="93" t="inlineStr">
+      <c r="S10" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S10" s="92" t="inlineStr">
+      <c r="T10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T10" s="92" t="inlineStr">
+      <c r="U10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U10" s="92" t="inlineStr">
+      <c r="V10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V10" s="92" t="inlineStr">
+      <c r="W10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W10" s="92" t="inlineStr">
+      <c r="X10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X10" s="92" t="inlineStr">
+      <c r="Y10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y10" s="93" t="inlineStr">
+      <c r="Z10" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z10" s="92" t="inlineStr">
+      <c r="AA10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA10" s="92" t="inlineStr">
+      <c r="AB10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB10" s="92" t="inlineStr">
+      <c r="AC10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC10" s="92" t="inlineStr">
+      <c r="AD10" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD10" s="92" t="inlineStr">
+      <c r="AE10" s="92" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AE10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -7554,91 +7554,91 @@
         <v>-3.56</v>
       </c>
       <c r="C11" s="94" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="D11" s="94" t="n">
         <v>-4.61</v>
       </c>
-      <c r="D11" s="94" t="n">
+      <c r="E11" s="94" t="n">
         <v>-4.67</v>
       </c>
-      <c r="E11" s="94" t="n">
+      <c r="F11" s="94" t="n">
         <v>-4.8</v>
       </c>
-      <c r="F11" s="94" t="n">
+      <c r="G11" s="94" t="n">
         <v>-3.32</v>
       </c>
-      <c r="G11" s="94" t="n">
+      <c r="H11" s="94" t="n">
         <v>-3.09</v>
       </c>
-      <c r="H11" s="94" t="n">
+      <c r="I11" s="94" t="n">
         <v>-2.2</v>
       </c>
-      <c r="I11" s="94" t="n">
+      <c r="J11" s="94" t="n">
         <v>-2.9</v>
       </c>
-      <c r="J11" s="94" t="n">
+      <c r="K11" s="94" t="n">
         <v>-2.76</v>
-      </c>
-      <c r="K11" s="94" t="n">
-        <v>-2.26</v>
       </c>
       <c r="L11" s="94" t="n">
         <v>-2.26</v>
       </c>
       <c r="M11" s="94" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="N11" s="94" t="n">
         <v>-0.05</v>
       </c>
-      <c r="N11" s="94" t="n">
+      <c r="O11" s="94" t="n">
         <v>0.95</v>
       </c>
-      <c r="O11" s="94" t="n">
+      <c r="P11" s="94" t="n">
         <v>-0.3</v>
       </c>
-      <c r="P11" s="94" t="n">
+      <c r="Q11" s="94" t="n">
         <v>-3.36</v>
-      </c>
-      <c r="Q11" s="94" t="n">
-        <v>-1.54</v>
       </c>
       <c r="R11" s="94" t="n">
         <v>-1.54</v>
       </c>
       <c r="S11" s="94" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="T11" s="94" t="n">
         <v>-4.33</v>
       </c>
-      <c r="T11" s="94" t="n">
+      <c r="U11" s="94" t="n">
         <v>-2.55</v>
       </c>
-      <c r="U11" s="94" t="n">
+      <c r="V11" s="94" t="n">
         <v>-2.78</v>
       </c>
-      <c r="V11" s="94" t="n">
+      <c r="W11" s="94" t="n">
         <v>-0.97</v>
-      </c>
-      <c r="W11" s="94" t="n">
-        <v>-0.37</v>
       </c>
       <c r="X11" s="94" t="n">
         <v>-0.37</v>
       </c>
       <c r="Y11" s="94" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="Z11" s="94" t="n">
         <v>-0.48</v>
       </c>
-      <c r="Z11" s="94" t="n">
+      <c r="AA11" s="94" t="n">
         <v>-2.89</v>
       </c>
-      <c r="AA11" s="94" t="n">
+      <c r="AB11" s="94" t="n">
         <v>-1.53</v>
       </c>
-      <c r="AB11" s="94" t="n">
+      <c r="AC11" s="94" t="n">
         <v>1.23</v>
-      </c>
-      <c r="AC11" s="94" t="n">
-        <v>-1.74</v>
       </c>
       <c r="AD11" s="94" t="n">
         <v>-1.74</v>
       </c>
       <c r="AE11" s="94" t="n">
-        <v>4.95</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="12">
@@ -7651,91 +7651,91 @@
         <v>-19.01</v>
       </c>
       <c r="C12" s="94" t="n">
+        <v>-19.01</v>
+      </c>
+      <c r="D12" s="94" t="n">
         <v>-3.24</v>
       </c>
-      <c r="D12" s="94" t="n">
+      <c r="E12" s="94" t="n">
         <v>11.48</v>
       </c>
-      <c r="E12" s="94" t="n">
+      <c r="F12" s="94" t="n">
         <v>22.73</v>
       </c>
-      <c r="F12" s="94" t="n">
+      <c r="G12" s="94" t="n">
         <v>29.65</v>
       </c>
-      <c r="G12" s="94" t="n">
+      <c r="H12" s="94" t="n">
         <v>32.8</v>
       </c>
-      <c r="H12" s="94" t="n">
+      <c r="I12" s="94" t="n">
         <v>39.82</v>
       </c>
-      <c r="I12" s="94" t="n">
+      <c r="J12" s="94" t="n">
         <v>39.63</v>
       </c>
-      <c r="J12" s="94" t="n">
+      <c r="K12" s="94" t="n">
         <v>39.19</v>
-      </c>
-      <c r="K12" s="94" t="n">
-        <v>40.35</v>
       </c>
       <c r="L12" s="94" t="n">
         <v>40.35</v>
       </c>
       <c r="M12" s="94" t="n">
+        <v>40.35</v>
+      </c>
+      <c r="N12" s="94" t="n">
         <v>43.31</v>
       </c>
-      <c r="N12" s="94" t="n">
+      <c r="O12" s="94" t="n">
         <v>43.21</v>
       </c>
-      <c r="O12" s="94" t="n">
+      <c r="P12" s="94" t="n">
         <v>43.01</v>
       </c>
-      <c r="P12" s="94" t="n">
+      <c r="Q12" s="94" t="n">
         <v>43.84</v>
-      </c>
-      <c r="Q12" s="94" t="n">
-        <v>44.68</v>
       </c>
       <c r="R12" s="94" t="n">
         <v>44.68</v>
       </c>
       <c r="S12" s="94" t="n">
+        <v>44.68</v>
+      </c>
+      <c r="T12" s="94" t="n">
         <v>40.83</v>
       </c>
-      <c r="T12" s="94" t="n">
+      <c r="U12" s="94" t="n">
         <v>40.04</v>
       </c>
-      <c r="U12" s="94" t="n">
+      <c r="V12" s="94" t="n">
         <v>41.77</v>
       </c>
-      <c r="V12" s="94" t="n">
+      <c r="W12" s="94" t="n">
         <v>41.35</v>
-      </c>
-      <c r="W12" s="94" t="n">
-        <v>43.49</v>
       </c>
       <c r="X12" s="94" t="n">
         <v>43.49</v>
       </c>
       <c r="Y12" s="94" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="Z12" s="94" t="n">
         <v>41.39</v>
       </c>
-      <c r="Z12" s="94" t="n">
+      <c r="AA12" s="94" t="n">
         <v>42.1</v>
       </c>
-      <c r="AA12" s="94" t="n">
+      <c r="AB12" s="94" t="n">
         <v>43.01</v>
       </c>
-      <c r="AB12" s="94" t="n">
+      <c r="AC12" s="94" t="n">
         <v>43.49</v>
-      </c>
-      <c r="AC12" s="94" t="n">
-        <v>40.45</v>
       </c>
       <c r="AD12" s="94" t="n">
         <v>40.45</v>
       </c>
       <c r="AE12" s="94" t="n">
-        <v>45.87</v>
+        <v>40.45</v>
       </c>
     </row>
     <row r="13">
@@ -7748,91 +7748,91 @@
         <v>5.09</v>
       </c>
       <c r="C13" s="94" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="D13" s="94" t="n">
         <v>16.8</v>
       </c>
-      <c r="D13" s="94" t="n">
+      <c r="E13" s="94" t="n">
         <v>6.77</v>
       </c>
-      <c r="E13" s="94" t="n">
+      <c r="F13" s="94" t="n">
         <v>7.15</v>
       </c>
-      <c r="F13" s="94" t="n">
+      <c r="G13" s="94" t="n">
         <v>14.43</v>
       </c>
-      <c r="G13" s="94" t="n">
+      <c r="H13" s="94" t="n">
         <v>27.11</v>
       </c>
-      <c r="H13" s="94" t="n">
+      <c r="I13" s="94" t="n">
         <v>11.06</v>
       </c>
-      <c r="I13" s="94" t="n">
+      <c r="J13" s="94" t="n">
         <v>13.13</v>
       </c>
-      <c r="J13" s="94" t="n">
+      <c r="K13" s="94" t="n">
         <v>15.59</v>
-      </c>
-      <c r="K13" s="94" t="n">
-        <v>15.18</v>
       </c>
       <c r="L13" s="94" t="n">
         <v>15.18</v>
       </c>
       <c r="M13" s="94" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="N13" s="94" t="n">
         <v>34.95</v>
       </c>
-      <c r="N13" s="94" t="n">
+      <c r="O13" s="94" t="n">
         <v>58.81</v>
       </c>
-      <c r="O13" s="94" t="n">
+      <c r="P13" s="94" t="n">
         <v>67.45999999999999</v>
       </c>
-      <c r="P13" s="94" t="n">
+      <c r="Q13" s="94" t="n">
         <v>58.78</v>
-      </c>
-      <c r="Q13" s="94" t="n">
-        <v>69.37</v>
       </c>
       <c r="R13" s="94" t="n">
         <v>69.37</v>
       </c>
       <c r="S13" s="94" t="n">
+        <v>69.37</v>
+      </c>
+      <c r="T13" s="94" t="n">
         <v>17.41</v>
       </c>
-      <c r="T13" s="94" t="n">
+      <c r="U13" s="94" t="n">
         <v>32.88</v>
       </c>
-      <c r="U13" s="94" t="n">
+      <c r="V13" s="94" t="n">
         <v>46.93</v>
       </c>
-      <c r="V13" s="94" t="n">
+      <c r="W13" s="94" t="n">
         <v>41.51</v>
-      </c>
-      <c r="W13" s="94" t="n">
-        <v>45.57</v>
       </c>
       <c r="X13" s="94" t="n">
         <v>45.57</v>
       </c>
       <c r="Y13" s="94" t="n">
+        <v>45.57</v>
+      </c>
+      <c r="Z13" s="94" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="Z13" s="94" t="n">
+      <c r="AA13" s="94" t="n">
         <v>34.52</v>
       </c>
-      <c r="AA13" s="94" t="n">
+      <c r="AB13" s="94" t="n">
         <v>34.18</v>
       </c>
-      <c r="AB13" s="94" t="n">
+      <c r="AC13" s="94" t="n">
         <v>37.1</v>
-      </c>
-      <c r="AC13" s="94" t="n">
-        <v>18.22</v>
       </c>
       <c r="AD13" s="94" t="n">
         <v>18.22</v>
       </c>
       <c r="AE13" s="94" t="n">
-        <v>53.52</v>
+        <v>18.22</v>
       </c>
     </row>
     <row r="14">
@@ -7846,129 +7846,129 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C14" s="91" t="inlineStr">
+      <c r="C14" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D14" s="91" t="inlineStr">
+      <c r="E14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E14" s="92" t="inlineStr">
+      <c r="F14" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F14" s="92" t="inlineStr">
+      <c r="G14" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G14" s="92" t="inlineStr">
+      <c r="H14" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H14" s="92" t="inlineStr">
+      <c r="I14" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I14" s="92" t="inlineStr">
+      <c r="J14" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J14" s="92" t="inlineStr">
+      <c r="K14" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K14" s="92" t="inlineStr">
+      <c r="L14" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L14" s="92" t="inlineStr">
+      <c r="M14" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M14" s="91" t="inlineStr">
+      <c r="N14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N14" s="93" t="inlineStr">
+      <c r="O14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O14" s="93" t="inlineStr">
+      <c r="P14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P14" s="93" t="inlineStr">
+      <c r="Q14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q14" s="93" t="inlineStr">
+      <c r="R14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R14" s="93" t="inlineStr">
+      <c r="S14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S14" s="91" t="inlineStr">
+      <c r="T14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T14" s="91" t="inlineStr">
+      <c r="U14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U14" s="91" t="inlineStr">
+      <c r="V14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V14" s="91" t="inlineStr">
+      <c r="W14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W14" s="93" t="inlineStr">
+      <c r="X14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X14" s="93" t="inlineStr">
+      <c r="Y14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y14" s="93" t="inlineStr">
+      <c r="Z14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z14" s="93" t="inlineStr">
+      <c r="AA14" s="93" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AA14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AB14" s="91" t="inlineStr">
@@ -8002,91 +8002,91 @@
         <v>16.06</v>
       </c>
       <c r="C15" s="94" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="D15" s="94" t="n">
         <v>17.42</v>
       </c>
-      <c r="D15" s="94" t="n">
+      <c r="E15" s="94" t="n">
         <v>18.26</v>
       </c>
-      <c r="E15" s="94" t="n">
+      <c r="F15" s="94" t="n">
         <v>15.25</v>
       </c>
-      <c r="F15" s="94" t="n">
+      <c r="G15" s="94" t="n">
         <v>16.89</v>
       </c>
-      <c r="G15" s="94" t="n">
+      <c r="H15" s="94" t="n">
         <v>17.36</v>
       </c>
-      <c r="H15" s="94" t="n">
+      <c r="I15" s="94" t="n">
         <v>16.84</v>
       </c>
-      <c r="I15" s="94" t="n">
+      <c r="J15" s="94" t="n">
         <v>17.41</v>
       </c>
-      <c r="J15" s="94" t="n">
+      <c r="K15" s="94" t="n">
         <v>21.22</v>
-      </c>
-      <c r="K15" s="94" t="n">
-        <v>19.93</v>
       </c>
       <c r="L15" s="94" t="n">
         <v>19.93</v>
       </c>
       <c r="M15" s="94" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="N15" s="94" t="n">
         <v>21.93</v>
       </c>
-      <c r="N15" s="94" t="n">
+      <c r="O15" s="94" t="n">
         <v>25.74</v>
       </c>
-      <c r="O15" s="94" t="n">
+      <c r="P15" s="94" t="n">
         <v>24.98</v>
       </c>
-      <c r="P15" s="94" t="n">
+      <c r="Q15" s="94" t="n">
         <v>20.9</v>
-      </c>
-      <c r="Q15" s="94" t="n">
-        <v>17.47</v>
       </c>
       <c r="R15" s="94" t="n">
         <v>17.47</v>
       </c>
       <c r="S15" s="94" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="T15" s="94" t="n">
         <v>16.41</v>
       </c>
-      <c r="T15" s="94" t="n">
+      <c r="U15" s="94" t="n">
         <v>16.19</v>
       </c>
-      <c r="U15" s="94" t="n">
+      <c r="V15" s="94" t="n">
         <v>16.5</v>
       </c>
-      <c r="V15" s="94" t="n">
+      <c r="W15" s="94" t="n">
         <v>19.72</v>
-      </c>
-      <c r="W15" s="94" t="n">
-        <v>23.88</v>
       </c>
       <c r="X15" s="94" t="n">
         <v>23.88</v>
       </c>
       <c r="Y15" s="94" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="Z15" s="94" t="n">
         <v>23.44</v>
       </c>
-      <c r="Z15" s="94" t="n">
+      <c r="AA15" s="94" t="n">
         <v>19.49</v>
       </c>
-      <c r="AA15" s="94" t="n">
+      <c r="AB15" s="94" t="n">
         <v>17.35</v>
       </c>
-      <c r="AB15" s="94" t="n">
+      <c r="AC15" s="94" t="n">
         <v>18.44</v>
-      </c>
-      <c r="AC15" s="94" t="n">
-        <v>18.46</v>
       </c>
       <c r="AD15" s="94" t="n">
         <v>18.46</v>
       </c>
       <c r="AE15" s="94" t="n">
-        <v>20.99</v>
+        <v>18.46</v>
       </c>
     </row>
     <row r="16">
@@ -8099,91 +8099,91 @@
         <v>9.19</v>
       </c>
       <c r="C16" s="94" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="D16" s="94" t="n">
         <v>0.44</v>
       </c>
-      <c r="D16" s="94" t="n">
+      <c r="E16" s="94" t="n">
         <v>2.07</v>
       </c>
-      <c r="E16" s="94" t="n">
+      <c r="F16" s="94" t="n">
         <v>4.55</v>
       </c>
-      <c r="F16" s="94" t="n">
+      <c r="G16" s="94" t="n">
         <v>4.38</v>
       </c>
-      <c r="G16" s="94" t="n">
+      <c r="H16" s="94" t="n">
         <v>11.57</v>
       </c>
-      <c r="H16" s="94" t="n">
+      <c r="I16" s="94" t="n">
         <v>13.82</v>
       </c>
-      <c r="I16" s="94" t="n">
+      <c r="J16" s="94" t="n">
         <v>17.16</v>
       </c>
-      <c r="J16" s="94" t="n">
+      <c r="K16" s="94" t="n">
         <v>24.97</v>
-      </c>
-      <c r="K16" s="94" t="n">
-        <v>24.68</v>
       </c>
       <c r="L16" s="94" t="n">
         <v>24.68</v>
       </c>
       <c r="M16" s="94" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="N16" s="94" t="n">
         <v>32.73</v>
       </c>
-      <c r="N16" s="94" t="n">
+      <c r="O16" s="94" t="n">
         <v>35.67</v>
       </c>
-      <c r="O16" s="94" t="n">
+      <c r="P16" s="94" t="n">
         <v>37.35</v>
       </c>
-      <c r="P16" s="94" t="n">
+      <c r="Q16" s="94" t="n">
         <v>36.72</v>
-      </c>
-      <c r="Q16" s="94" t="n">
-        <v>37.53</v>
       </c>
       <c r="R16" s="94" t="n">
         <v>37.53</v>
       </c>
       <c r="S16" s="94" t="n">
+        <v>37.53</v>
+      </c>
+      <c r="T16" s="94" t="n">
         <v>35.08</v>
       </c>
-      <c r="T16" s="94" t="n">
+      <c r="U16" s="94" t="n">
         <v>36.89</v>
       </c>
-      <c r="U16" s="94" t="n">
+      <c r="V16" s="94" t="n">
         <v>39.01</v>
       </c>
-      <c r="V16" s="94" t="n">
+      <c r="W16" s="94" t="n">
         <v>38</v>
-      </c>
-      <c r="W16" s="94" t="n">
-        <v>40.9</v>
       </c>
       <c r="X16" s="94" t="n">
         <v>40.9</v>
       </c>
       <c r="Y16" s="94" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="Z16" s="94" t="n">
         <v>39.7</v>
       </c>
-      <c r="Z16" s="94" t="n">
+      <c r="AA16" s="94" t="n">
         <v>35.15</v>
       </c>
-      <c r="AA16" s="94" t="n">
+      <c r="AB16" s="94" t="n">
         <v>29.97</v>
       </c>
-      <c r="AB16" s="94" t="n">
+      <c r="AC16" s="94" t="n">
         <v>30.04</v>
-      </c>
-      <c r="AC16" s="94" t="n">
-        <v>27.53</v>
       </c>
       <c r="AD16" s="94" t="n">
         <v>27.53</v>
       </c>
       <c r="AE16" s="94" t="n">
-        <v>33.35</v>
+        <v>27.53</v>
       </c>
     </row>
     <row r="17">
@@ -8196,91 +8196,91 @@
         <v>18.53</v>
       </c>
       <c r="C17" s="94" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="D17" s="94" t="n">
         <v>31.84</v>
       </c>
-      <c r="D17" s="94" t="n">
+      <c r="E17" s="94" t="n">
         <v>32.06</v>
       </c>
-      <c r="E17" s="94" t="n">
+      <c r="F17" s="94" t="n">
         <v>24.45</v>
       </c>
-      <c r="F17" s="94" t="n">
+      <c r="G17" s="94" t="n">
         <v>34.7</v>
       </c>
-      <c r="G17" s="94" t="n">
+      <c r="H17" s="94" t="n">
         <v>41.1</v>
       </c>
-      <c r="H17" s="94" t="n">
+      <c r="I17" s="94" t="n">
         <v>35.5</v>
       </c>
-      <c r="I17" s="94" t="n">
+      <c r="J17" s="94" t="n">
         <v>28.03</v>
       </c>
-      <c r="J17" s="94" t="n">
+      <c r="K17" s="94" t="n">
         <v>43.16</v>
-      </c>
-      <c r="K17" s="94" t="n">
-        <v>32.68</v>
       </c>
       <c r="L17" s="94" t="n">
         <v>32.68</v>
       </c>
       <c r="M17" s="94" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="N17" s="94" t="n">
         <v>49.51</v>
       </c>
-      <c r="N17" s="94" t="n">
+      <c r="O17" s="94" t="n">
         <v>82.73999999999999</v>
       </c>
-      <c r="O17" s="94" t="n">
+      <c r="P17" s="94" t="n">
         <v>82.23999999999999</v>
       </c>
-      <c r="P17" s="94" t="n">
+      <c r="Q17" s="94" t="n">
         <v>69.43000000000001</v>
-      </c>
-      <c r="Q17" s="94" t="n">
-        <v>63.22</v>
       </c>
       <c r="R17" s="94" t="n">
         <v>63.22</v>
       </c>
       <c r="S17" s="94" t="n">
+        <v>63.22</v>
+      </c>
+      <c r="T17" s="94" t="n">
         <v>37.82</v>
       </c>
-      <c r="T17" s="94" t="n">
+      <c r="U17" s="94" t="n">
         <v>44.15</v>
       </c>
-      <c r="U17" s="94" t="n">
+      <c r="V17" s="94" t="n">
         <v>52.92</v>
       </c>
-      <c r="V17" s="94" t="n">
+      <c r="W17" s="94" t="n">
         <v>52.98</v>
-      </c>
-      <c r="W17" s="94" t="n">
-        <v>73.12</v>
       </c>
       <c r="X17" s="94" t="n">
         <v>73.12</v>
       </c>
       <c r="Y17" s="94" t="n">
+        <v>73.12</v>
+      </c>
+      <c r="Z17" s="94" t="n">
         <v>80.18000000000001</v>
       </c>
-      <c r="Z17" s="94" t="n">
+      <c r="AA17" s="94" t="n">
         <v>66.63</v>
       </c>
-      <c r="AA17" s="94" t="n">
+      <c r="AB17" s="94" t="n">
         <v>41.31</v>
       </c>
-      <c r="AB17" s="94" t="n">
+      <c r="AC17" s="94" t="n">
         <v>43.77</v>
-      </c>
-      <c r="AC17" s="94" t="n">
-        <v>41.12</v>
       </c>
       <c r="AD17" s="94" t="n">
         <v>41.12</v>
       </c>
       <c r="AE17" s="94" t="n">
-        <v>71.27</v>
+        <v>41.12</v>
       </c>
     </row>
     <row r="18">
@@ -8289,154 +8289,154 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="91" t="inlineStr">
+      <c r="B18" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C18" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C18" s="91" t="inlineStr">
+      <c r="E18" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F18" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G18" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H18" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D18" s="92" t="inlineStr">
+      <c r="J18" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K18" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T18" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E18" s="92" t="inlineStr">
+      <c r="U18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V18" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F18" s="92" t="inlineStr">
+      <c r="W18" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G18" s="92" t="inlineStr">
+      <c r="X18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z18" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H18" s="91" t="inlineStr">
+      <c r="AA18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I18" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J18" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K18" s="91" t="inlineStr">
+      <c r="AB18" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC18" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L18" s="91" t="inlineStr">
+      <c r="AE18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="M18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S18" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="T18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U18" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V18" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y18" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA18" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB18" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE18" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -8447,94 +8447,94 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
+        <v>-9.69</v>
+      </c>
+      <c r="C19" s="94" t="n">
+        <v>-9.69</v>
+      </c>
+      <c r="D19" s="94" t="n">
         <v>-4.57</v>
       </c>
-      <c r="C19" s="94" t="n">
-        <v>-4.57</v>
-      </c>
-      <c r="D19" s="94" t="n">
+      <c r="E19" s="94" t="n">
         <v>-4.01</v>
       </c>
-      <c r="E19" s="94" t="n">
+      <c r="F19" s="94" t="n">
         <v>-4.59</v>
       </c>
-      <c r="F19" s="94" t="n">
+      <c r="G19" s="94" t="n">
         <v>-5.52</v>
       </c>
-      <c r="G19" s="94" t="n">
+      <c r="H19" s="94" t="n">
         <v>-4.65</v>
       </c>
-      <c r="H19" s="94" t="n">
+      <c r="I19" s="94" t="n">
         <v>-5.39</v>
       </c>
-      <c r="I19" s="94" t="n">
+      <c r="J19" s="94" t="n">
         <v>-4.36</v>
       </c>
-      <c r="J19" s="94" t="n">
+      <c r="K19" s="94" t="n">
         <v>-3.46</v>
-      </c>
-      <c r="K19" s="94" t="n">
-        <v>-4.44</v>
       </c>
       <c r="L19" s="94" t="n">
         <v>-4.44</v>
       </c>
       <c r="M19" s="94" t="n">
+        <v>-4.44</v>
+      </c>
+      <c r="N19" s="94" t="n">
         <v>-3.48</v>
       </c>
-      <c r="N19" s="94" t="n">
+      <c r="O19" s="94" t="n">
         <v>-3.35</v>
       </c>
-      <c r="O19" s="94" t="n">
+      <c r="P19" s="94" t="n">
         <v>-7.21</v>
       </c>
-      <c r="P19" s="94" t="n">
+      <c r="Q19" s="94" t="n">
         <v>-6.57</v>
-      </c>
-      <c r="Q19" s="94" t="n">
-        <v>-6.81</v>
       </c>
       <c r="R19" s="94" t="n">
         <v>-6.81</v>
       </c>
       <c r="S19" s="94" t="n">
+        <v>-6.81</v>
+      </c>
+      <c r="T19" s="94" t="n">
         <v>-8.75</v>
       </c>
-      <c r="T19" s="94" t="n">
+      <c r="U19" s="94" t="n">
         <v>-7.97</v>
       </c>
-      <c r="U19" s="94" t="n">
+      <c r="V19" s="94" t="n">
         <v>-7.67</v>
       </c>
-      <c r="V19" s="94" t="n">
+      <c r="W19" s="94" t="n">
         <v>-7.24</v>
-      </c>
-      <c r="W19" s="94" t="n">
-        <v>-5.26</v>
       </c>
       <c r="X19" s="94" t="n">
         <v>-5.26</v>
       </c>
       <c r="Y19" s="94" t="n">
+        <v>-5.26</v>
+      </c>
+      <c r="Z19" s="94" t="n">
         <v>-5.54</v>
       </c>
-      <c r="Z19" s="94" t="n">
+      <c r="AA19" s="94" t="n">
         <v>-4.01</v>
       </c>
-      <c r="AA19" s="94" t="n">
+      <c r="AB19" s="94" t="n">
         <v>-4.49</v>
       </c>
-      <c r="AB19" s="94" t="n">
+      <c r="AC19" s="94" t="n">
         <v>-3.26</v>
-      </c>
-      <c r="AC19" s="94" t="n">
-        <v>-1.29</v>
       </c>
       <c r="AD19" s="94" t="n">
         <v>-1.29</v>
       </c>
       <c r="AE19" s="94" t="n">
-        <v>-2.29</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="20">
@@ -8544,191 +8544,191 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
+        <v>-6.83</v>
+      </c>
+      <c r="C20" s="94" t="n">
+        <v>-6.83</v>
+      </c>
+      <c r="D20" s="94" t="n">
         <v>-1.39</v>
       </c>
-      <c r="C20" s="94" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="D20" s="94" t="n">
+      <c r="E20" s="94" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E20" s="94" t="n">
+      <c r="F20" s="94" t="n">
         <v>-2.42</v>
       </c>
-      <c r="F20" s="94" t="n">
+      <c r="G20" s="94" t="n">
         <v>-2.09</v>
       </c>
-      <c r="G20" s="94" t="n">
+      <c r="H20" s="94" t="n">
         <v>-0.28</v>
       </c>
-      <c r="H20" s="94" t="n">
+      <c r="I20" s="94" t="n">
         <v>0.06</v>
       </c>
-      <c r="I20" s="94" t="n">
+      <c r="J20" s="94" t="n">
         <v>0.25</v>
       </c>
-      <c r="J20" s="94" t="n">
+      <c r="K20" s="94" t="n">
         <v>0.51</v>
-      </c>
-      <c r="K20" s="94" t="n">
-        <v>-1.35</v>
       </c>
       <c r="L20" s="94" t="n">
         <v>-1.35</v>
       </c>
       <c r="M20" s="94" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="N20" s="94" t="n">
         <v>-1.04</v>
       </c>
-      <c r="N20" s="94" t="n">
+      <c r="O20" s="94" t="n">
         <v>-1.01</v>
       </c>
-      <c r="O20" s="94" t="n">
+      <c r="P20" s="94" t="n">
         <v>-1.82</v>
       </c>
-      <c r="P20" s="94" t="n">
+      <c r="Q20" s="94" t="n">
         <v>-0.48</v>
-      </c>
-      <c r="Q20" s="94" t="n">
-        <v>-1.31</v>
       </c>
       <c r="R20" s="94" t="n">
         <v>-1.31</v>
       </c>
       <c r="S20" s="94" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="T20" s="94" t="n">
         <v>-1.72</v>
       </c>
-      <c r="T20" s="94" t="n">
+      <c r="U20" s="94" t="n">
         <v>-0.63</v>
       </c>
-      <c r="U20" s="94" t="n">
+      <c r="V20" s="94" t="n">
         <v>-1.08</v>
       </c>
-      <c r="V20" s="94" t="n">
+      <c r="W20" s="94" t="n">
         <v>-0.2</v>
-      </c>
-      <c r="W20" s="94" t="n">
-        <v>3.12</v>
       </c>
       <c r="X20" s="94" t="n">
         <v>3.12</v>
       </c>
       <c r="Y20" s="94" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Z20" s="94" t="n">
         <v>3.32</v>
       </c>
-      <c r="Z20" s="94" t="n">
+      <c r="AA20" s="94" t="n">
         <v>6.32</v>
       </c>
-      <c r="AA20" s="94" t="n">
+      <c r="AB20" s="94" t="n">
         <v>5.61</v>
       </c>
-      <c r="AB20" s="94" t="n">
+      <c r="AC20" s="94" t="n">
         <v>8.16</v>
-      </c>
-      <c r="AC20" s="94" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="AD20" s="94" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AE20" s="94" t="n">
-        <v>6.19</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="96" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="94" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="C21" s="94" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="D21" s="94" t="n">
         <v>76.8</v>
       </c>
-      <c r="C21" s="94" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="D21" s="94" t="n">
+      <c r="E21" s="94" t="n">
         <v>52.81</v>
       </c>
-      <c r="E21" s="94" t="n">
+      <c r="F21" s="94" t="n">
         <v>33.59</v>
       </c>
-      <c r="F21" s="94" t="n">
+      <c r="G21" s="94" t="n">
         <v>5.59</v>
       </c>
-      <c r="G21" s="94" t="n">
+      <c r="H21" s="94" t="n">
         <v>23.94</v>
       </c>
-      <c r="H21" s="94" t="n">
+      <c r="I21" s="94" t="n">
         <v>33.06</v>
       </c>
-      <c r="I21" s="94" t="n">
+      <c r="J21" s="94" t="n">
         <v>94.42</v>
       </c>
-      <c r="J21" s="94" t="n">
+      <c r="K21" s="94" t="n">
         <v>93.58</v>
-      </c>
-      <c r="K21" s="94" t="n">
-        <v>62.65</v>
       </c>
       <c r="L21" s="94" t="n">
         <v>62.65</v>
       </c>
       <c r="M21" s="94" t="n">
+        <v>62.65</v>
+      </c>
+      <c r="N21" s="94" t="n">
         <v>57.92</v>
       </c>
-      <c r="N21" s="94" t="n">
+      <c r="O21" s="94" t="n">
         <v>69.63</v>
       </c>
-      <c r="O21" s="94" t="n">
+      <c r="P21" s="94" t="n">
         <v>39.94</v>
       </c>
-      <c r="P21" s="94" t="n">
+      <c r="Q21" s="94" t="n">
         <v>77.94</v>
-      </c>
-      <c r="Q21" s="94" t="n">
-        <v>69.16</v>
       </c>
       <c r="R21" s="94" t="n">
         <v>69.16</v>
       </c>
       <c r="S21" s="94" t="n">
+        <v>69.16</v>
+      </c>
+      <c r="T21" s="94" t="n">
         <v>13.01</v>
       </c>
-      <c r="T21" s="94" t="n">
+      <c r="U21" s="94" t="n">
         <v>32.79</v>
       </c>
-      <c r="U21" s="94" t="n">
+      <c r="V21" s="94" t="n">
         <v>8.44</v>
       </c>
-      <c r="V21" s="94" t="n">
+      <c r="W21" s="94" t="n">
         <v>11.76</v>
-      </c>
-      <c r="W21" s="94" t="n">
-        <v>42.26</v>
       </c>
       <c r="X21" s="94" t="n">
         <v>42.26</v>
       </c>
       <c r="Y21" s="94" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="Z21" s="94" t="n">
         <v>21.55</v>
       </c>
-      <c r="Z21" s="94" t="n">
+      <c r="AA21" s="94" t="n">
         <v>52.46</v>
       </c>
-      <c r="AA21" s="94" t="n">
+      <c r="AB21" s="94" t="n">
         <v>14.46</v>
       </c>
-      <c r="AB21" s="94" t="n">
+      <c r="AC21" s="94" t="n">
         <v>25.99</v>
-      </c>
-      <c r="AC21" s="94" t="n">
-        <v>62.38</v>
       </c>
       <c r="AD21" s="94" t="n">
         <v>62.38</v>
       </c>
       <c r="AE21" s="94" t="n">
-        <v>0.78</v>
+        <v>62.38</v>
       </c>
     </row>
     <row r="22">
@@ -8742,149 +8742,149 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C22" s="93" t="inlineStr">
+      <c r="C22" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D22" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D22" s="92" t="inlineStr">
+      <c r="E22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E22" s="92" t="inlineStr">
+      <c r="F22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F22" s="92" t="inlineStr">
+      <c r="G22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G22" s="91" t="inlineStr">
+      <c r="H22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H22" s="93" t="inlineStr">
+      <c r="I22" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I22" s="93" t="inlineStr">
+      <c r="J22" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J22" s="93" t="inlineStr">
+      <c r="K22" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K22" s="91" t="inlineStr">
+      <c r="L22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L22" s="91" t="inlineStr">
+      <c r="M22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M22" s="91" t="inlineStr">
+      <c r="N22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N22" s="91" t="inlineStr">
+      <c r="O22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O22" s="91" t="inlineStr">
+      <c r="P22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P22" s="91" t="inlineStr">
+      <c r="Q22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q22" s="91" t="inlineStr">
+      <c r="R22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R22" s="91" t="inlineStr">
+      <c r="S22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S22" s="92" t="inlineStr">
+      <c r="T22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T22" s="92" t="inlineStr">
+      <c r="U22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U22" s="92" t="inlineStr">
+      <c r="V22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V22" s="92" t="inlineStr">
+      <c r="W22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W22" s="91" t="inlineStr">
+      <c r="X22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X22" s="91" t="inlineStr">
+      <c r="Y22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y22" s="92" t="inlineStr">
+      <c r="Z22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z22" s="91" t="inlineStr">
+      <c r="AA22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA22" s="92" t="inlineStr">
+      <c r="AB22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB22" s="92" t="inlineStr">
+      <c r="AC22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC22" s="91" t="inlineStr">
+      <c r="AD22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD22" s="91" t="inlineStr">
+      <c r="AE22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE22" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -8898,91 +8898,91 @@
         <v>-5.06</v>
       </c>
       <c r="C23" s="94" t="n">
+        <v>-5.06</v>
+      </c>
+      <c r="D23" s="94" t="n">
         <v>-1.19</v>
       </c>
-      <c r="D23" s="94" t="n">
+      <c r="E23" s="94" t="n">
         <v>-0.95</v>
       </c>
-      <c r="E23" s="94" t="n">
+      <c r="F23" s="94" t="n">
         <v>-1.28</v>
       </c>
-      <c r="F23" s="94" t="n">
+      <c r="G23" s="94" t="n">
         <v>-2.32</v>
       </c>
-      <c r="G23" s="94" t="n">
+      <c r="H23" s="94" t="n">
         <v>-1.61</v>
       </c>
-      <c r="H23" s="94" t="n">
+      <c r="I23" s="94" t="n">
         <v>-2.01</v>
       </c>
-      <c r="I23" s="94" t="n">
+      <c r="J23" s="94" t="n">
         <v>-1.64</v>
       </c>
-      <c r="J23" s="94" t="n">
+      <c r="K23" s="94" t="n">
         <v>-0.75</v>
-      </c>
-      <c r="K23" s="94" t="n">
-        <v>-2</v>
       </c>
       <c r="L23" s="94" t="n">
         <v>-2</v>
       </c>
       <c r="M23" s="94" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N23" s="94" t="n">
         <v>-0.92</v>
       </c>
-      <c r="N23" s="94" t="n">
+      <c r="O23" s="94" t="n">
         <v>-0.86</v>
       </c>
-      <c r="O23" s="94" t="n">
+      <c r="P23" s="94" t="n">
         <v>-4.3</v>
       </c>
-      <c r="P23" s="94" t="n">
+      <c r="Q23" s="94" t="n">
         <v>-4.29</v>
-      </c>
-      <c r="Q23" s="94" t="n">
-        <v>-5.34</v>
       </c>
       <c r="R23" s="94" t="n">
         <v>-5.34</v>
       </c>
       <c r="S23" s="94" t="n">
+        <v>-5.34</v>
+      </c>
+      <c r="T23" s="94" t="n">
         <v>-7.06</v>
       </c>
-      <c r="T23" s="94" t="n">
+      <c r="U23" s="94" t="n">
         <v>-6.34</v>
       </c>
-      <c r="U23" s="94" t="n">
+      <c r="V23" s="94" t="n">
         <v>-6.36</v>
       </c>
-      <c r="V23" s="94" t="n">
+      <c r="W23" s="94" t="n">
         <v>-5.61</v>
-      </c>
-      <c r="W23" s="94" t="n">
-        <v>-4.12</v>
       </c>
       <c r="X23" s="94" t="n">
         <v>-4.12</v>
       </c>
       <c r="Y23" s="94" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="Z23" s="94" t="n">
         <v>-4.88</v>
       </c>
-      <c r="Z23" s="94" t="n">
+      <c r="AA23" s="94" t="n">
         <v>-4.46</v>
       </c>
-      <c r="AA23" s="94" t="n">
+      <c r="AB23" s="94" t="n">
         <v>-4.89</v>
       </c>
-      <c r="AB23" s="94" t="n">
+      <c r="AC23" s="94" t="n">
         <v>-3.55</v>
-      </c>
-      <c r="AC23" s="94" t="n">
-        <v>-2.38</v>
       </c>
       <c r="AD23" s="94" t="n">
         <v>-2.38</v>
       </c>
       <c r="AE23" s="94" t="n">
-        <v>-3.32</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="24">
@@ -8995,91 +8995,91 @@
         <v>-4.62</v>
       </c>
       <c r="C24" s="94" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="D24" s="94" t="n">
         <v>0.34</v>
       </c>
-      <c r="D24" s="94" t="n">
+      <c r="E24" s="94" t="n">
         <v>0.09</v>
       </c>
-      <c r="E24" s="94" t="n">
+      <c r="F24" s="94" t="n">
         <v>-0.83</v>
       </c>
-      <c r="F24" s="94" t="n">
+      <c r="G24" s="94" t="n">
         <v>-1.02</v>
       </c>
-      <c r="G24" s="94" t="n">
+      <c r="H24" s="94" t="n">
         <v>0.24</v>
       </c>
-      <c r="H24" s="94" t="n">
+      <c r="I24" s="94" t="n">
         <v>0.71</v>
       </c>
-      <c r="I24" s="94" t="n">
+      <c r="J24" s="94" t="n">
         <v>0.61</v>
       </c>
-      <c r="J24" s="94" t="n">
+      <c r="K24" s="94" t="n">
         <v>0.64</v>
-      </c>
-      <c r="K24" s="94" t="n">
-        <v>-0.45</v>
       </c>
       <c r="L24" s="94" t="n">
         <v>-0.45</v>
       </c>
       <c r="M24" s="94" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="N24" s="94" t="n">
         <v>0.09</v>
       </c>
-      <c r="N24" s="94" t="n">
+      <c r="O24" s="94" t="n">
         <v>-0.58</v>
       </c>
-      <c r="O24" s="94" t="n">
+      <c r="P24" s="94" t="n">
         <v>-1.29</v>
       </c>
-      <c r="P24" s="94" t="n">
+      <c r="Q24" s="94" t="n">
         <v>-0.53</v>
-      </c>
-      <c r="Q24" s="94" t="n">
-        <v>-1.28</v>
       </c>
       <c r="R24" s="94" t="n">
         <v>-1.28</v>
       </c>
       <c r="S24" s="94" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="T24" s="94" t="n">
         <v>-1.66</v>
       </c>
-      <c r="T24" s="94" t="n">
+      <c r="U24" s="94" t="n">
         <v>-0.61</v>
       </c>
-      <c r="U24" s="94" t="n">
+      <c r="V24" s="94" t="n">
         <v>-0.45</v>
       </c>
-      <c r="V24" s="94" t="n">
+      <c r="W24" s="94" t="n">
         <v>1.25</v>
-      </c>
-      <c r="W24" s="94" t="n">
-        <v>4.15</v>
       </c>
       <c r="X24" s="94" t="n">
         <v>4.15</v>
       </c>
       <c r="Y24" s="94" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Z24" s="94" t="n">
         <v>4.2</v>
       </c>
-      <c r="Z24" s="94" t="n">
+      <c r="AA24" s="94" t="n">
         <v>5.57</v>
       </c>
-      <c r="AA24" s="94" t="n">
+      <c r="AB24" s="94" t="n">
         <v>4.14</v>
       </c>
-      <c r="AB24" s="94" t="n">
+      <c r="AC24" s="94" t="n">
         <v>7.05</v>
-      </c>
-      <c r="AC24" s="94" t="n">
-        <v>7.57</v>
       </c>
       <c r="AD24" s="94" t="n">
         <v>7.57</v>
       </c>
       <c r="AE24" s="94" t="n">
-        <v>5.53</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="25">
@@ -9092,91 +9092,91 @@
         <v>14.42</v>
       </c>
       <c r="C25" s="94" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="D25" s="94" t="n">
         <v>63.09</v>
       </c>
-      <c r="D25" s="94" t="n">
+      <c r="E25" s="94" t="n">
         <v>46.09</v>
       </c>
-      <c r="E25" s="94" t="n">
+      <c r="F25" s="94" t="n">
         <v>46.81</v>
       </c>
-      <c r="F25" s="94" t="n">
+      <c r="G25" s="94" t="n">
         <v>15.69</v>
       </c>
-      <c r="G25" s="94" t="n">
+      <c r="H25" s="94" t="n">
         <v>47.29</v>
       </c>
-      <c r="H25" s="94" t="n">
+      <c r="I25" s="94" t="n">
         <v>66.68000000000001</v>
       </c>
-      <c r="I25" s="94" t="n">
+      <c r="J25" s="94" t="n">
         <v>87.05</v>
       </c>
-      <c r="J25" s="94" t="n">
+      <c r="K25" s="94" t="n">
         <v>86.95999999999999</v>
-      </c>
-      <c r="K25" s="94" t="n">
-        <v>66.09</v>
       </c>
       <c r="L25" s="94" t="n">
         <v>66.09</v>
       </c>
       <c r="M25" s="94" t="n">
+        <v>66.09</v>
+      </c>
+      <c r="N25" s="94" t="n">
         <v>64.04000000000001</v>
       </c>
-      <c r="N25" s="94" t="n">
+      <c r="O25" s="94" t="n">
         <v>64.95999999999999</v>
       </c>
-      <c r="O25" s="94" t="n">
+      <c r="P25" s="94" t="n">
         <v>47.92</v>
       </c>
-      <c r="P25" s="94" t="n">
+      <c r="Q25" s="94" t="n">
         <v>61.45</v>
-      </c>
-      <c r="Q25" s="94" t="n">
-        <v>48.21</v>
       </c>
       <c r="R25" s="94" t="n">
         <v>48.21</v>
       </c>
       <c r="S25" s="94" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="T25" s="94" t="n">
         <v>7.98</v>
       </c>
-      <c r="T25" s="94" t="n">
+      <c r="U25" s="94" t="n">
         <v>13.58</v>
       </c>
-      <c r="U25" s="94" t="n">
+      <c r="V25" s="94" t="n">
         <v>14.64</v>
       </c>
-      <c r="V25" s="94" t="n">
+      <c r="W25" s="94" t="n">
         <v>20.89</v>
-      </c>
-      <c r="W25" s="94" t="n">
-        <v>44.4</v>
       </c>
       <c r="X25" s="94" t="n">
         <v>44.4</v>
       </c>
       <c r="Y25" s="94" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="Z25" s="94" t="n">
         <v>31.55</v>
       </c>
-      <c r="Z25" s="94" t="n">
+      <c r="AA25" s="94" t="n">
         <v>44.8</v>
       </c>
-      <c r="AA25" s="94" t="n">
+      <c r="AB25" s="94" t="n">
         <v>19.04</v>
       </c>
-      <c r="AB25" s="94" t="n">
+      <c r="AC25" s="94" t="n">
         <v>33.38</v>
-      </c>
-      <c r="AC25" s="94" t="n">
-        <v>65.01000000000001</v>
       </c>
       <c r="AD25" s="94" t="n">
         <v>65.01000000000001</v>
       </c>
       <c r="AE25" s="94" t="n">
-        <v>15.7</v>
+        <v>65.01000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -9190,149 +9190,149 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C26" s="91" t="inlineStr">
+      <c r="C26" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D26" s="92" t="inlineStr">
+      <c r="E26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E26" s="92" t="inlineStr">
+      <c r="F26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F26" s="92" t="inlineStr">
+      <c r="G26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G26" s="92" t="inlineStr">
+      <c r="H26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H26" s="92" t="inlineStr">
+      <c r="I26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I26" s="93" t="inlineStr">
+      <c r="J26" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J26" s="93" t="inlineStr">
+      <c r="K26" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K26" s="91" t="inlineStr">
+      <c r="L26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L26" s="91" t="inlineStr">
+      <c r="M26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M26" s="91" t="inlineStr">
+      <c r="N26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N26" s="91" t="inlineStr">
+      <c r="O26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O26" s="91" t="inlineStr">
+      <c r="P26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P26" s="91" t="inlineStr">
+      <c r="Q26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q26" s="91" t="inlineStr">
+      <c r="R26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R26" s="91" t="inlineStr">
+      <c r="S26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S26" s="91" t="inlineStr">
+      <c r="T26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T26" s="91" t="inlineStr">
+      <c r="U26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U26" s="92" t="inlineStr">
+      <c r="V26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V26" s="92" t="inlineStr">
+      <c r="W26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W26" s="91" t="inlineStr">
+      <c r="X26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X26" s="91" t="inlineStr">
+      <c r="Y26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y26" s="92" t="inlineStr">
+      <c r="Z26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z26" s="91" t="inlineStr">
+      <c r="AA26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA26" s="92" t="inlineStr">
+      <c r="AB26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB26" s="92" t="inlineStr">
+      <c r="AC26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC26" s="91" t="inlineStr">
+      <c r="AD26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD26" s="91" t="inlineStr">
+      <c r="AE26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE26" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -9346,91 +9346,91 @@
         <v>-16.68</v>
       </c>
       <c r="C27" s="94" t="n">
+        <v>-16.68</v>
+      </c>
+      <c r="D27" s="94" t="n">
         <v>-10.3</v>
       </c>
-      <c r="D27" s="94" t="n">
+      <c r="E27" s="94" t="n">
         <v>-9.5</v>
       </c>
-      <c r="E27" s="94" t="n">
+      <c r="F27" s="94" t="n">
         <v>-10.42</v>
       </c>
-      <c r="F27" s="94" t="n">
+      <c r="G27" s="94" t="n">
         <v>-11.1</v>
       </c>
-      <c r="G27" s="94" t="n">
+      <c r="H27" s="94" t="n">
         <v>-9.73</v>
       </c>
-      <c r="H27" s="94" t="n">
+      <c r="I27" s="94" t="n">
         <v>-10.6</v>
       </c>
-      <c r="I27" s="94" t="n">
+      <c r="J27" s="94" t="n">
         <v>-8.779999999999999</v>
       </c>
-      <c r="J27" s="94" t="n">
+      <c r="K27" s="94" t="n">
         <v>-7.98</v>
-      </c>
-      <c r="K27" s="94" t="n">
-        <v>-9.140000000000001</v>
       </c>
       <c r="L27" s="94" t="n">
         <v>-9.140000000000001</v>
       </c>
       <c r="M27" s="94" t="n">
+        <v>-9.140000000000001</v>
+      </c>
+      <c r="N27" s="94" t="n">
         <v>-8.68</v>
       </c>
-      <c r="N27" s="94" t="n">
+      <c r="O27" s="94" t="n">
         <v>-8.470000000000001</v>
       </c>
-      <c r="O27" s="94" t="n">
+      <c r="P27" s="94" t="n">
         <v>-12.95</v>
       </c>
-      <c r="P27" s="94" t="n">
+      <c r="Q27" s="94" t="n">
         <v>-11.72</v>
-      </c>
-      <c r="Q27" s="94" t="n">
-        <v>-10.9</v>
       </c>
       <c r="R27" s="94" t="n">
         <v>-10.9</v>
       </c>
       <c r="S27" s="94" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="T27" s="94" t="n">
         <v>-13.06</v>
       </c>
-      <c r="T27" s="94" t="n">
+      <c r="U27" s="94" t="n">
         <v>-11.91</v>
       </c>
-      <c r="U27" s="94" t="n">
+      <c r="V27" s="94" t="n">
         <v>-11.43</v>
       </c>
-      <c r="V27" s="94" t="n">
+      <c r="W27" s="94" t="n">
         <v>-11.49</v>
-      </c>
-      <c r="W27" s="94" t="n">
-        <v>-8.380000000000001</v>
       </c>
       <c r="X27" s="94" t="n">
         <v>-8.380000000000001</v>
       </c>
       <c r="Y27" s="94" t="n">
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="Z27" s="94" t="n">
         <v>-8.279999999999999</v>
       </c>
-      <c r="Z27" s="94" t="n">
+      <c r="AA27" s="94" t="n">
         <v>-5.99</v>
       </c>
-      <c r="AA27" s="94" t="n">
+      <c r="AB27" s="94" t="n">
         <v>-6.14</v>
       </c>
-      <c r="AB27" s="94" t="n">
+      <c r="AC27" s="94" t="n">
         <v>-5.43</v>
-      </c>
-      <c r="AC27" s="94" t="n">
-        <v>-1.93</v>
       </c>
       <c r="AD27" s="94" t="n">
         <v>-1.93</v>
       </c>
       <c r="AE27" s="94" t="n">
-        <v>-2.71</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="28">
@@ -9443,91 +9443,91 @@
         <v>-9.52</v>
       </c>
       <c r="C28" s="94" t="n">
+        <v>-9.52</v>
+      </c>
+      <c r="D28" s="94" t="n">
         <v>-3.2</v>
       </c>
-      <c r="D28" s="94" t="n">
+      <c r="E28" s="94" t="n">
         <v>-2.64</v>
       </c>
-      <c r="E28" s="94" t="n">
+      <c r="F28" s="94" t="n">
         <v>-4.62</v>
       </c>
-      <c r="F28" s="94" t="n">
+      <c r="G28" s="94" t="n">
         <v>-3.32</v>
       </c>
-      <c r="G28" s="94" t="n">
+      <c r="H28" s="94" t="n">
         <v>-0.68</v>
       </c>
-      <c r="H28" s="94" t="n">
+      <c r="I28" s="94" t="n">
         <v>-0.06</v>
       </c>
-      <c r="I28" s="94" t="n">
+      <c r="J28" s="94" t="n">
         <v>0.45</v>
       </c>
-      <c r="J28" s="94" t="n">
+      <c r="K28" s="94" t="n">
         <v>0.38</v>
-      </c>
-      <c r="K28" s="94" t="n">
-        <v>-2.23</v>
       </c>
       <c r="L28" s="94" t="n">
         <v>-2.23</v>
       </c>
       <c r="M28" s="94" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="N28" s="94" t="n">
         <v>-2.16</v>
       </c>
-      <c r="N28" s="94" t="n">
+      <c r="O28" s="94" t="n">
         <v>-1.79</v>
       </c>
-      <c r="O28" s="94" t="n">
+      <c r="P28" s="94" t="n">
         <v>-2.62</v>
       </c>
-      <c r="P28" s="94" t="n">
+      <c r="Q28" s="94" t="n">
         <v>-0.78</v>
-      </c>
-      <c r="Q28" s="94" t="n">
-        <v>-1.44</v>
       </c>
       <c r="R28" s="94" t="n">
         <v>-1.44</v>
       </c>
       <c r="S28" s="94" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="T28" s="94" t="n">
         <v>-1.54</v>
       </c>
-      <c r="T28" s="94" t="n">
+      <c r="U28" s="94" t="n">
         <v>0.12</v>
       </c>
-      <c r="U28" s="94" t="n">
+      <c r="V28" s="94" t="n">
         <v>-0.89</v>
       </c>
-      <c r="V28" s="94" t="n">
+      <c r="W28" s="94" t="n">
         <v>-1.22</v>
-      </c>
-      <c r="W28" s="94" t="n">
-        <v>3.57</v>
       </c>
       <c r="X28" s="94" t="n">
         <v>3.57</v>
       </c>
       <c r="Y28" s="94" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="Z28" s="94" t="n">
         <v>3.87</v>
       </c>
-      <c r="Z28" s="94" t="n">
+      <c r="AA28" s="94" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="AA28" s="94" t="n">
+      <c r="AB28" s="94" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="AB28" s="94" t="n">
+      <c r="AC28" s="94" t="n">
         <v>9.94</v>
-      </c>
-      <c r="AC28" s="94" t="n">
-        <v>10.04</v>
       </c>
       <c r="AD28" s="94" t="n">
         <v>10.04</v>
       </c>
       <c r="AE28" s="94" t="n">
-        <v>8.550000000000001</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="29">
@@ -9540,91 +9540,91 @@
         <v>9.58</v>
       </c>
       <c r="C29" s="94" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="D29" s="94" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="D29" s="94" t="n">
+      <c r="E29" s="94" t="n">
         <v>48.94</v>
       </c>
-      <c r="E29" s="94" t="n">
+      <c r="F29" s="94" t="n">
         <v>5.77</v>
       </c>
-      <c r="F29" s="94" t="n">
+      <c r="G29" s="94" t="n">
         <v>6.18</v>
       </c>
-      <c r="G29" s="94" t="n">
+      <c r="H29" s="94" t="n">
         <v>22.32</v>
       </c>
-      <c r="H29" s="94" t="n">
+      <c r="I29" s="94" t="n">
         <v>30.08</v>
       </c>
-      <c r="I29" s="94" t="n">
+      <c r="J29" s="94" t="n">
         <v>94.62</v>
       </c>
-      <c r="J29" s="94" t="n">
+      <c r="K29" s="94" t="n">
         <v>92.92</v>
-      </c>
-      <c r="K29" s="94" t="n">
-        <v>69.84999999999999</v>
       </c>
       <c r="L29" s="94" t="n">
         <v>69.84999999999999</v>
       </c>
       <c r="M29" s="94" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="N29" s="94" t="n">
         <v>51.97</v>
       </c>
-      <c r="N29" s="94" t="n">
+      <c r="O29" s="94" t="n">
         <v>64.14</v>
       </c>
-      <c r="O29" s="94" t="n">
+      <c r="P29" s="94" t="n">
         <v>29.95</v>
       </c>
-      <c r="P29" s="94" t="n">
+      <c r="Q29" s="94" t="n">
         <v>72.81999999999999</v>
-      </c>
-      <c r="Q29" s="94" t="n">
-        <v>68.81999999999999</v>
       </c>
       <c r="R29" s="94" t="n">
         <v>68.81999999999999</v>
       </c>
       <c r="S29" s="94" t="n">
+        <v>68.81999999999999</v>
+      </c>
+      <c r="T29" s="94" t="n">
         <v>20.44</v>
       </c>
-      <c r="T29" s="94" t="n">
+      <c r="U29" s="94" t="n">
         <v>50.35</v>
       </c>
-      <c r="U29" s="94" t="n">
+      <c r="V29" s="94" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V29" s="94" t="n">
+      <c r="W29" s="94" t="n">
         <v>10.44</v>
-      </c>
-      <c r="W29" s="94" t="n">
-        <v>41.16</v>
       </c>
       <c r="X29" s="94" t="n">
         <v>41.16</v>
       </c>
       <c r="Y29" s="94" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="Z29" s="94" t="n">
         <v>20.86</v>
       </c>
-      <c r="Z29" s="94" t="n">
+      <c r="AA29" s="94" t="n">
         <v>60.82</v>
       </c>
-      <c r="AA29" s="94" t="n">
+      <c r="AB29" s="94" t="n">
         <v>16.64</v>
       </c>
-      <c r="AB29" s="94" t="n">
+      <c r="AC29" s="94" t="n">
         <v>19.28</v>
-      </c>
-      <c r="AC29" s="94" t="n">
-        <v>49.05</v>
       </c>
       <c r="AD29" s="94" t="n">
         <v>49.05</v>
       </c>
       <c r="AE29" s="94" t="n">
-        <v>3.78</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="30">
@@ -9658,119 +9658,119 @@
           <t>green</t>
         </is>
       </c>
-      <c r="G30" s="91" t="inlineStr">
+      <c r="G30" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H30" s="93" t="inlineStr">
+      <c r="I30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I30" s="93" t="inlineStr">
+      <c r="J30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J30" s="91" t="inlineStr">
+      <c r="K30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K30" s="93" t="inlineStr">
+      <c r="L30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L30" s="93" t="inlineStr">
+      <c r="M30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M30" s="93" t="inlineStr">
+      <c r="N30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N30" s="93" t="inlineStr">
+      <c r="O30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O30" s="93" t="inlineStr">
+      <c r="P30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P30" s="93" t="inlineStr">
+      <c r="Q30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q30" s="91" t="inlineStr">
+      <c r="R30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R30" s="91" t="inlineStr">
+      <c r="S30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S30" s="91" t="inlineStr">
+      <c r="T30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T30" s="91" t="inlineStr">
+      <c r="U30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U30" s="91" t="inlineStr">
+      <c r="V30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V30" s="91" t="inlineStr">
+      <c r="W30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W30" s="92" t="inlineStr">
+      <c r="X30" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X30" s="92" t="inlineStr">
+      <c r="Y30" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y30" s="91" t="inlineStr">
+      <c r="Z30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z30" s="91" t="inlineStr">
+      <c r="AA30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA30" s="92" t="inlineStr">
+      <c r="AB30" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB30" s="91" t="inlineStr">
+      <c r="AC30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AC30" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AD30" s="92" t="inlineStr">
@@ -9791,94 +9791,94 @@
         </is>
       </c>
       <c r="B31" s="94" t="n">
+        <v>-15.51</v>
+      </c>
+      <c r="C31" s="94" t="n">
         <v>-13.34</v>
       </c>
-      <c r="C31" s="94" t="n">
+      <c r="D31" s="94" t="n">
         <v>-9.109999999999999</v>
       </c>
-      <c r="D31" s="94" t="n">
+      <c r="E31" s="94" t="n">
         <v>-10.7</v>
       </c>
-      <c r="E31" s="94" t="n">
+      <c r="F31" s="94" t="n">
         <v>-11.58</v>
       </c>
-      <c r="F31" s="94" t="n">
+      <c r="G31" s="94" t="n">
         <v>-6.19</v>
       </c>
-      <c r="G31" s="94" t="n">
+      <c r="H31" s="94" t="n">
         <v>-3.4</v>
       </c>
-      <c r="H31" s="94" t="n">
+      <c r="I31" s="94" t="n">
         <v>-2.59</v>
       </c>
-      <c r="I31" s="94" t="n">
+      <c r="J31" s="94" t="n">
         <v>-3.53</v>
       </c>
-      <c r="J31" s="94" t="n">
+      <c r="K31" s="94" t="n">
         <v>-2.83</v>
-      </c>
-      <c r="K31" s="94" t="n">
-        <v>-2.93</v>
       </c>
       <c r="L31" s="94" t="n">
         <v>-2.93</v>
       </c>
       <c r="M31" s="94" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="N31" s="94" t="n">
         <v>-3.09</v>
       </c>
-      <c r="N31" s="94" t="n">
+      <c r="O31" s="94" t="n">
         <v>-4.1</v>
       </c>
-      <c r="O31" s="94" t="n">
+      <c r="P31" s="94" t="n">
         <v>-4.09</v>
       </c>
-      <c r="P31" s="94" t="n">
+      <c r="Q31" s="94" t="n">
         <v>-5.25</v>
-      </c>
-      <c r="Q31" s="94" t="n">
-        <v>-7.02</v>
       </c>
       <c r="R31" s="94" t="n">
         <v>-7.02</v>
       </c>
       <c r="S31" s="94" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="T31" s="94" t="n">
         <v>-6.56</v>
       </c>
-      <c r="T31" s="94" t="n">
+      <c r="U31" s="94" t="n">
         <v>-6.47</v>
       </c>
-      <c r="U31" s="94" t="n">
+      <c r="V31" s="94" t="n">
         <v>-6.05</v>
       </c>
-      <c r="V31" s="94" t="n">
+      <c r="W31" s="94" t="n">
         <v>-5.28</v>
-      </c>
-      <c r="W31" s="94" t="n">
-        <v>-6.37</v>
       </c>
       <c r="X31" s="94" t="n">
         <v>-6.37</v>
       </c>
       <c r="Y31" s="94" t="n">
+        <v>-6.37</v>
+      </c>
+      <c r="Z31" s="94" t="n">
         <v>-4</v>
       </c>
-      <c r="Z31" s="94" t="n">
+      <c r="AA31" s="94" t="n">
         <v>-4.66</v>
       </c>
-      <c r="AA31" s="94" t="n">
+      <c r="AB31" s="94" t="n">
         <v>-3.07</v>
       </c>
-      <c r="AB31" s="94" t="n">
+      <c r="AC31" s="94" t="n">
         <v>-1.11</v>
-      </c>
-      <c r="AC31" s="94" t="n">
-        <v>-3.11</v>
       </c>
       <c r="AD31" s="94" t="n">
         <v>-3.11</v>
       </c>
       <c r="AE31" s="94" t="n">
-        <v>0.32</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="32">
@@ -9888,94 +9888,94 @@
         </is>
       </c>
       <c r="B32" s="94" t="n">
+        <v>-14</v>
+      </c>
+      <c r="C32" s="94" t="n">
         <v>-10.79</v>
       </c>
-      <c r="C32" s="94" t="n">
+      <c r="D32" s="94" t="n">
         <v>-9.17</v>
       </c>
-      <c r="D32" s="94" t="n">
+      <c r="E32" s="94" t="n">
         <v>-7.79</v>
       </c>
-      <c r="E32" s="94" t="n">
+      <c r="F32" s="94" t="n">
         <v>-7.61</v>
       </c>
-      <c r="F32" s="94" t="n">
+      <c r="G32" s="94" t="n">
         <v>-1.82</v>
       </c>
-      <c r="G32" s="94" t="n">
+      <c r="H32" s="94" t="n">
         <v>-2.2</v>
       </c>
-      <c r="H32" s="94" t="n">
+      <c r="I32" s="94" t="n">
         <v>0.28</v>
       </c>
-      <c r="I32" s="94" t="n">
+      <c r="J32" s="94" t="n">
         <v>-5.14</v>
       </c>
-      <c r="J32" s="94" t="n">
+      <c r="K32" s="94" t="n">
         <v>-3.38</v>
-      </c>
-      <c r="K32" s="94" t="n">
-        <v>-0.51</v>
       </c>
       <c r="L32" s="94" t="n">
         <v>-0.51</v>
       </c>
       <c r="M32" s="94" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="N32" s="94" t="n">
         <v>-0.18</v>
       </c>
-      <c r="N32" s="94" t="n">
+      <c r="O32" s="94" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="O32" s="94" t="n">
+      <c r="P32" s="94" t="n">
         <v>1.86</v>
       </c>
-      <c r="P32" s="94" t="n">
+      <c r="Q32" s="94" t="n">
         <v>2.79</v>
-      </c>
-      <c r="Q32" s="94" t="n">
-        <v>2.35</v>
       </c>
       <c r="R32" s="94" t="n">
         <v>2.35</v>
       </c>
       <c r="S32" s="94" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T32" s="94" t="n">
         <v>0.63</v>
       </c>
-      <c r="T32" s="94" t="n">
+      <c r="U32" s="94" t="n">
         <v>0.65</v>
       </c>
-      <c r="U32" s="94" t="n">
+      <c r="V32" s="94" t="n">
         <v>-0.11</v>
       </c>
-      <c r="V32" s="94" t="n">
+      <c r="W32" s="94" t="n">
         <v>3.95</v>
-      </c>
-      <c r="W32" s="94" t="n">
-        <v>2.01</v>
       </c>
       <c r="X32" s="94" t="n">
         <v>2.01</v>
       </c>
       <c r="Y32" s="94" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z32" s="94" t="n">
         <v>4.11</v>
       </c>
-      <c r="Z32" s="94" t="n">
+      <c r="AA32" s="94" t="n">
         <v>2.82</v>
       </c>
-      <c r="AA32" s="94" t="n">
+      <c r="AB32" s="94" t="n">
         <v>1.84</v>
       </c>
-      <c r="AB32" s="94" t="n">
+      <c r="AC32" s="94" t="n">
         <v>1.99</v>
-      </c>
-      <c r="AC32" s="94" t="n">
-        <v>-3.96</v>
       </c>
       <c r="AD32" s="94" t="n">
         <v>-3.96</v>
       </c>
       <c r="AE32" s="94" t="n">
-        <v>-1.15</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="33">
@@ -9985,94 +9985,94 @@
         </is>
       </c>
       <c r="B33" s="94" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="C33" s="94" t="n">
         <v>18.88</v>
       </c>
-      <c r="C33" s="94" t="n">
+      <c r="D33" s="94" t="n">
         <v>25.75</v>
       </c>
-      <c r="D33" s="94" t="n">
+      <c r="E33" s="94" t="n">
         <v>23.21</v>
       </c>
-      <c r="E33" s="94" t="n">
+      <c r="F33" s="94" t="n">
         <v>23.05</v>
       </c>
-      <c r="F33" s="94" t="n">
+      <c r="G33" s="94" t="n">
         <v>38.53</v>
       </c>
-      <c r="G33" s="94" t="n">
+      <c r="H33" s="94" t="n">
         <v>52.79</v>
       </c>
-      <c r="H33" s="94" t="n">
+      <c r="I33" s="94" t="n">
         <v>59.31</v>
       </c>
-      <c r="I33" s="94" t="n">
+      <c r="J33" s="94" t="n">
         <v>53.8</v>
       </c>
-      <c r="J33" s="94" t="n">
+      <c r="K33" s="94" t="n">
         <v>49.57</v>
-      </c>
-      <c r="K33" s="94" t="n">
-        <v>51.23</v>
       </c>
       <c r="L33" s="94" t="n">
         <v>51.23</v>
       </c>
       <c r="M33" s="94" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="N33" s="94" t="n">
         <v>55.99</v>
       </c>
-      <c r="N33" s="94" t="n">
+      <c r="O33" s="94" t="n">
         <v>53.63</v>
       </c>
-      <c r="O33" s="94" t="n">
+      <c r="P33" s="94" t="n">
         <v>55.69</v>
       </c>
-      <c r="P33" s="94" t="n">
+      <c r="Q33" s="94" t="n">
         <v>47</v>
-      </c>
-      <c r="Q33" s="94" t="n">
-        <v>38.84</v>
       </c>
       <c r="R33" s="94" t="n">
         <v>38.84</v>
       </c>
       <c r="S33" s="94" t="n">
+        <v>38.84</v>
+      </c>
+      <c r="T33" s="94" t="n">
         <v>31.69</v>
       </c>
-      <c r="T33" s="94" t="n">
+      <c r="U33" s="94" t="n">
         <v>32.06</v>
       </c>
-      <c r="U33" s="94" t="n">
+      <c r="V33" s="94" t="n">
         <v>31.42</v>
       </c>
-      <c r="V33" s="94" t="n">
+      <c r="W33" s="94" t="n">
         <v>33.97</v>
-      </c>
-      <c r="W33" s="94" t="n">
-        <v>30.98</v>
       </c>
       <c r="X33" s="94" t="n">
         <v>30.98</v>
       </c>
       <c r="Y33" s="94" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="Z33" s="94" t="n">
         <v>40.4</v>
       </c>
-      <c r="Z33" s="94" t="n">
+      <c r="AA33" s="94" t="n">
         <v>34.16</v>
       </c>
-      <c r="AA33" s="94" t="n">
+      <c r="AB33" s="94" t="n">
         <v>32.25</v>
       </c>
-      <c r="AB33" s="94" t="n">
+      <c r="AC33" s="94" t="n">
         <v>37.27</v>
-      </c>
-      <c r="AC33" s="94" t="n">
-        <v>22.38</v>
       </c>
       <c r="AD33" s="94" t="n">
         <v>22.38</v>
       </c>
       <c r="AE33" s="94" t="n">
-        <v>35.45</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="34">
@@ -10086,124 +10086,124 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C34" s="91" t="inlineStr">
+      <c r="C34" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D34" s="91" t="inlineStr">
+      <c r="E34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E34" s="92" t="inlineStr">
+      <c r="F34" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F34" s="92" t="inlineStr">
+      <c r="G34" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G34" s="92" t="inlineStr">
+      <c r="H34" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H34" s="91" t="inlineStr">
+      <c r="I34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I34" s="93" t="inlineStr">
+      <c r="J34" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J34" s="93" t="inlineStr">
+      <c r="K34" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K34" s="92" t="inlineStr">
+      <c r="L34" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L34" s="92" t="inlineStr">
+      <c r="M34" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M34" s="91" t="inlineStr">
+      <c r="N34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N34" s="91" t="inlineStr">
+      <c r="O34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O34" s="91" t="inlineStr">
+      <c r="P34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P34" s="93" t="inlineStr">
+      <c r="Q34" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q34" s="91" t="inlineStr">
+      <c r="R34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R34" s="91" t="inlineStr">
+      <c r="S34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S34" s="91" t="inlineStr">
+      <c r="T34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T34" s="91" t="inlineStr">
+      <c r="U34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U34" s="93" t="inlineStr">
+      <c r="V34" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V34" s="93" t="inlineStr">
+      <c r="W34" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W34" s="93" t="inlineStr">
+      <c r="X34" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X34" s="93" t="inlineStr">
+      <c r="Y34" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y34" s="93" t="inlineStr">
+      <c r="Z34" s="93" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="Z34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AA34" s="91" t="inlineStr">
@@ -10239,94 +10239,94 @@
         </is>
       </c>
       <c r="B35" s="94" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="C35" s="94" t="n">
         <v>-3.14</v>
       </c>
-      <c r="C35" s="94" t="n">
+      <c r="D35" s="94" t="n">
         <v>4.03</v>
       </c>
-      <c r="D35" s="94" t="n">
+      <c r="E35" s="94" t="n">
         <v>3.56</v>
       </c>
-      <c r="E35" s="94" t="n">
+      <c r="F35" s="94" t="n">
         <v>2.49</v>
       </c>
-      <c r="F35" s="94" t="n">
+      <c r="G35" s="94" t="n">
         <v>3.5</v>
       </c>
-      <c r="G35" s="94" t="n">
+      <c r="H35" s="94" t="n">
         <v>3.91</v>
       </c>
-      <c r="H35" s="94" t="n">
+      <c r="I35" s="94" t="n">
         <v>5.22</v>
       </c>
-      <c r="I35" s="94" t="n">
+      <c r="J35" s="94" t="n">
         <v>5.48</v>
       </c>
-      <c r="J35" s="94" t="n">
+      <c r="K35" s="94" t="n">
         <v>5.79</v>
-      </c>
-      <c r="K35" s="94" t="n">
-        <v>5.36</v>
       </c>
       <c r="L35" s="94" t="n">
         <v>5.36</v>
       </c>
       <c r="M35" s="94" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="N35" s="94" t="n">
         <v>4.58</v>
       </c>
-      <c r="N35" s="94" t="n">
+      <c r="O35" s="94" t="n">
         <v>4.99</v>
       </c>
-      <c r="O35" s="94" t="n">
+      <c r="P35" s="94" t="n">
         <v>5.32</v>
       </c>
-      <c r="P35" s="94" t="n">
+      <c r="Q35" s="94" t="n">
         <v>5.84</v>
-      </c>
-      <c r="Q35" s="94" t="n">
-        <v>4.64</v>
       </c>
       <c r="R35" s="94" t="n">
         <v>4.64</v>
       </c>
       <c r="S35" s="94" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="T35" s="94" t="n">
         <v>4.52</v>
       </c>
-      <c r="T35" s="94" t="n">
+      <c r="U35" s="94" t="n">
         <v>4.9</v>
       </c>
-      <c r="U35" s="94" t="n">
+      <c r="V35" s="94" t="n">
         <v>4.61</v>
       </c>
-      <c r="V35" s="94" t="n">
+      <c r="W35" s="94" t="n">
         <v>4.73</v>
-      </c>
-      <c r="W35" s="94" t="n">
-        <v>4.62</v>
       </c>
       <c r="X35" s="94" t="n">
         <v>4.62</v>
       </c>
       <c r="Y35" s="94" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="Z35" s="94" t="n">
         <v>6.27</v>
       </c>
-      <c r="Z35" s="94" t="n">
+      <c r="AA35" s="94" t="n">
         <v>4.39</v>
       </c>
-      <c r="AA35" s="94" t="n">
+      <c r="AB35" s="94" t="n">
         <v>4.85</v>
       </c>
-      <c r="AB35" s="94" t="n">
+      <c r="AC35" s="94" t="n">
         <v>4.71</v>
-      </c>
-      <c r="AC35" s="94" t="n">
-        <v>5.09</v>
       </c>
       <c r="AD35" s="94" t="n">
         <v>5.09</v>
       </c>
       <c r="AE35" s="94" t="n">
-        <v>5.3</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="36">
@@ -10336,94 +10336,94 @@
         </is>
       </c>
       <c r="B36" s="94" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="C36" s="94" t="n">
         <v>-4.06</v>
       </c>
-      <c r="C36" s="94" t="n">
+      <c r="D36" s="94" t="n">
         <v>3.6</v>
       </c>
-      <c r="D36" s="94" t="n">
+      <c r="E36" s="94" t="n">
         <v>3.73</v>
       </c>
-      <c r="E36" s="94" t="n">
+      <c r="F36" s="94" t="n">
         <v>2.85</v>
       </c>
-      <c r="F36" s="94" t="n">
+      <c r="G36" s="94" t="n">
         <v>3.08</v>
       </c>
-      <c r="G36" s="94" t="n">
+      <c r="H36" s="94" t="n">
         <v>2.79</v>
       </c>
-      <c r="H36" s="94" t="n">
+      <c r="I36" s="94" t="n">
         <v>2.62</v>
       </c>
-      <c r="I36" s="94" t="n">
+      <c r="J36" s="94" t="n">
         <v>3.41</v>
       </c>
-      <c r="J36" s="94" t="n">
+      <c r="K36" s="94" t="n">
         <v>3.05</v>
-      </c>
-      <c r="K36" s="94" t="n">
-        <v>2.35</v>
       </c>
       <c r="L36" s="94" t="n">
         <v>2.35</v>
       </c>
       <c r="M36" s="94" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N36" s="94" t="n">
         <v>2.83</v>
       </c>
-      <c r="N36" s="94" t="n">
+      <c r="O36" s="94" t="n">
         <v>3.73</v>
       </c>
-      <c r="O36" s="94" t="n">
+      <c r="P36" s="94" t="n">
         <v>4.93</v>
       </c>
-      <c r="P36" s="94" t="n">
+      <c r="Q36" s="94" t="n">
         <v>5.05</v>
-      </c>
-      <c r="Q36" s="94" t="n">
-        <v>4.32</v>
       </c>
       <c r="R36" s="94" t="n">
         <v>4.32</v>
       </c>
       <c r="S36" s="94" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="T36" s="94" t="n">
         <v>4.85</v>
       </c>
-      <c r="T36" s="94" t="n">
+      <c r="U36" s="94" t="n">
         <v>5.99</v>
       </c>
-      <c r="U36" s="94" t="n">
+      <c r="V36" s="94" t="n">
         <v>7.53</v>
       </c>
-      <c r="V36" s="94" t="n">
+      <c r="W36" s="94" t="n">
         <v>6.28</v>
-      </c>
-      <c r="W36" s="94" t="n">
-        <v>5.55</v>
       </c>
       <c r="X36" s="94" t="n">
         <v>5.55</v>
       </c>
       <c r="Y36" s="94" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="Z36" s="94" t="n">
         <v>5.18</v>
       </c>
-      <c r="Z36" s="94" t="n">
+      <c r="AA36" s="94" t="n">
         <v>3.94</v>
       </c>
-      <c r="AA36" s="94" t="n">
+      <c r="AB36" s="94" t="n">
         <v>3.48</v>
       </c>
-      <c r="AB36" s="94" t="n">
+      <c r="AC36" s="94" t="n">
         <v>2.78</v>
-      </c>
-      <c r="AC36" s="94" t="n">
-        <v>2.93</v>
       </c>
       <c r="AD36" s="94" t="n">
         <v>2.93</v>
       </c>
       <c r="AE36" s="94" t="n">
-        <v>2.51</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="37">
@@ -10433,94 +10433,94 @@
         </is>
       </c>
       <c r="B37" s="94" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="C37" s="94" t="n">
         <v>5.54</v>
       </c>
-      <c r="C37" s="94" t="n">
+      <c r="D37" s="94" t="n">
         <v>50.33</v>
       </c>
-      <c r="D37" s="94" t="n">
+      <c r="E37" s="94" t="n">
         <v>48.76</v>
       </c>
-      <c r="E37" s="94" t="n">
+      <c r="F37" s="94" t="n">
         <v>8.33</v>
       </c>
-      <c r="F37" s="94" t="n">
+      <c r="G37" s="94" t="n">
         <v>17.82</v>
       </c>
-      <c r="G37" s="94" t="n">
+      <c r="H37" s="94" t="n">
         <v>32.69</v>
       </c>
-      <c r="H37" s="94" t="n">
+      <c r="I37" s="94" t="n">
         <v>40.84</v>
       </c>
-      <c r="I37" s="94" t="n">
+      <c r="J37" s="94" t="n">
         <v>71.06</v>
       </c>
-      <c r="J37" s="94" t="n">
+      <c r="K37" s="94" t="n">
         <v>66.54000000000001</v>
-      </c>
-      <c r="K37" s="94" t="n">
-        <v>25.54</v>
       </c>
       <c r="L37" s="94" t="n">
         <v>25.54</v>
       </c>
       <c r="M37" s="94" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="N37" s="94" t="n">
         <v>31.86</v>
       </c>
-      <c r="N37" s="94" t="n">
+      <c r="O37" s="94" t="n">
         <v>33.76</v>
       </c>
-      <c r="O37" s="94" t="n">
+      <c r="P37" s="94" t="n">
         <v>52.78</v>
       </c>
-      <c r="P37" s="94" t="n">
+      <c r="Q37" s="94" t="n">
         <v>76.89</v>
-      </c>
-      <c r="Q37" s="94" t="n">
-        <v>44.73</v>
       </c>
       <c r="R37" s="94" t="n">
         <v>44.73</v>
       </c>
       <c r="S37" s="94" t="n">
+        <v>44.73</v>
+      </c>
+      <c r="T37" s="94" t="n">
         <v>45.22</v>
       </c>
-      <c r="T37" s="94" t="n">
+      <c r="U37" s="94" t="n">
         <v>91.12</v>
       </c>
-      <c r="U37" s="94" t="n">
+      <c r="V37" s="94" t="n">
         <v>89.48</v>
       </c>
-      <c r="V37" s="94" t="n">
+      <c r="W37" s="94" t="n">
         <v>87.65000000000001</v>
-      </c>
-      <c r="W37" s="94" t="n">
-        <v>84.23</v>
       </c>
       <c r="X37" s="94" t="n">
         <v>84.23</v>
       </c>
       <c r="Y37" s="94" t="n">
+        <v>84.23</v>
+      </c>
+      <c r="Z37" s="94" t="n">
         <v>76.01000000000001</v>
       </c>
-      <c r="Z37" s="94" t="n">
+      <c r="AA37" s="94" t="n">
         <v>40.18</v>
       </c>
-      <c r="AA37" s="94" t="n">
+      <c r="AB37" s="94" t="n">
         <v>85.62</v>
       </c>
-      <c r="AB37" s="94" t="n">
+      <c r="AC37" s="94" t="n">
         <v>80.41</v>
-      </c>
-      <c r="AC37" s="94" t="n">
-        <v>68.34</v>
       </c>
       <c r="AD37" s="94" t="n">
         <v>68.34</v>
       </c>
       <c r="AE37" s="94" t="n">
-        <v>91.12</v>
+        <v>68.34</v>
       </c>
     </row>
     <row r="38">
@@ -10534,149 +10534,149 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C38" s="91" t="inlineStr">
+      <c r="C38" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D38" s="92" t="inlineStr">
+      <c r="E38" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E38" s="91" t="inlineStr">
+      <c r="F38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F38" s="91" t="inlineStr">
+      <c r="G38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G38" s="91" t="inlineStr">
+      <c r="H38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H38" s="91" t="inlineStr">
+      <c r="I38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I38" s="93" t="inlineStr">
+      <c r="J38" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J38" s="93" t="inlineStr">
+      <c r="K38" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K38" s="93" t="inlineStr">
+      <c r="L38" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L38" s="93" t="inlineStr">
+      <c r="M38" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M38" s="93" t="inlineStr">
+      <c r="N38" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N38" s="93" t="inlineStr">
+      <c r="O38" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O38" s="93" t="inlineStr">
+      <c r="P38" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P38" s="91" t="inlineStr">
+      <c r="Q38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q38" s="91" t="inlineStr">
+      <c r="R38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R38" s="91" t="inlineStr">
+      <c r="S38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S38" s="91" t="inlineStr">
+      <c r="T38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T38" s="91" t="inlineStr">
+      <c r="U38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U38" s="91" t="inlineStr">
+      <c r="V38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V38" s="91" t="inlineStr">
+      <c r="W38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W38" s="91" t="inlineStr">
+      <c r="X38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X38" s="91" t="inlineStr">
+      <c r="Y38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y38" s="91" t="inlineStr">
+      <c r="Z38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z38" s="91" t="inlineStr">
+      <c r="AA38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA38" s="92" t="inlineStr">
+      <c r="AB38" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB38" s="92" t="inlineStr">
+      <c r="AC38" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC38" s="92" t="inlineStr">
+      <c r="AD38" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD38" s="92" t="inlineStr">
+      <c r="AE38" s="92" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AE38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -10687,52 +10687,52 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="C39" s="94" t="n">
         <v>-2.43</v>
       </c>
-      <c r="C39" s="94" t="n">
+      <c r="D39" s="94" t="n">
         <v>-1.73</v>
       </c>
-      <c r="D39" s="94" t="n">
+      <c r="E39" s="94" t="n">
         <v>-4.04</v>
-      </c>
-      <c r="E39" s="94" t="n">
-        <v>-3.16</v>
       </c>
       <c r="F39" s="94" t="n">
         <v>-3.16</v>
       </c>
       <c r="G39" s="94" t="n">
+        <v>-3.16</v>
+      </c>
+      <c r="H39" s="94" t="n">
         <v>-1.15</v>
       </c>
-      <c r="H39" s="94" t="n">
+      <c r="I39" s="94" t="n">
         <v>-1.09</v>
       </c>
-      <c r="I39" s="94" t="n">
+      <c r="J39" s="94" t="n">
         <v>-0.3</v>
       </c>
-      <c r="J39" s="94" t="n">
+      <c r="K39" s="94" t="n">
         <v>-0.91</v>
-      </c>
-      <c r="K39" s="94" t="n">
-        <v>-2</v>
       </c>
       <c r="L39" s="94" t="n">
         <v>-2</v>
       </c>
       <c r="M39" s="94" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N39" s="94" t="n">
         <v>-2.71</v>
       </c>
-      <c r="N39" s="94" t="n">
+      <c r="O39" s="94" t="n">
         <v>-3.94</v>
       </c>
-      <c r="O39" s="94" t="n">
+      <c r="P39" s="94" t="n">
         <v>-3.51</v>
       </c>
-      <c r="P39" s="94" t="n">
+      <c r="Q39" s="94" t="n">
         <v>-6.37</v>
-      </c>
-      <c r="Q39" s="94" t="n">
-        <v>-7.92</v>
       </c>
       <c r="R39" s="94" t="n">
         <v>-7.92</v>
@@ -10741,40 +10741,40 @@
         <v>-7.92</v>
       </c>
       <c r="T39" s="94" t="n">
+        <v>-7.92</v>
+      </c>
+      <c r="U39" s="94" t="n">
         <v>-8.25</v>
       </c>
-      <c r="U39" s="94" t="n">
+      <c r="V39" s="94" t="n">
         <v>-9.35</v>
       </c>
-      <c r="V39" s="94" t="n">
+      <c r="W39" s="94" t="n">
         <v>-9.76</v>
-      </c>
-      <c r="W39" s="94" t="n">
-        <v>-8.56</v>
       </c>
       <c r="X39" s="94" t="n">
         <v>-8.56</v>
       </c>
       <c r="Y39" s="94" t="n">
+        <v>-8.56</v>
+      </c>
+      <c r="Z39" s="94" t="n">
         <v>-8.81</v>
       </c>
-      <c r="Z39" s="94" t="n">
+      <c r="AA39" s="94" t="n">
         <v>-9.539999999999999</v>
       </c>
-      <c r="AA39" s="94" t="n">
+      <c r="AB39" s="94" t="n">
         <v>-10.45</v>
       </c>
-      <c r="AB39" s="94" t="n">
+      <c r="AC39" s="94" t="n">
         <v>-10.55</v>
-      </c>
-      <c r="AC39" s="94" t="n">
-        <v>-10.48</v>
       </c>
       <c r="AD39" s="94" t="n">
         <v>-10.48</v>
       </c>
       <c r="AE39" s="94" t="n">
-        <v>-7.84</v>
+        <v>-10.48</v>
       </c>
     </row>
     <row r="40">
@@ -10784,49 +10784,49 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="C40" s="94" t="n">
         <v>-6.51</v>
       </c>
-      <c r="C40" s="94" t="n">
+      <c r="D40" s="94" t="n">
         <v>-5.95</v>
       </c>
-      <c r="D40" s="94" t="n">
+      <c r="E40" s="94" t="n">
         <v>-6.87</v>
-      </c>
-      <c r="E40" s="94" t="n">
-        <v>-4.48</v>
       </c>
       <c r="F40" s="94" t="n">
         <v>-4.48</v>
       </c>
       <c r="G40" s="94" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="H40" s="94" t="n">
         <v>-5</v>
       </c>
-      <c r="H40" s="94" t="n">
+      <c r="I40" s="94" t="n">
         <v>-6.31</v>
       </c>
-      <c r="I40" s="94" t="n">
+      <c r="J40" s="94" t="n">
         <v>-7.42</v>
       </c>
-      <c r="J40" s="94" t="n">
+      <c r="K40" s="94" t="n">
         <v>-7.49</v>
-      </c>
-      <c r="K40" s="94" t="n">
-        <v>-10.13</v>
       </c>
       <c r="L40" s="94" t="n">
         <v>-10.13</v>
       </c>
       <c r="M40" s="94" t="n">
+        <v>-10.13</v>
+      </c>
+      <c r="N40" s="94" t="n">
         <v>-11.05</v>
       </c>
-      <c r="N40" s="94" t="n">
+      <c r="O40" s="94" t="n">
         <v>-11.41</v>
       </c>
-      <c r="O40" s="94" t="n">
+      <c r="P40" s="94" t="n">
         <v>-11.32</v>
-      </c>
-      <c r="P40" s="94" t="n">
-        <v>-12.67</v>
       </c>
       <c r="Q40" s="94" t="n">
         <v>-12.67</v>
@@ -10838,40 +10838,40 @@
         <v>-12.67</v>
       </c>
       <c r="T40" s="94" t="n">
+        <v>-12.67</v>
+      </c>
+      <c r="U40" s="94" t="n">
         <v>-11.01</v>
       </c>
-      <c r="U40" s="94" t="n">
+      <c r="V40" s="94" t="n">
         <v>-10.66</v>
       </c>
-      <c r="V40" s="94" t="n">
+      <c r="W40" s="94" t="n">
         <v>-10.79</v>
-      </c>
-      <c r="W40" s="94" t="n">
-        <v>-10.43</v>
       </c>
       <c r="X40" s="94" t="n">
         <v>-10.43</v>
       </c>
       <c r="Y40" s="94" t="n">
+        <v>-10.43</v>
+      </c>
+      <c r="Z40" s="94" t="n">
         <v>-10.32</v>
       </c>
-      <c r="Z40" s="94" t="n">
+      <c r="AA40" s="94" t="n">
         <v>-11.13</v>
       </c>
-      <c r="AA40" s="94" t="n">
+      <c r="AB40" s="94" t="n">
         <v>-10.47</v>
       </c>
-      <c r="AB40" s="94" t="n">
+      <c r="AC40" s="94" t="n">
         <v>-10.79</v>
-      </c>
-      <c r="AC40" s="94" t="n">
-        <v>-10.25</v>
       </c>
       <c r="AD40" s="94" t="n">
         <v>-10.25</v>
       </c>
       <c r="AE40" s="94" t="n">
-        <v>-8.09</v>
+        <v>-10.25</v>
       </c>
     </row>
     <row r="41">
@@ -10881,52 +10881,52 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
+        <v>43.58</v>
+      </c>
+      <c r="C41" s="94" t="n">
         <v>51.3</v>
       </c>
-      <c r="C41" s="94" t="n">
+      <c r="D41" s="94" t="n">
         <v>54.73</v>
       </c>
-      <c r="D41" s="94" t="n">
+      <c r="E41" s="94" t="n">
         <v>49.08</v>
-      </c>
-      <c r="E41" s="94" t="n">
-        <v>66.64</v>
       </c>
       <c r="F41" s="94" t="n">
         <v>66.64</v>
       </c>
       <c r="G41" s="94" t="n">
+        <v>66.64</v>
+      </c>
+      <c r="H41" s="94" t="n">
         <v>69.73</v>
       </c>
-      <c r="H41" s="94" t="n">
+      <c r="I41" s="94" t="n">
         <v>67.48</v>
       </c>
-      <c r="I41" s="94" t="n">
+      <c r="J41" s="94" t="n">
         <v>79.73</v>
       </c>
-      <c r="J41" s="94" t="n">
+      <c r="K41" s="94" t="n">
         <v>79.58</v>
-      </c>
-      <c r="K41" s="94" t="n">
-        <v>73.84</v>
       </c>
       <c r="L41" s="94" t="n">
         <v>73.84</v>
       </c>
       <c r="M41" s="94" t="n">
+        <v>73.84</v>
+      </c>
+      <c r="N41" s="94" t="n">
         <v>69.91</v>
       </c>
-      <c r="N41" s="94" t="n">
+      <c r="O41" s="94" t="n">
         <v>61.51</v>
       </c>
-      <c r="O41" s="94" t="n">
+      <c r="P41" s="94" t="n">
         <v>59.85</v>
       </c>
-      <c r="P41" s="94" t="n">
+      <c r="Q41" s="94" t="n">
         <v>42.91</v>
-      </c>
-      <c r="Q41" s="94" t="n">
-        <v>35.52</v>
       </c>
       <c r="R41" s="94" t="n">
         <v>35.52</v>
@@ -10935,40 +10935,40 @@
         <v>35.52</v>
       </c>
       <c r="T41" s="94" t="n">
+        <v>35.52</v>
+      </c>
+      <c r="U41" s="94" t="n">
         <v>38.14</v>
       </c>
-      <c r="U41" s="94" t="n">
+      <c r="V41" s="94" t="n">
         <v>39.07</v>
       </c>
-      <c r="V41" s="94" t="n">
+      <c r="W41" s="94" t="n">
         <v>39.23</v>
-      </c>
-      <c r="W41" s="94" t="n">
-        <v>41.72</v>
       </c>
       <c r="X41" s="94" t="n">
         <v>41.72</v>
       </c>
       <c r="Y41" s="94" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="Z41" s="94" t="n">
         <v>41.8</v>
       </c>
-      <c r="Z41" s="94" t="n">
+      <c r="AA41" s="94" t="n">
         <v>31.96</v>
       </c>
-      <c r="AA41" s="94" t="n">
+      <c r="AB41" s="94" t="n">
         <v>16.55</v>
       </c>
-      <c r="AB41" s="94" t="n">
+      <c r="AC41" s="94" t="n">
         <v>17</v>
-      </c>
-      <c r="AC41" s="94" t="n">
-        <v>17.5</v>
       </c>
       <c r="AD41" s="94" t="n">
         <v>17.5</v>
       </c>
       <c r="AE41" s="94" t="n">
-        <v>26.26</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="42">
@@ -10982,139 +10982,139 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C42" s="91" t="inlineStr">
+      <c r="C42" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D42" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D42" s="91" t="inlineStr">
+      <c r="E42" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E42" s="92" t="inlineStr">
+      <c r="F42" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F42" s="92" t="inlineStr">
+      <c r="G42" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G42" s="92" t="inlineStr">
+      <c r="H42" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H42" s="92" t="inlineStr">
+      <c r="I42" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I42" s="93" t="inlineStr">
+      <c r="J42" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J42" s="92" t="inlineStr">
+      <c r="K42" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K42" s="92" t="inlineStr">
+      <c r="L42" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L42" s="92" t="inlineStr">
+      <c r="M42" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M42" s="93" t="inlineStr">
+      <c r="N42" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N42" s="93" t="inlineStr">
+      <c r="O42" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O42" s="93" t="inlineStr">
+      <c r="P42" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P42" s="93" t="inlineStr">
+      <c r="Q42" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q42" s="91" t="inlineStr">
+      <c r="R42" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R42" s="91" t="inlineStr">
+      <c r="S42" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S42" s="92" t="inlineStr">
+      <c r="T42" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T42" s="92" t="inlineStr">
+      <c r="U42" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U42" s="92" t="inlineStr">
+      <c r="V42" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V42" s="92" t="inlineStr">
+      <c r="W42" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W42" s="92" t="inlineStr">
+      <c r="X42" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X42" s="92" t="inlineStr">
+      <c r="Y42" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y42" s="93" t="inlineStr">
+      <c r="Z42" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z42" s="93" t="inlineStr">
+      <c r="AA42" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA42" s="92" t="inlineStr">
+      <c r="AB42" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB42" s="93" t="inlineStr">
+      <c r="AC42" s="93" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AC42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AD42" s="91" t="inlineStr">
@@ -11135,94 +11135,94 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C43" s="94" t="n">
         <v>1.45</v>
       </c>
-      <c r="C43" s="94" t="n">
+      <c r="D43" s="94" t="n">
         <v>5.45</v>
       </c>
-      <c r="D43" s="94" t="n">
+      <c r="E43" s="94" t="n">
         <v>5.17</v>
       </c>
-      <c r="E43" s="94" t="n">
+      <c r="F43" s="94" t="n">
         <v>4.63</v>
       </c>
-      <c r="F43" s="94" t="n">
+      <c r="G43" s="94" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="G43" s="94" t="n">
+      <c r="H43" s="94" t="n">
         <v>8.07</v>
       </c>
-      <c r="H43" s="94" t="n">
+      <c r="I43" s="94" t="n">
         <v>8.81</v>
       </c>
-      <c r="I43" s="94" t="n">
+      <c r="J43" s="94" t="n">
         <v>10.87</v>
       </c>
-      <c r="J43" s="94" t="n">
+      <c r="K43" s="94" t="n">
         <v>9.07</v>
-      </c>
-      <c r="K43" s="94" t="n">
-        <v>10.44</v>
       </c>
       <c r="L43" s="94" t="n">
         <v>10.44</v>
       </c>
       <c r="M43" s="94" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="N43" s="94" t="n">
         <v>11.3</v>
       </c>
-      <c r="N43" s="94" t="n">
+      <c r="O43" s="94" t="n">
         <v>12.33</v>
       </c>
-      <c r="O43" s="94" t="n">
+      <c r="P43" s="94" t="n">
         <v>11.24</v>
       </c>
-      <c r="P43" s="94" t="n">
+      <c r="Q43" s="94" t="n">
         <v>9.34</v>
-      </c>
-      <c r="Q43" s="94" t="n">
-        <v>9</v>
       </c>
       <c r="R43" s="94" t="n">
         <v>9</v>
       </c>
       <c r="S43" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="T43" s="94" t="n">
         <v>7.9</v>
       </c>
-      <c r="T43" s="94" t="n">
+      <c r="U43" s="94" t="n">
         <v>7.82</v>
       </c>
-      <c r="U43" s="94" t="n">
+      <c r="V43" s="94" t="n">
         <v>7.02</v>
       </c>
-      <c r="V43" s="94" t="n">
+      <c r="W43" s="94" t="n">
         <v>8.41</v>
-      </c>
-      <c r="W43" s="94" t="n">
-        <v>9.82</v>
       </c>
       <c r="X43" s="94" t="n">
         <v>9.82</v>
       </c>
       <c r="Y43" s="94" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="Z43" s="94" t="n">
         <v>9.59</v>
       </c>
-      <c r="Z43" s="94" t="n">
+      <c r="AA43" s="94" t="n">
         <v>10.06</v>
       </c>
-      <c r="AA43" s="94" t="n">
+      <c r="AB43" s="94" t="n">
         <v>9.789999999999999</v>
       </c>
-      <c r="AB43" s="94" t="n">
+      <c r="AC43" s="94" t="n">
         <v>12.27</v>
-      </c>
-      <c r="AC43" s="94" t="n">
-        <v>11.8</v>
       </c>
       <c r="AD43" s="94" t="n">
         <v>11.8</v>
       </c>
       <c r="AE43" s="94" t="n">
-        <v>11.96</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="44">
@@ -11232,94 +11232,94 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="C44" s="94" t="n">
         <v>-0.04</v>
       </c>
-      <c r="C44" s="94" t="n">
+      <c r="D44" s="94" t="n">
         <v>3.71</v>
       </c>
-      <c r="D44" s="94" t="n">
+      <c r="E44" s="94" t="n">
         <v>4.44</v>
       </c>
-      <c r="E44" s="94" t="n">
+      <c r="F44" s="94" t="n">
         <v>3.05</v>
       </c>
-      <c r="F44" s="94" t="n">
+      <c r="G44" s="94" t="n">
         <v>5.25</v>
       </c>
-      <c r="G44" s="94" t="n">
+      <c r="H44" s="94" t="n">
         <v>5.47</v>
       </c>
-      <c r="H44" s="94" t="n">
+      <c r="I44" s="94" t="n">
         <v>6.49</v>
       </c>
-      <c r="I44" s="94" t="n">
+      <c r="J44" s="94" t="n">
         <v>8.44</v>
       </c>
-      <c r="J44" s="94" t="n">
+      <c r="K44" s="94" t="n">
         <v>5.87</v>
-      </c>
-      <c r="K44" s="94" t="n">
-        <v>6.19</v>
       </c>
       <c r="L44" s="94" t="n">
         <v>6.19</v>
       </c>
       <c r="M44" s="94" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="N44" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="N44" s="94" t="n">
+      <c r="O44" s="94" t="n">
         <v>4.87</v>
       </c>
-      <c r="O44" s="94" t="n">
+      <c r="P44" s="94" t="n">
         <v>4.81</v>
       </c>
-      <c r="P44" s="94" t="n">
+      <c r="Q44" s="94" t="n">
         <v>6.72</v>
-      </c>
-      <c r="Q44" s="94" t="n">
-        <v>5.58</v>
       </c>
       <c r="R44" s="94" t="n">
         <v>5.58</v>
       </c>
       <c r="S44" s="94" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="T44" s="94" t="n">
         <v>5.73</v>
       </c>
-      <c r="T44" s="94" t="n">
+      <c r="U44" s="94" t="n">
         <v>6.52</v>
       </c>
-      <c r="U44" s="94" t="n">
+      <c r="V44" s="94" t="n">
         <v>4.29</v>
       </c>
-      <c r="V44" s="94" t="n">
+      <c r="W44" s="94" t="n">
         <v>8.1</v>
-      </c>
-      <c r="W44" s="94" t="n">
-        <v>8.460000000000001</v>
       </c>
       <c r="X44" s="94" t="n">
         <v>8.460000000000001</v>
       </c>
       <c r="Y44" s="94" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="Z44" s="94" t="n">
         <v>10.04</v>
       </c>
-      <c r="Z44" s="94" t="n">
+      <c r="AA44" s="94" t="n">
         <v>9.49</v>
       </c>
-      <c r="AA44" s="94" t="n">
+      <c r="AB44" s="94" t="n">
         <v>8.24</v>
       </c>
-      <c r="AB44" s="94" t="n">
+      <c r="AC44" s="94" t="n">
         <v>10.85</v>
-      </c>
-      <c r="AC44" s="94" t="n">
-        <v>9.5</v>
       </c>
       <c r="AD44" s="94" t="n">
         <v>9.5</v>
       </c>
       <c r="AE44" s="94" t="n">
-        <v>9.119999999999999</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="45">
@@ -11329,94 +11329,94 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="C45" s="94" t="n">
         <v>17.48</v>
       </c>
-      <c r="C45" s="94" t="n">
+      <c r="D45" s="94" t="n">
         <v>34.95</v>
       </c>
-      <c r="D45" s="94" t="n">
+      <c r="E45" s="94" t="n">
         <v>36.94</v>
       </c>
-      <c r="E45" s="94" t="n">
+      <c r="F45" s="94" t="n">
         <v>18.86</v>
       </c>
-      <c r="F45" s="94" t="n">
+      <c r="G45" s="94" t="n">
         <v>28.39</v>
       </c>
-      <c r="G45" s="94" t="n">
+      <c r="H45" s="94" t="n">
         <v>37.31</v>
       </c>
-      <c r="H45" s="94" t="n">
+      <c r="I45" s="94" t="n">
         <v>43.26</v>
       </c>
-      <c r="I45" s="94" t="n">
+      <c r="J45" s="94" t="n">
         <v>57.32</v>
       </c>
-      <c r="J45" s="94" t="n">
+      <c r="K45" s="94" t="n">
         <v>40.07</v>
-      </c>
-      <c r="K45" s="94" t="n">
-        <v>43.42</v>
       </c>
       <c r="L45" s="94" t="n">
         <v>43.42</v>
       </c>
       <c r="M45" s="94" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="N45" s="94" t="n">
         <v>52.1</v>
       </c>
-      <c r="N45" s="94" t="n">
+      <c r="O45" s="94" t="n">
         <v>68.64</v>
       </c>
-      <c r="O45" s="94" t="n">
+      <c r="P45" s="94" t="n">
         <v>61.42</v>
       </c>
-      <c r="P45" s="94" t="n">
+      <c r="Q45" s="94" t="n">
         <v>55.59</v>
-      </c>
-      <c r="Q45" s="94" t="n">
-        <v>48.6</v>
       </c>
       <c r="R45" s="94" t="n">
         <v>48.6</v>
       </c>
       <c r="S45" s="94" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="T45" s="94" t="n">
         <v>31.62</v>
       </c>
-      <c r="T45" s="94" t="n">
+      <c r="U45" s="94" t="n">
         <v>37.15</v>
       </c>
-      <c r="U45" s="94" t="n">
+      <c r="V45" s="94" t="n">
         <v>27.78</v>
       </c>
-      <c r="V45" s="94" t="n">
+      <c r="W45" s="94" t="n">
         <v>37.95</v>
-      </c>
-      <c r="W45" s="94" t="n">
-        <v>47.6</v>
       </c>
       <c r="X45" s="94" t="n">
         <v>47.6</v>
       </c>
       <c r="Y45" s="94" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="Z45" s="94" t="n">
         <v>60.55</v>
       </c>
-      <c r="Z45" s="94" t="n">
+      <c r="AA45" s="94" t="n">
         <v>57.69</v>
       </c>
-      <c r="AA45" s="94" t="n">
+      <c r="AB45" s="94" t="n">
         <v>39.06</v>
       </c>
-      <c r="AB45" s="94" t="n">
+      <c r="AC45" s="94" t="n">
         <v>67.92</v>
-      </c>
-      <c r="AC45" s="94" t="n">
-        <v>51.18</v>
       </c>
       <c r="AD45" s="94" t="n">
         <v>51.18</v>
       </c>
       <c r="AE45" s="94" t="n">
-        <v>48.97</v>
+        <v>51.18</v>
       </c>
     </row>
     <row r="46">
@@ -11430,139 +11430,139 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C46" s="91" t="inlineStr">
+      <c r="C46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D46" s="91" t="inlineStr">
+      <c r="E46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E46" s="92" t="inlineStr">
+      <c r="F46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F46" s="92" t="inlineStr">
+      <c r="G46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G46" s="92" t="inlineStr">
+      <c r="H46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H46" s="92" t="inlineStr">
+      <c r="I46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I46" s="93" t="inlineStr">
+      <c r="J46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J46" s="92" t="inlineStr">
+      <c r="K46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K46" s="92" t="inlineStr">
+      <c r="L46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L46" s="92" t="inlineStr">
+      <c r="M46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M46" s="91" t="inlineStr">
+      <c r="N46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N46" s="93" t="inlineStr">
+      <c r="O46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O46" s="93" t="inlineStr">
+      <c r="P46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P46" s="93" t="inlineStr">
+      <c r="Q46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q46" s="93" t="inlineStr">
+      <c r="R46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R46" s="93" t="inlineStr">
+      <c r="S46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S46" s="92" t="inlineStr">
+      <c r="T46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T46" s="91" t="inlineStr">
+      <c r="U46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U46" s="92" t="inlineStr">
+      <c r="V46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V46" s="92" t="inlineStr">
+      <c r="W46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W46" s="91" t="inlineStr">
+      <c r="X46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X46" s="91" t="inlineStr">
+      <c r="Y46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y46" s="93" t="inlineStr">
+      <c r="Z46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z46" s="93" t="inlineStr">
+      <c r="AA46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA46" s="92" t="inlineStr">
+      <c r="AB46" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB46" s="93" t="inlineStr">
+      <c r="AC46" s="93" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AC46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AD46" s="91" t="inlineStr">
@@ -11583,94 +11583,94 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="C47" s="94" t="n">
         <v>6.89</v>
       </c>
-      <c r="C47" s="94" t="n">
+      <c r="D47" s="94" t="n">
         <v>10.14</v>
       </c>
-      <c r="D47" s="94" t="n">
+      <c r="E47" s="94" t="n">
         <v>10.81</v>
       </c>
-      <c r="E47" s="94" t="n">
+      <c r="F47" s="94" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="F47" s="94" t="n">
+      <c r="G47" s="94" t="n">
         <v>12.84</v>
       </c>
-      <c r="G47" s="94" t="n">
+      <c r="H47" s="94" t="n">
         <v>13.25</v>
       </c>
-      <c r="H47" s="94" t="n">
+      <c r="I47" s="94" t="n">
         <v>14.72</v>
       </c>
-      <c r="I47" s="94" t="n">
+      <c r="J47" s="94" t="n">
         <v>15.64</v>
       </c>
-      <c r="J47" s="94" t="n">
+      <c r="K47" s="94" t="n">
         <v>15.13</v>
-      </c>
-      <c r="K47" s="94" t="n">
-        <v>15.12</v>
       </c>
       <c r="L47" s="94" t="n">
         <v>15.12</v>
       </c>
       <c r="M47" s="94" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="N47" s="94" t="n">
         <v>15.17</v>
       </c>
-      <c r="N47" s="94" t="n">
+      <c r="O47" s="94" t="n">
         <v>15.04</v>
       </c>
-      <c r="O47" s="94" t="n">
+      <c r="P47" s="94" t="n">
         <v>15.48</v>
       </c>
-      <c r="P47" s="94" t="n">
+      <c r="Q47" s="94" t="n">
         <v>13.98</v>
-      </c>
-      <c r="Q47" s="94" t="n">
-        <v>12.65</v>
       </c>
       <c r="R47" s="94" t="n">
         <v>12.65</v>
       </c>
       <c r="S47" s="94" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="T47" s="94" t="n">
         <v>10.48</v>
       </c>
-      <c r="T47" s="94" t="n">
+      <c r="U47" s="94" t="n">
         <v>11.16</v>
       </c>
-      <c r="U47" s="94" t="n">
+      <c r="V47" s="94" t="n">
         <v>9.84</v>
       </c>
-      <c r="V47" s="94" t="n">
+      <c r="W47" s="94" t="n">
         <v>11.18</v>
-      </c>
-      <c r="W47" s="94" t="n">
-        <v>12.87</v>
       </c>
       <c r="X47" s="94" t="n">
         <v>12.87</v>
       </c>
       <c r="Y47" s="94" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="Z47" s="94" t="n">
         <v>15.03</v>
       </c>
-      <c r="Z47" s="94" t="n">
+      <c r="AA47" s="94" t="n">
         <v>14.08</v>
       </c>
-      <c r="AA47" s="94" t="n">
+      <c r="AB47" s="94" t="n">
         <v>11.54</v>
       </c>
-      <c r="AB47" s="94" t="n">
+      <c r="AC47" s="94" t="n">
         <v>16.12</v>
-      </c>
-      <c r="AC47" s="94" t="n">
-        <v>14.9</v>
       </c>
       <c r="AD47" s="94" t="n">
         <v>14.9</v>
       </c>
       <c r="AE47" s="94" t="n">
-        <v>16.09</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="48">
@@ -11680,94 +11680,94 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="C48" s="94" t="n">
         <v>13.05</v>
       </c>
-      <c r="C48" s="94" t="n">
+      <c r="D48" s="94" t="n">
         <v>16.29</v>
       </c>
-      <c r="D48" s="94" t="n">
+      <c r="E48" s="94" t="n">
         <v>18.22</v>
       </c>
-      <c r="E48" s="94" t="n">
+      <c r="F48" s="94" t="n">
         <v>16.01</v>
       </c>
-      <c r="F48" s="94" t="n">
+      <c r="G48" s="94" t="n">
         <v>17.47</v>
       </c>
-      <c r="G48" s="94" t="n">
+      <c r="H48" s="94" t="n">
         <v>19.27</v>
       </c>
-      <c r="H48" s="94" t="n">
+      <c r="I48" s="94" t="n">
         <v>19.17</v>
       </c>
-      <c r="I48" s="94" t="n">
+      <c r="J48" s="94" t="n">
         <v>20.28</v>
       </c>
-      <c r="J48" s="94" t="n">
+      <c r="K48" s="94" t="n">
         <v>18.25</v>
-      </c>
-      <c r="K48" s="94" t="n">
-        <v>17.55</v>
       </c>
       <c r="L48" s="94" t="n">
         <v>17.55</v>
       </c>
       <c r="M48" s="94" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="N48" s="94" t="n">
         <v>19.55</v>
       </c>
-      <c r="N48" s="94" t="n">
+      <c r="O48" s="94" t="n">
         <v>23.1</v>
       </c>
-      <c r="O48" s="94" t="n">
+      <c r="P48" s="94" t="n">
         <v>23.08</v>
       </c>
-      <c r="P48" s="94" t="n">
+      <c r="Q48" s="94" t="n">
         <v>22.86</v>
-      </c>
-      <c r="Q48" s="94" t="n">
-        <v>22.79</v>
       </c>
       <c r="R48" s="94" t="n">
         <v>22.79</v>
       </c>
       <c r="S48" s="94" t="n">
+        <v>22.79</v>
+      </c>
+      <c r="T48" s="94" t="n">
         <v>18.76</v>
       </c>
-      <c r="T48" s="94" t="n">
+      <c r="U48" s="94" t="n">
         <v>21.19</v>
       </c>
-      <c r="U48" s="94" t="n">
+      <c r="V48" s="94" t="n">
         <v>19.24</v>
       </c>
-      <c r="V48" s="94" t="n">
+      <c r="W48" s="94" t="n">
         <v>21.4</v>
-      </c>
-      <c r="W48" s="94" t="n">
-        <v>23.05</v>
       </c>
       <c r="X48" s="94" t="n">
         <v>23.05</v>
       </c>
       <c r="Y48" s="94" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="Z48" s="94" t="n">
         <v>26.47</v>
       </c>
-      <c r="Z48" s="94" t="n">
+      <c r="AA48" s="94" t="n">
         <v>25.92</v>
       </c>
-      <c r="AA48" s="94" t="n">
+      <c r="AB48" s="94" t="n">
         <v>22.23</v>
       </c>
-      <c r="AB48" s="94" t="n">
+      <c r="AC48" s="94" t="n">
         <v>25.5</v>
-      </c>
-      <c r="AC48" s="94" t="n">
-        <v>23.22</v>
       </c>
       <c r="AD48" s="94" t="n">
         <v>23.22</v>
       </c>
       <c r="AE48" s="94" t="n">
-        <v>21.39</v>
+        <v>23.22</v>
       </c>
     </row>
     <row r="49">
@@ -11777,100 +11777,100 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="C49" s="94" t="n">
         <v>25.18</v>
       </c>
-      <c r="C49" s="94" t="n">
+      <c r="D49" s="94" t="n">
         <v>39.55</v>
       </c>
-      <c r="D49" s="94" t="n">
+      <c r="E49" s="94" t="n">
         <v>44.2</v>
       </c>
-      <c r="E49" s="94" t="n">
+      <c r="F49" s="94" t="n">
         <v>25.84</v>
       </c>
-      <c r="F49" s="94" t="n">
+      <c r="G49" s="94" t="n">
         <v>33</v>
       </c>
-      <c r="G49" s="94" t="n">
+      <c r="H49" s="94" t="n">
         <v>39.69</v>
       </c>
-      <c r="H49" s="94" t="n">
+      <c r="I49" s="94" t="n">
         <v>45.34</v>
       </c>
-      <c r="I49" s="94" t="n">
+      <c r="J49" s="94" t="n">
         <v>56.7</v>
       </c>
-      <c r="J49" s="94" t="n">
+      <c r="K49" s="94" t="n">
         <v>45.99</v>
-      </c>
-      <c r="K49" s="94" t="n">
-        <v>47.47</v>
       </c>
       <c r="L49" s="94" t="n">
         <v>47.47</v>
       </c>
       <c r="M49" s="94" t="n">
+        <v>47.47</v>
+      </c>
+      <c r="N49" s="94" t="n">
         <v>51.27</v>
       </c>
-      <c r="N49" s="94" t="n">
+      <c r="O49" s="94" t="n">
         <v>62.47</v>
       </c>
-      <c r="O49" s="94" t="n">
+      <c r="P49" s="94" t="n">
         <v>66.34</v>
       </c>
-      <c r="P49" s="94" t="n">
+      <c r="Q49" s="94" t="n">
         <v>61.48</v>
-      </c>
-      <c r="Q49" s="94" t="n">
-        <v>57.71</v>
       </c>
       <c r="R49" s="94" t="n">
         <v>57.71</v>
       </c>
       <c r="S49" s="94" t="n">
+        <v>57.71</v>
+      </c>
+      <c r="T49" s="94" t="n">
         <v>46.87</v>
       </c>
-      <c r="T49" s="94" t="n">
+      <c r="U49" s="94" t="n">
         <v>49.63</v>
       </c>
-      <c r="U49" s="94" t="n">
+      <c r="V49" s="94" t="n">
         <v>40.3</v>
       </c>
-      <c r="V49" s="94" t="n">
+      <c r="W49" s="94" t="n">
         <v>46.31</v>
-      </c>
-      <c r="W49" s="94" t="n">
-        <v>55.45</v>
       </c>
       <c r="X49" s="94" t="n">
         <v>55.45</v>
       </c>
       <c r="Y49" s="94" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="Z49" s="94" t="n">
         <v>67.13</v>
       </c>
-      <c r="Z49" s="94" t="n">
+      <c r="AA49" s="94" t="n">
         <v>61.57</v>
       </c>
-      <c r="AA49" s="94" t="n">
+      <c r="AB49" s="94" t="n">
         <v>43.95</v>
       </c>
-      <c r="AB49" s="94" t="n">
+      <c r="AC49" s="94" t="n">
         <v>75.19</v>
-      </c>
-      <c r="AC49" s="94" t="n">
-        <v>56.46</v>
       </c>
       <c r="AD49" s="94" t="n">
         <v>56.46</v>
       </c>
       <c r="AE49" s="94" t="n">
-        <v>56.43</v>
+        <v>56.46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RS4:18.53&lt;=22;us30:RS3:14.42&lt;=25;ixic:RS2:9.58&lt;=38;jp225:RNG60:-13.34&lt;=-10;jp225:RS9:18.88&lt;=28;vn:RS3:5.54&lt;=25;fr40:RS5:17.48&lt;=20</t>
+          <t>今日买报：hk50:RS4:18.53&lt;=22;us500:RS2:9.18&lt;=22;us30:RS3:14.42&lt;=25;ixic:RS2:9.58&lt;=38;jp225:RNG60:-15.51&lt;=-10;jp225:RS9:14.64&lt;=28;vn:RS3:4.29&lt;=25;fr40:RS5:14.05&lt;=20</t>
         </is>
       </c>
     </row>

--- a/report_2504.xlsx
+++ b/report_2504.xlsx
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>-9.69</v>
+        <v>-14.13</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>-9.69</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>-6.83</v>
+        <v>-12.21</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>-6.83</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>9.18</v>
+        <v>2.99</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>9.18</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>-5.06</v>
+        <v>-9.91</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>-5.06</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>-4.62</v>
+        <v>-9.75</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>-4.62</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>14.42</v>
+        <v>5.68</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>14.42</v>
@@ -9337,13 +9337,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="76" t="inlineStr">
+      <c r="A27" s="96" t="inlineStr">
         <is>
           <t>ixic:RNG60</t>
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>-16.68</v>
+        <v>-20.02</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>-16.68</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>-9.52</v>
+        <v>-14.74</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>-9.52</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>9.58</v>
+        <v>3.7</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>9.58</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-3.42</v>
+        <v>-3.56</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-2.43</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-7.25</v>
+        <v>-7.39</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-6.51</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>43.58</v>
+        <v>42.69</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>51.3</v>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>1.45</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-0.32</v>
+        <v>-3.28</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-0.04</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>14.05</v>
+        <v>9.82</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>17.48</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>5.66</v>
+        <v>2.11</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>6.89</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>10.24</v>
+        <v>6.54</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>13.05</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>20.43</v>
+        <v>14.84</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>25.18</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RS4:18.53&lt;=22;us500:RS2:9.18&lt;=22;us30:RS3:14.42&lt;=25;ixic:RS2:9.58&lt;=38;jp225:RNG60:-15.51&lt;=-10;jp225:RS9:14.64&lt;=28;vn:RS3:4.29&lt;=25;fr40:RS5:14.05&lt;=20</t>
+          <t>今日买报：hk50:RS4:18.53&lt;=22;us500:RS2:2.99&lt;=22;us30:RS3:5.68&lt;=25;ixic:RNG60:-20.02&lt;=-20;ixic:RS2:3.7&lt;=38;jp225:RNG60:-15.51&lt;=-10;jp225:RS9:14.64&lt;=28;vn:RS3:4.29&lt;=25;fr40:RS5:9.82&lt;=20</t>
         </is>
       </c>
     </row>

--- a/report_2504.xlsx
+++ b/report_2504.xlsx
@@ -800,7 +800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1058,11 +1058,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -6342,152 +6341,152 @@
       </c>
       <c r="B1" s="77" t="inlineStr">
         <is>
+          <t>250407</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
+          <t>250406</t>
+        </is>
+      </c>
+      <c r="D1" s="77" t="inlineStr">
+        <is>
           <t>250404</t>
         </is>
       </c>
-      <c r="C1" s="77" t="inlineStr">
+      <c r="E1" s="77" t="inlineStr">
         <is>
           <t>250403</t>
         </is>
       </c>
-      <c r="D1" s="77" t="inlineStr">
+      <c r="F1" s="77" t="inlineStr">
         <is>
           <t>250402</t>
         </is>
       </c>
-      <c r="E1" s="77" t="inlineStr">
+      <c r="G1" s="77" t="inlineStr">
         <is>
           <t>250401</t>
         </is>
       </c>
-      <c r="F1" s="77" t="inlineStr">
+      <c r="H1" s="77" t="inlineStr">
         <is>
           <t>250331</t>
         </is>
       </c>
-      <c r="G1" s="77" t="inlineStr">
+      <c r="I1" s="77" t="inlineStr">
         <is>
           <t>250328</t>
         </is>
       </c>
-      <c r="H1" s="77" t="inlineStr">
+      <c r="J1" s="77" t="inlineStr">
         <is>
           <t>250327</t>
         </is>
       </c>
-      <c r="I1" s="77" t="inlineStr">
+      <c r="K1" s="77" t="inlineStr">
         <is>
           <t>250326</t>
         </is>
       </c>
-      <c r="J1" s="77" t="inlineStr">
+      <c r="L1" s="77" t="inlineStr">
         <is>
           <t>250325</t>
         </is>
       </c>
-      <c r="K1" s="77" t="inlineStr">
+      <c r="M1" s="77" t="inlineStr">
         <is>
           <t>250324</t>
         </is>
       </c>
-      <c r="L1" s="77" t="inlineStr">
+      <c r="N1" s="77" t="inlineStr">
         <is>
           <t>250323</t>
         </is>
       </c>
-      <c r="M1" s="77" t="inlineStr">
+      <c r="O1" s="77" t="inlineStr">
         <is>
           <t>250321</t>
         </is>
       </c>
-      <c r="N1" s="77" t="inlineStr">
+      <c r="P1" s="77" t="inlineStr">
         <is>
           <t>250320</t>
         </is>
       </c>
-      <c r="O1" s="77" t="inlineStr">
+      <c r="Q1" s="77" t="inlineStr">
         <is>
           <t>250319</t>
         </is>
       </c>
-      <c r="P1" s="77" t="inlineStr">
+      <c r="R1" s="77" t="inlineStr">
         <is>
           <t>250318</t>
         </is>
       </c>
-      <c r="Q1" s="77" t="inlineStr">
+      <c r="S1" s="77" t="inlineStr">
         <is>
           <t>250317</t>
         </is>
       </c>
-      <c r="R1" s="77" t="inlineStr">
+      <c r="T1" s="77" t="inlineStr">
         <is>
           <t>250316</t>
         </is>
       </c>
-      <c r="S1" s="77" t="inlineStr">
+      <c r="U1" s="77" t="inlineStr">
         <is>
           <t>250314</t>
         </is>
       </c>
-      <c r="T1" s="77" t="inlineStr">
+      <c r="V1" s="77" t="inlineStr">
         <is>
           <t>250313</t>
         </is>
       </c>
-      <c r="U1" s="77" t="inlineStr">
+      <c r="W1" s="77" t="inlineStr">
         <is>
           <t>250312</t>
         </is>
       </c>
-      <c r="V1" s="77" t="inlineStr">
+      <c r="X1" s="77" t="inlineStr">
         <is>
           <t>250311</t>
         </is>
       </c>
-      <c r="W1" s="77" t="inlineStr">
+      <c r="Y1" s="77" t="inlineStr">
         <is>
           <t>250310</t>
         </is>
       </c>
-      <c r="X1" s="77" t="inlineStr">
+      <c r="Z1" s="77" t="inlineStr">
         <is>
           <t>250309</t>
         </is>
       </c>
-      <c r="Y1" s="77" t="inlineStr">
+      <c r="AA1" s="77" t="inlineStr">
         <is>
           <t>250307</t>
         </is>
       </c>
-      <c r="Z1" s="77" t="inlineStr">
+      <c r="AB1" s="77" t="inlineStr">
         <is>
           <t>250306</t>
         </is>
       </c>
-      <c r="AA1" s="77" t="inlineStr">
+      <c r="AC1" s="77" t="inlineStr">
         <is>
           <t>250305</t>
         </is>
       </c>
-      <c r="AB1" s="77" t="inlineStr">
+      <c r="AD1" s="77" t="inlineStr">
         <is>
           <t>250304</t>
         </is>
       </c>
-      <c r="AC1" s="77" t="inlineStr">
+      <c r="AE1" s="77" t="inlineStr">
         <is>
           <t>250303</t>
-        </is>
-      </c>
-      <c r="AD1" s="77" t="inlineStr">
-        <is>
-          <t>250302</t>
-        </is>
-      </c>
-      <c r="AE1" s="77" t="inlineStr">
-        <is>
-          <t>250228</t>
         </is>
       </c>
     </row>
@@ -6499,150 +6498,150 @@
       </c>
       <c r="B2" s="91" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C2" s="92" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C2" s="91" t="inlineStr">
+      <c r="D2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D2" s="91" t="inlineStr">
+      <c r="E2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E2" s="91" t="inlineStr">
+      <c r="F2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F2" s="92" t="inlineStr">
+      <c r="G2" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G2" s="92" t="inlineStr">
+      <c r="I2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H2" s="92" t="inlineStr">
+      <c r="J2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I2" s="92" t="inlineStr">
+      <c r="K2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J2" s="92" t="inlineStr">
+      <c r="L2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K2" s="92" t="inlineStr">
+      <c r="M2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L2" s="92" t="inlineStr">
+      <c r="N2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M2" s="92" t="inlineStr">
+      <c r="O2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N2" s="91" t="inlineStr">
+      <c r="P2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O2" s="93" t="inlineStr">
+      <c r="Q2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P2" s="93" t="inlineStr">
+      <c r="R2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q2" s="93" t="inlineStr">
+      <c r="S2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R2" s="93" t="inlineStr">
+      <c r="T2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S2" s="93" t="inlineStr">
+      <c r="U2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T2" s="91" t="inlineStr">
+      <c r="V2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U2" s="91" t="inlineStr">
+      <c r="W2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V2" s="93" t="inlineStr">
+      <c r="X2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W2" s="93" t="inlineStr">
+      <c r="Y2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X2" s="93" t="inlineStr">
+      <c r="Z2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y2" s="93" t="inlineStr">
+      <c r="AA2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z2" s="93" t="inlineStr">
+      <c r="AB2" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA2" s="91" t="inlineStr">
+      <c r="AC2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB2" s="92" t="inlineStr">
+      <c r="AD2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC2" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD2" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE2" s="92" t="inlineStr">
+      <c r="AE2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -6655,94 +6654,94 @@
         </is>
       </c>
       <c r="B3" s="94" t="n">
-        <v>-0.29</v>
+        <v>-4.53</v>
       </c>
       <c r="C3" s="94" t="n">
         <v>-0.29</v>
       </c>
       <c r="D3" s="94" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="E3" s="94" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="F3" s="94" t="n">
         <v>-1.68</v>
       </c>
-      <c r="E3" s="94" t="n">
+      <c r="G3" s="94" t="n">
         <v>-1.52</v>
       </c>
-      <c r="F3" s="94" t="n">
+      <c r="H3" s="94" t="n">
         <v>-1.83</v>
       </c>
-      <c r="G3" s="94" t="n">
+      <c r="I3" s="94" t="n">
         <v>-1.24</v>
       </c>
-      <c r="H3" s="94" t="n">
+      <c r="J3" s="94" t="n">
         <v>-0.58</v>
       </c>
-      <c r="I3" s="94" t="n">
+      <c r="K3" s="94" t="n">
         <v>0.52</v>
       </c>
-      <c r="J3" s="94" t="n">
+      <c r="L3" s="94" t="n">
         <v>0.06</v>
       </c>
-      <c r="K3" s="94" t="n">
+      <c r="M3" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="94" t="n">
+      <c r="N3" s="94" t="n">
         <v>-0.51</v>
       </c>
-      <c r="M3" s="94" t="n">
+      <c r="O3" s="94" t="n">
         <v>-0.51</v>
       </c>
-      <c r="N3" s="94" t="n">
+      <c r="P3" s="94" t="n">
         <v>1.41</v>
       </c>
-      <c r="O3" s="94" t="n">
+      <c r="Q3" s="94" t="n">
         <v>1.18</v>
       </c>
-      <c r="P3" s="94" t="n">
+      <c r="R3" s="94" t="n">
         <v>1.12</v>
       </c>
-      <c r="Q3" s="94" t="n">
+      <c r="S3" s="94" t="n">
         <v>-1.02</v>
       </c>
-      <c r="R3" s="94" t="n">
+      <c r="T3" s="94" t="n">
         <v>-0.38</v>
       </c>
-      <c r="S3" s="94" t="n">
+      <c r="U3" s="94" t="n">
         <v>-0.38</v>
       </c>
-      <c r="T3" s="94" t="n">
+      <c r="V3" s="94" t="n">
         <v>-1.87</v>
       </c>
-      <c r="U3" s="94" t="n">
+      <c r="W3" s="94" t="n">
         <v>-0.9</v>
       </c>
-      <c r="V3" s="94" t="n">
+      <c r="X3" s="94" t="n">
         <v>-0.71</v>
       </c>
-      <c r="W3" s="94" t="n">
+      <c r="Y3" s="94" t="n">
         <v>-0.08</v>
       </c>
-      <c r="X3" s="94" t="n">
+      <c r="Z3" s="94" t="n">
         <v>0.23</v>
       </c>
-      <c r="Y3" s="94" t="n">
+      <c r="AA3" s="94" t="n">
         <v>0.23</v>
       </c>
-      <c r="Z3" s="94" t="n">
+      <c r="AB3" s="94" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AA3" s="94" t="n">
+      <c r="AC3" s="94" t="n">
         <v>-0.65</v>
       </c>
-      <c r="AB3" s="94" t="n">
+      <c r="AD3" s="94" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AC3" s="94" t="n">
+      <c r="AE3" s="94" t="n">
         <v>0.64</v>
-      </c>
-      <c r="AD3" s="94" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="AE3" s="94" t="n">
-        <v>0.34</v>
       </c>
     </row>
     <row r="4">
@@ -6752,191 +6751,191 @@
         </is>
       </c>
       <c r="B4" s="94" t="n">
-        <v>-4.23</v>
+        <v>-4.42</v>
       </c>
       <c r="C4" s="94" t="n">
         <v>-4.23</v>
       </c>
       <c r="D4" s="94" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="E4" s="94" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="F4" s="94" t="n">
         <v>0.41</v>
       </c>
-      <c r="E4" s="94" t="n">
+      <c r="G4" s="94" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="F4" s="94" t="n">
+      <c r="H4" s="94" t="n">
         <v>11.16</v>
       </c>
-      <c r="G4" s="94" t="n">
+      <c r="I4" s="94" t="n">
         <v>15.71</v>
       </c>
-      <c r="H4" s="94" t="n">
+      <c r="J4" s="94" t="n">
         <v>17.83</v>
       </c>
-      <c r="I4" s="94" t="n">
+      <c r="K4" s="94" t="n">
         <v>22.55</v>
       </c>
-      <c r="J4" s="94" t="n">
+      <c r="L4" s="94" t="n">
         <v>23.14</v>
       </c>
-      <c r="K4" s="94" t="n">
+      <c r="M4" s="94" t="n">
         <v>23.17</v>
       </c>
-      <c r="L4" s="94" t="n">
+      <c r="N4" s="94" t="n">
         <v>23.83</v>
       </c>
-      <c r="M4" s="94" t="n">
+      <c r="O4" s="94" t="n">
         <v>23.83</v>
       </c>
-      <c r="N4" s="94" t="n">
+      <c r="P4" s="94" t="n">
         <v>26.07</v>
       </c>
-      <c r="O4" s="94" t="n">
+      <c r="Q4" s="94" t="n">
         <v>26.11</v>
       </c>
-      <c r="P4" s="94" t="n">
+      <c r="R4" s="94" t="n">
         <v>26.01</v>
       </c>
-      <c r="Q4" s="94" t="n">
+      <c r="S4" s="94" t="n">
         <v>24.85</v>
       </c>
-      <c r="R4" s="94" t="n">
+      <c r="T4" s="94" t="n">
         <v>24.96</v>
       </c>
-      <c r="S4" s="94" t="n">
+      <c r="U4" s="94" t="n">
         <v>24.96</v>
       </c>
-      <c r="T4" s="94" t="n">
+      <c r="V4" s="94" t="n">
         <v>21.44</v>
       </c>
-      <c r="U4" s="94" t="n">
+      <c r="W4" s="94" t="n">
         <v>20.93</v>
       </c>
-      <c r="V4" s="94" t="n">
+      <c r="X4" s="94" t="n">
         <v>21.39</v>
       </c>
-      <c r="W4" s="94" t="n">
+      <c r="Y4" s="94" t="n">
         <v>20.09</v>
       </c>
-      <c r="X4" s="94" t="n">
+      <c r="Z4" s="94" t="n">
         <v>19.98</v>
       </c>
-      <c r="Y4" s="94" t="n">
+      <c r="AA4" s="94" t="n">
         <v>19.98</v>
       </c>
-      <c r="Z4" s="94" t="n">
+      <c r="AB4" s="94" t="n">
         <v>18.96</v>
       </c>
-      <c r="AA4" s="94" t="n">
+      <c r="AC4" s="94" t="n">
         <v>18.38</v>
       </c>
-      <c r="AB4" s="94" t="n">
+      <c r="AD4" s="94" t="n">
         <v>17.16</v>
       </c>
-      <c r="AC4" s="94" t="n">
+      <c r="AE4" s="94" t="n">
         <v>16.44</v>
       </c>
-      <c r="AD4" s="94" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="AE4" s="94" t="n">
-        <v>16.3</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="76" t="inlineStr">
+      <c r="A5" s="95" t="inlineStr">
         <is>
           <t>sh:RS3</t>
         </is>
       </c>
       <c r="B5" s="94" t="n">
-        <v>29.66</v>
+        <v>2.16</v>
       </c>
       <c r="C5" s="94" t="n">
         <v>29.66</v>
       </c>
       <c r="D5" s="94" t="n">
+        <v>29.66</v>
+      </c>
+      <c r="E5" s="94" t="n">
+        <v>29.66</v>
+      </c>
+      <c r="F5" s="94" t="n">
         <v>42.58</v>
       </c>
-      <c r="E5" s="94" t="n">
+      <c r="G5" s="94" t="n">
         <v>38.88</v>
       </c>
-      <c r="F5" s="94" t="n">
+      <c r="H5" s="94" t="n">
         <v>9.85</v>
       </c>
-      <c r="G5" s="94" t="n">
+      <c r="I5" s="94" t="n">
         <v>16.11</v>
       </c>
-      <c r="H5" s="94" t="n">
+      <c r="J5" s="94" t="n">
         <v>41.34</v>
       </c>
-      <c r="I5" s="94" t="n">
+      <c r="K5" s="94" t="n">
         <v>23.32</v>
       </c>
-      <c r="J5" s="94" t="n">
+      <c r="L5" s="94" t="n">
         <v>24.6</v>
       </c>
-      <c r="K5" s="94" t="n">
+      <c r="M5" s="94" t="n">
         <v>24.63</v>
       </c>
-      <c r="L5" s="94" t="n">
+      <c r="N5" s="94" t="n">
         <v>16.35</v>
       </c>
-      <c r="M5" s="94" t="n">
+      <c r="O5" s="94" t="n">
         <v>16.35</v>
       </c>
-      <c r="N5" s="94" t="n">
+      <c r="P5" s="94" t="n">
         <v>43.2</v>
       </c>
-      <c r="O5" s="94" t="n">
+      <c r="Q5" s="94" t="n">
         <v>76.29000000000001</v>
       </c>
-      <c r="P5" s="94" t="n">
+      <c r="R5" s="94" t="n">
         <v>84.51000000000001</v>
       </c>
-      <c r="Q5" s="94" t="n">
+      <c r="S5" s="94" t="n">
         <v>83.2</v>
       </c>
-      <c r="R5" s="94" t="n">
+      <c r="T5" s="94" t="n">
         <v>81.28</v>
       </c>
-      <c r="S5" s="94" t="n">
+      <c r="U5" s="94" t="n">
         <v>81.28</v>
       </c>
-      <c r="T5" s="94" t="n">
+      <c r="V5" s="94" t="n">
         <v>36.47</v>
       </c>
-      <c r="U5" s="94" t="n">
+      <c r="W5" s="94" t="n">
         <v>55.76</v>
       </c>
-      <c r="V5" s="94" t="n">
+      <c r="X5" s="94" t="n">
         <v>70.7</v>
       </c>
-      <c r="W5" s="94" t="n">
+      <c r="Y5" s="94" t="n">
         <v>57.61</v>
       </c>
-      <c r="X5" s="94" t="n">
+      <c r="Z5" s="94" t="n">
         <v>66.93000000000001</v>
       </c>
-      <c r="Y5" s="94" t="n">
+      <c r="AA5" s="94" t="n">
         <v>66.93000000000001</v>
       </c>
-      <c r="Z5" s="94" t="n">
+      <c r="AB5" s="94" t="n">
         <v>78.22</v>
       </c>
-      <c r="AA5" s="94" t="n">
+      <c r="AC5" s="94" t="n">
         <v>55.12</v>
       </c>
-      <c r="AB5" s="94" t="n">
+      <c r="AD5" s="94" t="n">
         <v>33.93</v>
       </c>
-      <c r="AC5" s="94" t="n">
+      <c r="AE5" s="94" t="n">
         <v>24.13</v>
-      </c>
-      <c r="AD5" s="94" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="AE5" s="94" t="n">
-        <v>25.5</v>
       </c>
     </row>
     <row r="6">
@@ -6947,152 +6946,152 @@
       </c>
       <c r="B6" s="91" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C6" s="92" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C6" s="91" t="inlineStr">
+      <c r="D6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D6" s="91" t="inlineStr">
+      <c r="E6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E6" s="91" t="inlineStr">
+      <c r="F6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F6" s="91" t="inlineStr">
+      <c r="G6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G6" s="91" t="inlineStr">
+      <c r="H6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H6" s="91" t="inlineStr">
+      <c r="I6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I6" s="92" t="inlineStr">
+      <c r="J6" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K6" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J6" s="92" t="inlineStr">
+      <c r="L6" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K6" s="92" t="inlineStr">
+      <c r="M6" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L6" s="92" t="inlineStr">
+      <c r="N6" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M6" s="92" t="inlineStr">
+      <c r="O6" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N6" s="92" t="inlineStr">
+      <c r="P6" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O6" s="92" t="inlineStr">
+      <c r="Q6" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P6" s="93" t="inlineStr">
+      <c r="R6" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q6" s="92" t="inlineStr">
+      <c r="S6" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R6" s="91" t="inlineStr">
+      <c r="T6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S6" s="91" t="inlineStr">
+      <c r="U6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T6" s="92" t="inlineStr">
+      <c r="V6" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U6" s="91" t="inlineStr">
+      <c r="W6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V6" s="91" t="inlineStr">
+      <c r="X6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W6" s="91" t="inlineStr">
+      <c r="Y6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X6" s="91" t="inlineStr">
+      <c r="Z6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y6" s="91" t="inlineStr">
+      <c r="AA6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z6" s="93" t="inlineStr">
+      <c r="AB6" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA6" s="91" t="inlineStr">
+      <c r="AC6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB6" s="91" t="inlineStr">
+      <c r="AD6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC6" s="92" t="inlineStr">
+      <c r="AE6" s="91" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AD6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -7103,94 +7102,94 @@
         </is>
       </c>
       <c r="B7" s="94" t="n">
-        <v>2.95</v>
+        <v>-1.08</v>
       </c>
       <c r="C7" s="94" t="n">
         <v>2.95</v>
       </c>
       <c r="D7" s="94" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E7" s="94" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F7" s="94" t="n">
         <v>0.21</v>
       </c>
-      <c r="E7" s="94" t="n">
+      <c r="G7" s="94" t="n">
         <v>0.57</v>
       </c>
-      <c r="F7" s="94" t="n">
+      <c r="H7" s="94" t="n">
         <v>-0.42</v>
       </c>
-      <c r="G7" s="94" t="n">
+      <c r="I7" s="94" t="n">
         <v>1.19</v>
       </c>
-      <c r="H7" s="94" t="n">
+      <c r="J7" s="94" t="n">
         <v>2.62</v>
       </c>
-      <c r="I7" s="94" t="n">
+      <c r="K7" s="94" t="n">
         <v>3.05</v>
       </c>
-      <c r="J7" s="94" t="n">
+      <c r="L7" s="94" t="n">
         <v>2.03</v>
       </c>
-      <c r="K7" s="94" t="n">
+      <c r="M7" s="94" t="n">
         <v>5.33</v>
       </c>
-      <c r="L7" s="94" t="n">
+      <c r="N7" s="94" t="n">
         <v>6.25</v>
       </c>
-      <c r="M7" s="94" t="n">
+      <c r="O7" s="94" t="n">
         <v>6.25</v>
       </c>
-      <c r="N7" s="94" t="n">
+      <c r="P7" s="94" t="n">
         <v>10.08</v>
       </c>
-      <c r="O7" s="94" t="n">
+      <c r="Q7" s="94" t="n">
         <v>10.42</v>
       </c>
-      <c r="P7" s="94" t="n">
+      <c r="R7" s="94" t="n">
         <v>10.11</v>
       </c>
-      <c r="Q7" s="94" t="n">
+      <c r="S7" s="94" t="n">
         <v>7.15</v>
       </c>
-      <c r="R7" s="94" t="n">
+      <c r="T7" s="94" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="S7" s="94" t="n">
+      <c r="U7" s="94" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="T7" s="94" t="n">
+      <c r="V7" s="94" t="n">
         <v>5.82</v>
       </c>
-      <c r="U7" s="94" t="n">
+      <c r="W7" s="94" t="n">
         <v>8.9</v>
       </c>
-      <c r="V7" s="94" t="n">
+      <c r="X7" s="94" t="n">
         <v>8.51</v>
       </c>
-      <c r="W7" s="94" t="n">
+      <c r="Y7" s="94" t="n">
         <v>10.31</v>
       </c>
-      <c r="X7" s="94" t="n">
+      <c r="Z7" s="94" t="n">
         <v>10.83</v>
       </c>
-      <c r="Y7" s="94" t="n">
+      <c r="AA7" s="94" t="n">
         <v>10.83</v>
       </c>
-      <c r="Z7" s="94" t="n">
+      <c r="AB7" s="94" t="n">
         <v>11.57</v>
       </c>
-      <c r="AA7" s="94" t="n">
+      <c r="AC7" s="94" t="n">
         <v>6.7</v>
       </c>
-      <c r="AB7" s="94" t="n">
+      <c r="AD7" s="94" t="n">
         <v>7.27</v>
       </c>
-      <c r="AC7" s="94" t="n">
+      <c r="AE7" s="94" t="n">
         <v>8</v>
-      </c>
-      <c r="AD7" s="94" t="n">
-        <v>9.42</v>
-      </c>
-      <c r="AE7" s="94" t="n">
-        <v>9.42</v>
       </c>
     </row>
     <row r="8">
@@ -7200,191 +7199,191 @@
         </is>
       </c>
       <c r="B8" s="94" t="n">
-        <v>-0.58</v>
+        <v>-5.29</v>
       </c>
       <c r="C8" s="94" t="n">
         <v>-0.58</v>
       </c>
       <c r="D8" s="94" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E8" s="94" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="F8" s="94" t="n">
         <v>17.24</v>
       </c>
-      <c r="E8" s="94" t="n">
+      <c r="G8" s="94" t="n">
         <v>38.43</v>
       </c>
-      <c r="F8" s="94" t="n">
+      <c r="H8" s="94" t="n">
         <v>47.55</v>
       </c>
-      <c r="G8" s="94" t="n">
+      <c r="I8" s="94" t="n">
         <v>54.27</v>
       </c>
-      <c r="H8" s="94" t="n">
+      <c r="J8" s="94" t="n">
         <v>56</v>
       </c>
-      <c r="I8" s="94" t="n">
+      <c r="K8" s="94" t="n">
         <v>60.03</v>
       </c>
-      <c r="J8" s="94" t="n">
+      <c r="L8" s="94" t="n">
         <v>59.12</v>
       </c>
-      <c r="K8" s="94" t="n">
+      <c r="M8" s="94" t="n">
         <v>60.55</v>
       </c>
-      <c r="L8" s="94" t="n">
+      <c r="N8" s="94" t="n">
         <v>61.09</v>
       </c>
-      <c r="M8" s="94" t="n">
+      <c r="O8" s="94" t="n">
         <v>61.09</v>
       </c>
-      <c r="N8" s="94" t="n">
+      <c r="P8" s="94" t="n">
         <v>62.55</v>
       </c>
-      <c r="O8" s="94" t="n">
+      <c r="Q8" s="94" t="n">
         <v>63.46</v>
       </c>
-      <c r="P8" s="94" t="n">
+      <c r="R8" s="94" t="n">
         <v>64.05</v>
       </c>
-      <c r="Q8" s="94" t="n">
+      <c r="S8" s="94" t="n">
         <v>64.12</v>
       </c>
-      <c r="R8" s="94" t="n">
+      <c r="T8" s="94" t="n">
         <v>66.14</v>
       </c>
-      <c r="S8" s="94" t="n">
+      <c r="U8" s="94" t="n">
         <v>66.14</v>
       </c>
-      <c r="T8" s="94" t="n">
+      <c r="V8" s="94" t="n">
         <v>61.5</v>
       </c>
-      <c r="U8" s="94" t="n">
+      <c r="W8" s="94" t="n">
         <v>62.78</v>
       </c>
-      <c r="V8" s="94" t="n">
+      <c r="X8" s="94" t="n">
         <v>63.73</v>
       </c>
-      <c r="W8" s="94" t="n">
+      <c r="Y8" s="94" t="n">
         <v>63.74</v>
       </c>
-      <c r="X8" s="94" t="n">
+      <c r="Z8" s="94" t="n">
         <v>65.31</v>
       </c>
-      <c r="Y8" s="94" t="n">
+      <c r="AA8" s="94" t="n">
         <v>65.31</v>
       </c>
-      <c r="Z8" s="94" t="n">
+      <c r="AB8" s="94" t="n">
         <v>61.57</v>
       </c>
-      <c r="AA8" s="94" t="n">
+      <c r="AC8" s="94" t="n">
         <v>59.48</v>
       </c>
-      <c r="AB8" s="94" t="n">
+      <c r="AD8" s="94" t="n">
         <v>61</v>
       </c>
-      <c r="AC8" s="94" t="n">
+      <c r="AE8" s="94" t="n">
         <v>57.54</v>
       </c>
-      <c r="AD8" s="94" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="AE8" s="94" t="n">
-        <v>58.07</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="76" t="inlineStr">
+      <c r="A9" s="95" t="inlineStr">
         <is>
           <t>kc:RS5</t>
         </is>
       </c>
       <c r="B9" s="94" t="n">
-        <v>22.95</v>
+        <v>6.02</v>
       </c>
       <c r="C9" s="94" t="n">
         <v>22.95</v>
       </c>
       <c r="D9" s="94" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="E9" s="94" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="F9" s="94" t="n">
         <v>26.81</v>
       </c>
-      <c r="E9" s="94" t="n">
+      <c r="G9" s="94" t="n">
         <v>28.13</v>
       </c>
-      <c r="F9" s="94" t="n">
+      <c r="H9" s="94" t="n">
         <v>25.11</v>
       </c>
-      <c r="G9" s="94" t="n">
+      <c r="I9" s="94" t="n">
         <v>29.08</v>
       </c>
-      <c r="H9" s="94" t="n">
+      <c r="J9" s="94" t="n">
         <v>36.65</v>
       </c>
-      <c r="I9" s="94" t="n">
+      <c r="K9" s="94" t="n">
         <v>19.14</v>
       </c>
-      <c r="J9" s="94" t="n">
+      <c r="L9" s="94" t="n">
         <v>20.17</v>
       </c>
-      <c r="K9" s="94" t="n">
+      <c r="M9" s="94" t="n">
         <v>26.21</v>
       </c>
-      <c r="L9" s="94" t="n">
+      <c r="N9" s="94" t="n">
         <v>22.22</v>
       </c>
-      <c r="M9" s="94" t="n">
+      <c r="O9" s="94" t="n">
         <v>22.22</v>
       </c>
-      <c r="N9" s="94" t="n">
+      <c r="P9" s="94" t="n">
         <v>32.22</v>
       </c>
-      <c r="O9" s="94" t="n">
+      <c r="Q9" s="94" t="n">
         <v>40.27</v>
       </c>
-      <c r="P9" s="94" t="n">
+      <c r="R9" s="94" t="n">
         <v>51.11</v>
       </c>
-      <c r="Q9" s="94" t="n">
+      <c r="S9" s="94" t="n">
         <v>45.03</v>
       </c>
-      <c r="R9" s="94" t="n">
+      <c r="T9" s="94" t="n">
         <v>48.61</v>
       </c>
-      <c r="S9" s="94" t="n">
+      <c r="U9" s="94" t="n">
         <v>48.61</v>
       </c>
-      <c r="T9" s="94" t="n">
+      <c r="V9" s="94" t="n">
         <v>32.49</v>
       </c>
-      <c r="U9" s="94" t="n">
+      <c r="W9" s="94" t="n">
         <v>47.34</v>
       </c>
-      <c r="V9" s="94" t="n">
+      <c r="X9" s="94" t="n">
         <v>54.26</v>
       </c>
-      <c r="W9" s="94" t="n">
+      <c r="Y9" s="94" t="n">
         <v>58</v>
       </c>
-      <c r="X9" s="94" t="n">
+      <c r="Z9" s="94" t="n">
         <v>59.83</v>
       </c>
-      <c r="Y9" s="94" t="n">
+      <c r="AA9" s="94" t="n">
         <v>59.83</v>
       </c>
-      <c r="Z9" s="94" t="n">
+      <c r="AB9" s="94" t="n">
         <v>69.86</v>
       </c>
-      <c r="AA9" s="94" t="n">
+      <c r="AC9" s="94" t="n">
         <v>52.7</v>
       </c>
-      <c r="AB9" s="94" t="n">
+      <c r="AD9" s="94" t="n">
         <v>50.83</v>
       </c>
-      <c r="AC9" s="94" t="n">
+      <c r="AE9" s="94" t="n">
         <v>39.77</v>
-      </c>
-      <c r="AD9" s="94" t="n">
-        <v>47.44</v>
-      </c>
-      <c r="AE9" s="94" t="n">
-        <v>47.44</v>
       </c>
     </row>
     <row r="10">
@@ -7393,252 +7392,252 @@
           <t>cy:EIDE</t>
         </is>
       </c>
-      <c r="B10" s="92" t="inlineStr">
+      <c r="B10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C10" s="92" t="inlineStr">
+      <c r="C10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
       <c r="D10" s="91" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E10" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F10" s="92" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E10" s="92" t="inlineStr">
+      <c r="G10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F10" s="92" t="inlineStr">
+      <c r="H10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G10" s="92" t="inlineStr">
+      <c r="I10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H10" s="91" t="inlineStr">
+      <c r="J10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I10" s="92" t="inlineStr">
+      <c r="K10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J10" s="92" t="inlineStr">
+      <c r="L10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K10" s="92" t="inlineStr">
+      <c r="M10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L10" s="92" t="inlineStr">
+      <c r="N10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M10" s="92" t="inlineStr">
+      <c r="O10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N10" s="92" t="inlineStr">
+      <c r="P10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O10" s="93" t="inlineStr">
+      <c r="Q10" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P10" s="93" t="inlineStr">
+      <c r="R10" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q10" s="93" t="inlineStr">
+      <c r="S10" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R10" s="93" t="inlineStr">
+      <c r="T10" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S10" s="93" t="inlineStr">
+      <c r="U10" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T10" s="92" t="inlineStr">
+      <c r="V10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U10" s="92" t="inlineStr">
+      <c r="W10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V10" s="92" t="inlineStr">
+      <c r="X10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W10" s="92" t="inlineStr">
+      <c r="Y10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X10" s="92" t="inlineStr">
+      <c r="Z10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y10" s="92" t="inlineStr">
+      <c r="AA10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z10" s="93" t="inlineStr">
+      <c r="AB10" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA10" s="92" t="inlineStr">
+      <c r="AC10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB10" s="92" t="inlineStr">
+      <c r="AD10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC10" s="92" t="inlineStr">
+      <c r="AE10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD10" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE10" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="76" t="inlineStr">
+      <c r="A11" s="95" t="inlineStr">
         <is>
           <t>cy:RNG60</t>
         </is>
       </c>
       <c r="B11" s="94" t="n">
-        <v>-3.56</v>
+        <v>-10.01</v>
       </c>
       <c r="C11" s="94" t="n">
         <v>-3.56</v>
       </c>
       <c r="D11" s="94" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="E11" s="94" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="F11" s="94" t="n">
         <v>-4.61</v>
       </c>
-      <c r="E11" s="94" t="n">
+      <c r="G11" s="94" t="n">
         <v>-4.67</v>
       </c>
-      <c r="F11" s="94" t="n">
+      <c r="H11" s="94" t="n">
         <v>-4.8</v>
       </c>
-      <c r="G11" s="94" t="n">
+      <c r="I11" s="94" t="n">
         <v>-3.32</v>
       </c>
-      <c r="H11" s="94" t="n">
+      <c r="J11" s="94" t="n">
         <v>-3.09</v>
       </c>
-      <c r="I11" s="94" t="n">
+      <c r="K11" s="94" t="n">
         <v>-2.2</v>
       </c>
-      <c r="J11" s="94" t="n">
+      <c r="L11" s="94" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K11" s="94" t="n">
+      <c r="M11" s="94" t="n">
         <v>-2.76</v>
       </c>
-      <c r="L11" s="94" t="n">
+      <c r="N11" s="94" t="n">
         <v>-2.26</v>
       </c>
-      <c r="M11" s="94" t="n">
+      <c r="O11" s="94" t="n">
         <v>-2.26</v>
       </c>
-      <c r="N11" s="94" t="n">
+      <c r="P11" s="94" t="n">
         <v>-0.05</v>
       </c>
-      <c r="O11" s="94" t="n">
+      <c r="Q11" s="94" t="n">
         <v>0.95</v>
       </c>
-      <c r="P11" s="94" t="n">
+      <c r="R11" s="94" t="n">
         <v>-0.3</v>
       </c>
-      <c r="Q11" s="94" t="n">
+      <c r="S11" s="94" t="n">
         <v>-3.36</v>
       </c>
-      <c r="R11" s="94" t="n">
+      <c r="T11" s="94" t="n">
         <v>-1.54</v>
       </c>
-      <c r="S11" s="94" t="n">
+      <c r="U11" s="94" t="n">
         <v>-1.54</v>
       </c>
-      <c r="T11" s="94" t="n">
+      <c r="V11" s="94" t="n">
         <v>-4.33</v>
       </c>
-      <c r="U11" s="94" t="n">
+      <c r="W11" s="94" t="n">
         <v>-2.55</v>
       </c>
-      <c r="V11" s="94" t="n">
+      <c r="X11" s="94" t="n">
         <v>-2.78</v>
       </c>
-      <c r="W11" s="94" t="n">
+      <c r="Y11" s="94" t="n">
         <v>-0.97</v>
       </c>
-      <c r="X11" s="94" t="n">
+      <c r="Z11" s="94" t="n">
         <v>-0.37</v>
       </c>
-      <c r="Y11" s="94" t="n">
+      <c r="AA11" s="94" t="n">
         <v>-0.37</v>
       </c>
-      <c r="Z11" s="94" t="n">
+      <c r="AB11" s="94" t="n">
         <v>-0.48</v>
       </c>
-      <c r="AA11" s="94" t="n">
+      <c r="AC11" s="94" t="n">
         <v>-2.89</v>
       </c>
-      <c r="AB11" s="94" t="n">
+      <c r="AD11" s="94" t="n">
         <v>-1.53</v>
       </c>
-      <c r="AC11" s="94" t="n">
+      <c r="AE11" s="94" t="n">
         <v>1.23</v>
-      </c>
-      <c r="AD11" s="94" t="n">
-        <v>-1.74</v>
-      </c>
-      <c r="AE11" s="94" t="n">
-        <v>-1.74</v>
       </c>
     </row>
     <row r="12">
@@ -7648,191 +7647,191 @@
         </is>
       </c>
       <c r="B12" s="94" t="n">
-        <v>-19.01</v>
+        <v>-18.68</v>
       </c>
       <c r="C12" s="94" t="n">
         <v>-19.01</v>
       </c>
       <c r="D12" s="94" t="n">
+        <v>-19.01</v>
+      </c>
+      <c r="E12" s="94" t="n">
+        <v>-19.01</v>
+      </c>
+      <c r="F12" s="94" t="n">
         <v>-3.24</v>
       </c>
-      <c r="E12" s="94" t="n">
+      <c r="G12" s="94" t="n">
         <v>11.48</v>
       </c>
-      <c r="F12" s="94" t="n">
+      <c r="H12" s="94" t="n">
         <v>22.73</v>
       </c>
-      <c r="G12" s="94" t="n">
+      <c r="I12" s="94" t="n">
         <v>29.65</v>
       </c>
-      <c r="H12" s="94" t="n">
+      <c r="J12" s="94" t="n">
         <v>32.8</v>
       </c>
-      <c r="I12" s="94" t="n">
+      <c r="K12" s="94" t="n">
         <v>39.82</v>
       </c>
-      <c r="J12" s="94" t="n">
+      <c r="L12" s="94" t="n">
         <v>39.63</v>
       </c>
-      <c r="K12" s="94" t="n">
+      <c r="M12" s="94" t="n">
         <v>39.19</v>
       </c>
-      <c r="L12" s="94" t="n">
+      <c r="N12" s="94" t="n">
         <v>40.35</v>
       </c>
-      <c r="M12" s="94" t="n">
+      <c r="O12" s="94" t="n">
         <v>40.35</v>
       </c>
-      <c r="N12" s="94" t="n">
+      <c r="P12" s="94" t="n">
         <v>43.31</v>
       </c>
-      <c r="O12" s="94" t="n">
+      <c r="Q12" s="94" t="n">
         <v>43.21</v>
       </c>
-      <c r="P12" s="94" t="n">
+      <c r="R12" s="94" t="n">
         <v>43.01</v>
       </c>
-      <c r="Q12" s="94" t="n">
+      <c r="S12" s="94" t="n">
         <v>43.84</v>
       </c>
-      <c r="R12" s="94" t="n">
+      <c r="T12" s="94" t="n">
         <v>44.68</v>
       </c>
-      <c r="S12" s="94" t="n">
+      <c r="U12" s="94" t="n">
         <v>44.68</v>
       </c>
-      <c r="T12" s="94" t="n">
+      <c r="V12" s="94" t="n">
         <v>40.83</v>
       </c>
-      <c r="U12" s="94" t="n">
+      <c r="W12" s="94" t="n">
         <v>40.04</v>
       </c>
-      <c r="V12" s="94" t="n">
+      <c r="X12" s="94" t="n">
         <v>41.77</v>
       </c>
-      <c r="W12" s="94" t="n">
+      <c r="Y12" s="94" t="n">
         <v>41.35</v>
       </c>
-      <c r="X12" s="94" t="n">
+      <c r="Z12" s="94" t="n">
         <v>43.49</v>
       </c>
-      <c r="Y12" s="94" t="n">
+      <c r="AA12" s="94" t="n">
         <v>43.49</v>
       </c>
-      <c r="Z12" s="94" t="n">
+      <c r="AB12" s="94" t="n">
         <v>41.39</v>
       </c>
-      <c r="AA12" s="94" t="n">
+      <c r="AC12" s="94" t="n">
         <v>42.1</v>
       </c>
-      <c r="AB12" s="94" t="n">
+      <c r="AD12" s="94" t="n">
         <v>43.01</v>
       </c>
-      <c r="AC12" s="94" t="n">
+      <c r="AE12" s="94" t="n">
         <v>43.49</v>
       </c>
-      <c r="AD12" s="94" t="n">
-        <v>40.45</v>
-      </c>
-      <c r="AE12" s="94" t="n">
-        <v>40.45</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="76" t="inlineStr">
+      <c r="A13" s="95" t="inlineStr">
         <is>
           <t>cy:RS3</t>
         </is>
       </c>
       <c r="B13" s="94" t="n">
-        <v>5.09</v>
+        <v>0.77</v>
       </c>
       <c r="C13" s="94" t="n">
         <v>5.09</v>
       </c>
       <c r="D13" s="94" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="E13" s="94" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="F13" s="94" t="n">
         <v>16.8</v>
       </c>
-      <c r="E13" s="94" t="n">
+      <c r="G13" s="94" t="n">
         <v>6.77</v>
       </c>
-      <c r="F13" s="94" t="n">
+      <c r="H13" s="94" t="n">
         <v>7.15</v>
       </c>
-      <c r="G13" s="94" t="n">
+      <c r="I13" s="94" t="n">
         <v>14.43</v>
       </c>
-      <c r="H13" s="94" t="n">
+      <c r="J13" s="94" t="n">
         <v>27.11</v>
       </c>
-      <c r="I13" s="94" t="n">
+      <c r="K13" s="94" t="n">
         <v>11.06</v>
       </c>
-      <c r="J13" s="94" t="n">
+      <c r="L13" s="94" t="n">
         <v>13.13</v>
       </c>
-      <c r="K13" s="94" t="n">
+      <c r="M13" s="94" t="n">
         <v>15.59</v>
       </c>
-      <c r="L13" s="94" t="n">
+      <c r="N13" s="94" t="n">
         <v>15.18</v>
       </c>
-      <c r="M13" s="94" t="n">
+      <c r="O13" s="94" t="n">
         <v>15.18</v>
       </c>
-      <c r="N13" s="94" t="n">
+      <c r="P13" s="94" t="n">
         <v>34.95</v>
       </c>
-      <c r="O13" s="94" t="n">
+      <c r="Q13" s="94" t="n">
         <v>58.81</v>
       </c>
-      <c r="P13" s="94" t="n">
+      <c r="R13" s="94" t="n">
         <v>67.45999999999999</v>
       </c>
-      <c r="Q13" s="94" t="n">
+      <c r="S13" s="94" t="n">
         <v>58.78</v>
       </c>
-      <c r="R13" s="94" t="n">
+      <c r="T13" s="94" t="n">
         <v>69.37</v>
       </c>
-      <c r="S13" s="94" t="n">
+      <c r="U13" s="94" t="n">
         <v>69.37</v>
       </c>
-      <c r="T13" s="94" t="n">
+      <c r="V13" s="94" t="n">
         <v>17.41</v>
       </c>
-      <c r="U13" s="94" t="n">
+      <c r="W13" s="94" t="n">
         <v>32.88</v>
       </c>
-      <c r="V13" s="94" t="n">
+      <c r="X13" s="94" t="n">
         <v>46.93</v>
       </c>
-      <c r="W13" s="94" t="n">
+      <c r="Y13" s="94" t="n">
         <v>41.51</v>
       </c>
-      <c r="X13" s="94" t="n">
+      <c r="Z13" s="94" t="n">
         <v>45.57</v>
       </c>
-      <c r="Y13" s="94" t="n">
+      <c r="AA13" s="94" t="n">
         <v>45.57</v>
       </c>
-      <c r="Z13" s="94" t="n">
+      <c r="AB13" s="94" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="AA13" s="94" t="n">
+      <c r="AC13" s="94" t="n">
         <v>34.52</v>
       </c>
-      <c r="AB13" s="94" t="n">
+      <c r="AD13" s="94" t="n">
         <v>34.18</v>
       </c>
-      <c r="AC13" s="94" t="n">
+      <c r="AE13" s="94" t="n">
         <v>37.1</v>
-      </c>
-      <c r="AD13" s="94" t="n">
-        <v>18.22</v>
-      </c>
-      <c r="AE13" s="94" t="n">
-        <v>18.22</v>
       </c>
     </row>
     <row r="14">
@@ -7841,252 +7840,252 @@
           <t>hk50:EIDE</t>
         </is>
       </c>
-      <c r="B14" s="92" t="inlineStr">
+      <c r="B14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C14" s="92" t="inlineStr">
+      <c r="C14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
       <c r="D14" s="91" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E14" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F14" s="92" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E14" s="91" t="inlineStr">
+      <c r="G14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F14" s="92" t="inlineStr">
+      <c r="H14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G14" s="92" t="inlineStr">
+      <c r="I14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H14" s="92" t="inlineStr">
+      <c r="J14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I14" s="92" t="inlineStr">
+      <c r="K14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J14" s="92" t="inlineStr">
+      <c r="L14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K14" s="92" t="inlineStr">
+      <c r="M14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L14" s="92" t="inlineStr">
+      <c r="N14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M14" s="92" t="inlineStr">
+      <c r="O14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N14" s="91" t="inlineStr">
+      <c r="P14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O14" s="93" t="inlineStr">
+      <c r="Q14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P14" s="93" t="inlineStr">
+      <c r="R14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q14" s="93" t="inlineStr">
+      <c r="S14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R14" s="93" t="inlineStr">
+      <c r="T14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S14" s="93" t="inlineStr">
+      <c r="U14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T14" s="91" t="inlineStr">
+      <c r="V14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U14" s="91" t="inlineStr">
+      <c r="W14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V14" s="91" t="inlineStr">
+      <c r="X14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W14" s="91" t="inlineStr">
+      <c r="Y14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X14" s="93" t="inlineStr">
+      <c r="Z14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y14" s="93" t="inlineStr">
+      <c r="AA14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z14" s="93" t="inlineStr">
+      <c r="AB14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA14" s="93" t="inlineStr">
+      <c r="AC14" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB14" s="91" t="inlineStr">
+      <c r="AD14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC14" s="91" t="inlineStr">
+      <c r="AE14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="95" t="inlineStr">
+      <c r="A15" s="76" t="inlineStr">
         <is>
           <t>hk50:RNG60</t>
         </is>
       </c>
       <c r="B15" s="94" t="n">
-        <v>16.06</v>
+        <v>5.7</v>
       </c>
       <c r="C15" s="94" t="n">
         <v>16.06</v>
       </c>
       <c r="D15" s="94" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="E15" s="94" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="F15" s="94" t="n">
         <v>17.42</v>
       </c>
-      <c r="E15" s="94" t="n">
+      <c r="G15" s="94" t="n">
         <v>18.26</v>
       </c>
-      <c r="F15" s="94" t="n">
+      <c r="H15" s="94" t="n">
         <v>15.25</v>
       </c>
-      <c r="G15" s="94" t="n">
+      <c r="I15" s="94" t="n">
         <v>16.89</v>
       </c>
-      <c r="H15" s="94" t="n">
+      <c r="J15" s="94" t="n">
         <v>17.36</v>
       </c>
-      <c r="I15" s="94" t="n">
+      <c r="K15" s="94" t="n">
         <v>16.84</v>
       </c>
-      <c r="J15" s="94" t="n">
+      <c r="L15" s="94" t="n">
         <v>17.41</v>
       </c>
-      <c r="K15" s="94" t="n">
+      <c r="M15" s="94" t="n">
         <v>21.22</v>
       </c>
-      <c r="L15" s="94" t="n">
+      <c r="N15" s="94" t="n">
         <v>19.93</v>
       </c>
-      <c r="M15" s="94" t="n">
+      <c r="O15" s="94" t="n">
         <v>19.93</v>
       </c>
-      <c r="N15" s="94" t="n">
+      <c r="P15" s="94" t="n">
         <v>21.93</v>
       </c>
-      <c r="O15" s="94" t="n">
+      <c r="Q15" s="94" t="n">
         <v>25.74</v>
       </c>
-      <c r="P15" s="94" t="n">
+      <c r="R15" s="94" t="n">
         <v>24.98</v>
       </c>
-      <c r="Q15" s="94" t="n">
+      <c r="S15" s="94" t="n">
         <v>20.9</v>
       </c>
-      <c r="R15" s="94" t="n">
+      <c r="T15" s="94" t="n">
         <v>17.47</v>
       </c>
-      <c r="S15" s="94" t="n">
+      <c r="U15" s="94" t="n">
         <v>17.47</v>
       </c>
-      <c r="T15" s="94" t="n">
+      <c r="V15" s="94" t="n">
         <v>16.41</v>
       </c>
-      <c r="U15" s="94" t="n">
+      <c r="W15" s="94" t="n">
         <v>16.19</v>
       </c>
-      <c r="V15" s="94" t="n">
+      <c r="X15" s="94" t="n">
         <v>16.5</v>
       </c>
-      <c r="W15" s="94" t="n">
+      <c r="Y15" s="94" t="n">
         <v>19.72</v>
       </c>
-      <c r="X15" s="94" t="n">
+      <c r="Z15" s="94" t="n">
         <v>23.88</v>
       </c>
-      <c r="Y15" s="94" t="n">
+      <c r="AA15" s="94" t="n">
         <v>23.88</v>
       </c>
-      <c r="Z15" s="94" t="n">
+      <c r="AB15" s="94" t="n">
         <v>23.44</v>
       </c>
-      <c r="AA15" s="94" t="n">
+      <c r="AC15" s="94" t="n">
         <v>19.49</v>
       </c>
-      <c r="AB15" s="94" t="n">
+      <c r="AD15" s="94" t="n">
         <v>17.35</v>
       </c>
-      <c r="AC15" s="94" t="n">
+      <c r="AE15" s="94" t="n">
         <v>18.44</v>
-      </c>
-      <c r="AD15" s="94" t="n">
-        <v>18.46</v>
-      </c>
-      <c r="AE15" s="94" t="n">
-        <v>18.46</v>
       </c>
     </row>
     <row r="16">
@@ -8096,191 +8095,191 @@
         </is>
       </c>
       <c r="B16" s="94" t="n">
-        <v>9.19</v>
+        <v>-0.4</v>
       </c>
       <c r="C16" s="94" t="n">
         <v>9.19</v>
       </c>
       <c r="D16" s="94" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="E16" s="94" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="F16" s="94" t="n">
         <v>0.44</v>
       </c>
-      <c r="E16" s="94" t="n">
+      <c r="G16" s="94" t="n">
         <v>2.07</v>
       </c>
-      <c r="F16" s="94" t="n">
+      <c r="H16" s="94" t="n">
         <v>4.55</v>
       </c>
-      <c r="G16" s="94" t="n">
+      <c r="I16" s="94" t="n">
         <v>4.38</v>
       </c>
-      <c r="H16" s="94" t="n">
+      <c r="J16" s="94" t="n">
         <v>11.57</v>
       </c>
-      <c r="I16" s="94" t="n">
+      <c r="K16" s="94" t="n">
         <v>13.82</v>
       </c>
-      <c r="J16" s="94" t="n">
+      <c r="L16" s="94" t="n">
         <v>17.16</v>
       </c>
-      <c r="K16" s="94" t="n">
+      <c r="M16" s="94" t="n">
         <v>24.97</v>
       </c>
-      <c r="L16" s="94" t="n">
+      <c r="N16" s="94" t="n">
         <v>24.68</v>
       </c>
-      <c r="M16" s="94" t="n">
+      <c r="O16" s="94" t="n">
         <v>24.68</v>
       </c>
-      <c r="N16" s="94" t="n">
+      <c r="P16" s="94" t="n">
         <v>32.73</v>
       </c>
-      <c r="O16" s="94" t="n">
+      <c r="Q16" s="94" t="n">
         <v>35.67</v>
       </c>
-      <c r="P16" s="94" t="n">
+      <c r="R16" s="94" t="n">
         <v>37.35</v>
       </c>
-      <c r="Q16" s="94" t="n">
+      <c r="S16" s="94" t="n">
         <v>36.72</v>
       </c>
-      <c r="R16" s="94" t="n">
+      <c r="T16" s="94" t="n">
         <v>37.53</v>
       </c>
-      <c r="S16" s="94" t="n">
+      <c r="U16" s="94" t="n">
         <v>37.53</v>
       </c>
-      <c r="T16" s="94" t="n">
+      <c r="V16" s="94" t="n">
         <v>35.08</v>
       </c>
-      <c r="U16" s="94" t="n">
+      <c r="W16" s="94" t="n">
         <v>36.89</v>
       </c>
-      <c r="V16" s="94" t="n">
+      <c r="X16" s="94" t="n">
         <v>39.01</v>
       </c>
-      <c r="W16" s="94" t="n">
+      <c r="Y16" s="94" t="n">
         <v>38</v>
       </c>
-      <c r="X16" s="94" t="n">
+      <c r="Z16" s="94" t="n">
         <v>40.9</v>
       </c>
-      <c r="Y16" s="94" t="n">
+      <c r="AA16" s="94" t="n">
         <v>40.9</v>
       </c>
-      <c r="Z16" s="94" t="n">
+      <c r="AB16" s="94" t="n">
         <v>39.7</v>
       </c>
-      <c r="AA16" s="94" t="n">
+      <c r="AC16" s="94" t="n">
         <v>35.15</v>
       </c>
-      <c r="AB16" s="94" t="n">
+      <c r="AD16" s="94" t="n">
         <v>29.97</v>
       </c>
-      <c r="AC16" s="94" t="n">
+      <c r="AE16" s="94" t="n">
         <v>30.04</v>
       </c>
-      <c r="AD16" s="94" t="n">
-        <v>27.53</v>
-      </c>
-      <c r="AE16" s="94" t="n">
-        <v>27.53</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="96" t="inlineStr">
+      <c r="A17" s="95" t="inlineStr">
         <is>
           <t>hk50:RS4</t>
         </is>
       </c>
       <c r="B17" s="94" t="n">
-        <v>18.53</v>
+        <v>4.01</v>
       </c>
       <c r="C17" s="94" t="n">
         <v>18.53</v>
       </c>
       <c r="D17" s="94" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="E17" s="94" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="F17" s="94" t="n">
         <v>31.84</v>
       </c>
-      <c r="E17" s="94" t="n">
+      <c r="G17" s="94" t="n">
         <v>32.06</v>
       </c>
-      <c r="F17" s="94" t="n">
+      <c r="H17" s="94" t="n">
         <v>24.45</v>
       </c>
-      <c r="G17" s="94" t="n">
+      <c r="I17" s="94" t="n">
         <v>34.7</v>
       </c>
-      <c r="H17" s="94" t="n">
+      <c r="J17" s="94" t="n">
         <v>41.1</v>
       </c>
-      <c r="I17" s="94" t="n">
+      <c r="K17" s="94" t="n">
         <v>35.5</v>
       </c>
-      <c r="J17" s="94" t="n">
+      <c r="L17" s="94" t="n">
         <v>28.03</v>
       </c>
-      <c r="K17" s="94" t="n">
+      <c r="M17" s="94" t="n">
         <v>43.16</v>
       </c>
-      <c r="L17" s="94" t="n">
+      <c r="N17" s="94" t="n">
         <v>32.68</v>
       </c>
-      <c r="M17" s="94" t="n">
+      <c r="O17" s="94" t="n">
         <v>32.68</v>
       </c>
-      <c r="N17" s="94" t="n">
+      <c r="P17" s="94" t="n">
         <v>49.51</v>
       </c>
-      <c r="O17" s="94" t="n">
+      <c r="Q17" s="94" t="n">
         <v>82.73999999999999</v>
       </c>
-      <c r="P17" s="94" t="n">
+      <c r="R17" s="94" t="n">
         <v>82.23999999999999</v>
       </c>
-      <c r="Q17" s="94" t="n">
+      <c r="S17" s="94" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="R17" s="94" t="n">
+      <c r="T17" s="94" t="n">
         <v>63.22</v>
       </c>
-      <c r="S17" s="94" t="n">
+      <c r="U17" s="94" t="n">
         <v>63.22</v>
       </c>
-      <c r="T17" s="94" t="n">
+      <c r="V17" s="94" t="n">
         <v>37.82</v>
       </c>
-      <c r="U17" s="94" t="n">
+      <c r="W17" s="94" t="n">
         <v>44.15</v>
       </c>
-      <c r="V17" s="94" t="n">
+      <c r="X17" s="94" t="n">
         <v>52.92</v>
       </c>
-      <c r="W17" s="94" t="n">
+      <c r="Y17" s="94" t="n">
         <v>52.98</v>
       </c>
-      <c r="X17" s="94" t="n">
+      <c r="Z17" s="94" t="n">
         <v>73.12</v>
       </c>
-      <c r="Y17" s="94" t="n">
+      <c r="AA17" s="94" t="n">
         <v>73.12</v>
       </c>
-      <c r="Z17" s="94" t="n">
+      <c r="AB17" s="94" t="n">
         <v>80.18000000000001</v>
       </c>
-      <c r="AA17" s="94" t="n">
+      <c r="AC17" s="94" t="n">
         <v>66.63</v>
       </c>
-      <c r="AB17" s="94" t="n">
+      <c r="AD17" s="94" t="n">
         <v>41.31</v>
       </c>
-      <c r="AC17" s="94" t="n">
+      <c r="AE17" s="94" t="n">
         <v>43.77</v>
-      </c>
-      <c r="AD17" s="94" t="n">
-        <v>41.12</v>
-      </c>
-      <c r="AE17" s="94" t="n">
-        <v>41.12</v>
       </c>
     </row>
     <row r="18">
@@ -8289,154 +8288,154 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
+      <c r="B18" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C18" s="92" t="inlineStr">
+      <c r="C18" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
       <c r="D18" s="91" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E18" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F18" s="92" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E18" s="92" t="inlineStr">
+      <c r="G18" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F18" s="92" t="inlineStr">
+      <c r="H18" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G18" s="92" t="inlineStr">
+      <c r="I18" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H18" s="92" t="inlineStr">
+      <c r="J18" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I18" s="91" t="inlineStr">
+      <c r="K18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J18" s="93" t="inlineStr">
+      <c r="L18" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K18" s="93" t="inlineStr">
+      <c r="M18" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L18" s="91" t="inlineStr">
+      <c r="N18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M18" s="91" t="inlineStr">
+      <c r="O18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N18" s="91" t="inlineStr">
+      <c r="P18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O18" s="91" t="inlineStr">
+      <c r="Q18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P18" s="91" t="inlineStr">
+      <c r="R18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q18" s="91" t="inlineStr">
+      <c r="S18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R18" s="91" t="inlineStr">
+      <c r="T18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S18" s="91" t="inlineStr">
+      <c r="U18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T18" s="92" t="inlineStr">
+      <c r="V18" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U18" s="91" t="inlineStr">
+      <c r="W18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V18" s="92" t="inlineStr">
+      <c r="X18" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W18" s="92" t="inlineStr">
+      <c r="Y18" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X18" s="91" t="inlineStr">
+      <c r="Z18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y18" s="91" t="inlineStr">
+      <c r="AA18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z18" s="92" t="inlineStr">
+      <c r="AB18" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA18" s="91" t="inlineStr">
+      <c r="AC18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB18" s="92" t="inlineStr">
+      <c r="AD18" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC18" s="92" t="inlineStr">
+      <c r="AE18" s="91" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AD18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -8450,91 +8449,91 @@
         <v>-14.13</v>
       </c>
       <c r="C19" s="94" t="n">
+        <v>-14.13</v>
+      </c>
+      <c r="D19" s="94" t="n">
+        <v>-14.13</v>
+      </c>
+      <c r="E19" s="94" t="n">
         <v>-9.69</v>
       </c>
-      <c r="D19" s="94" t="n">
+      <c r="F19" s="94" t="n">
         <v>-4.57</v>
       </c>
-      <c r="E19" s="94" t="n">
+      <c r="G19" s="94" t="n">
         <v>-4.01</v>
       </c>
-      <c r="F19" s="94" t="n">
+      <c r="H19" s="94" t="n">
         <v>-4.59</v>
       </c>
-      <c r="G19" s="94" t="n">
+      <c r="I19" s="94" t="n">
         <v>-5.52</v>
       </c>
-      <c r="H19" s="94" t="n">
+      <c r="J19" s="94" t="n">
         <v>-4.65</v>
       </c>
-      <c r="I19" s="94" t="n">
+      <c r="K19" s="94" t="n">
         <v>-5.39</v>
       </c>
-      <c r="J19" s="94" t="n">
+      <c r="L19" s="94" t="n">
         <v>-4.36</v>
       </c>
-      <c r="K19" s="94" t="n">
+      <c r="M19" s="94" t="n">
         <v>-3.46</v>
       </c>
-      <c r="L19" s="94" t="n">
+      <c r="N19" s="94" t="n">
         <v>-4.44</v>
       </c>
-      <c r="M19" s="94" t="n">
+      <c r="O19" s="94" t="n">
         <v>-4.44</v>
       </c>
-      <c r="N19" s="94" t="n">
+      <c r="P19" s="94" t="n">
         <v>-3.48</v>
       </c>
-      <c r="O19" s="94" t="n">
+      <c r="Q19" s="94" t="n">
         <v>-3.35</v>
       </c>
-      <c r="P19" s="94" t="n">
+      <c r="R19" s="94" t="n">
         <v>-7.21</v>
       </c>
-      <c r="Q19" s="94" t="n">
+      <c r="S19" s="94" t="n">
         <v>-6.57</v>
       </c>
-      <c r="R19" s="94" t="n">
+      <c r="T19" s="94" t="n">
         <v>-6.81</v>
       </c>
-      <c r="S19" s="94" t="n">
+      <c r="U19" s="94" t="n">
         <v>-6.81</v>
       </c>
-      <c r="T19" s="94" t="n">
+      <c r="V19" s="94" t="n">
         <v>-8.75</v>
       </c>
-      <c r="U19" s="94" t="n">
+      <c r="W19" s="94" t="n">
         <v>-7.97</v>
       </c>
-      <c r="V19" s="94" t="n">
+      <c r="X19" s="94" t="n">
         <v>-7.67</v>
       </c>
-      <c r="W19" s="94" t="n">
+      <c r="Y19" s="94" t="n">
         <v>-7.24</v>
       </c>
-      <c r="X19" s="94" t="n">
+      <c r="Z19" s="94" t="n">
         <v>-5.26</v>
       </c>
-      <c r="Y19" s="94" t="n">
+      <c r="AA19" s="94" t="n">
         <v>-5.26</v>
       </c>
-      <c r="Z19" s="94" t="n">
+      <c r="AB19" s="94" t="n">
         <v>-5.54</v>
       </c>
-      <c r="AA19" s="94" t="n">
+      <c r="AC19" s="94" t="n">
         <v>-4.01</v>
       </c>
-      <c r="AB19" s="94" t="n">
+      <c r="AD19" s="94" t="n">
         <v>-4.49</v>
       </c>
-      <c r="AC19" s="94" t="n">
+      <c r="AE19" s="94" t="n">
         <v>-3.26</v>
-      </c>
-      <c r="AD19" s="94" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="AE19" s="94" t="n">
-        <v>-1.29</v>
       </c>
     </row>
     <row r="20">
@@ -8547,95 +8546,95 @@
         <v>-12.21</v>
       </c>
       <c r="C20" s="94" t="n">
+        <v>-12.21</v>
+      </c>
+      <c r="D20" s="94" t="n">
+        <v>-12.21</v>
+      </c>
+      <c r="E20" s="94" t="n">
         <v>-6.83</v>
       </c>
-      <c r="D20" s="94" t="n">
+      <c r="F20" s="94" t="n">
         <v>-1.39</v>
       </c>
-      <c r="E20" s="94" t="n">
+      <c r="G20" s="94" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F20" s="94" t="n">
+      <c r="H20" s="94" t="n">
         <v>-2.42</v>
       </c>
-      <c r="G20" s="94" t="n">
+      <c r="I20" s="94" t="n">
         <v>-2.09</v>
       </c>
-      <c r="H20" s="94" t="n">
+      <c r="J20" s="94" t="n">
         <v>-0.28</v>
       </c>
-      <c r="I20" s="94" t="n">
+      <c r="K20" s="94" t="n">
         <v>0.06</v>
       </c>
-      <c r="J20" s="94" t="n">
+      <c r="L20" s="94" t="n">
         <v>0.25</v>
       </c>
-      <c r="K20" s="94" t="n">
+      <c r="M20" s="94" t="n">
         <v>0.51</v>
       </c>
-      <c r="L20" s="94" t="n">
+      <c r="N20" s="94" t="n">
         <v>-1.35</v>
       </c>
-      <c r="M20" s="94" t="n">
+      <c r="O20" s="94" t="n">
         <v>-1.35</v>
       </c>
-      <c r="N20" s="94" t="n">
+      <c r="P20" s="94" t="n">
         <v>-1.04</v>
       </c>
-      <c r="O20" s="94" t="n">
+      <c r="Q20" s="94" t="n">
         <v>-1.01</v>
       </c>
-      <c r="P20" s="94" t="n">
+      <c r="R20" s="94" t="n">
         <v>-1.82</v>
       </c>
-      <c r="Q20" s="94" t="n">
+      <c r="S20" s="94" t="n">
         <v>-0.48</v>
       </c>
-      <c r="R20" s="94" t="n">
+      <c r="T20" s="94" t="n">
         <v>-1.31</v>
       </c>
-      <c r="S20" s="94" t="n">
+      <c r="U20" s="94" t="n">
         <v>-1.31</v>
       </c>
-      <c r="T20" s="94" t="n">
+      <c r="V20" s="94" t="n">
         <v>-1.72</v>
       </c>
-      <c r="U20" s="94" t="n">
+      <c r="W20" s="94" t="n">
         <v>-0.63</v>
       </c>
-      <c r="V20" s="94" t="n">
+      <c r="X20" s="94" t="n">
         <v>-1.08</v>
       </c>
-      <c r="W20" s="94" t="n">
+      <c r="Y20" s="94" t="n">
         <v>-0.2</v>
       </c>
-      <c r="X20" s="94" t="n">
+      <c r="Z20" s="94" t="n">
         <v>3.12</v>
       </c>
-      <c r="Y20" s="94" t="n">
+      <c r="AA20" s="94" t="n">
         <v>3.12</v>
       </c>
-      <c r="Z20" s="94" t="n">
+      <c r="AB20" s="94" t="n">
         <v>3.32</v>
       </c>
-      <c r="AA20" s="94" t="n">
+      <c r="AC20" s="94" t="n">
         <v>6.32</v>
       </c>
-      <c r="AB20" s="94" t="n">
+      <c r="AD20" s="94" t="n">
         <v>5.61</v>
       </c>
-      <c r="AC20" s="94" t="n">
+      <c r="AE20" s="94" t="n">
         <v>8.16</v>
       </c>
-      <c r="AD20" s="94" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AE20" s="94" t="n">
-        <v>8.199999999999999</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="96" t="inlineStr">
+      <c r="A21" s="95" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
@@ -8644,91 +8643,91 @@
         <v>2.99</v>
       </c>
       <c r="C21" s="94" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D21" s="94" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E21" s="94" t="n">
         <v>9.18</v>
       </c>
-      <c r="D21" s="94" t="n">
+      <c r="F21" s="94" t="n">
         <v>76.8</v>
       </c>
-      <c r="E21" s="94" t="n">
+      <c r="G21" s="94" t="n">
         <v>52.81</v>
       </c>
-      <c r="F21" s="94" t="n">
+      <c r="H21" s="94" t="n">
         <v>33.59</v>
       </c>
-      <c r="G21" s="94" t="n">
+      <c r="I21" s="94" t="n">
         <v>5.59</v>
       </c>
-      <c r="H21" s="94" t="n">
+      <c r="J21" s="94" t="n">
         <v>23.94</v>
       </c>
-      <c r="I21" s="94" t="n">
+      <c r="K21" s="94" t="n">
         <v>33.06</v>
       </c>
-      <c r="J21" s="94" t="n">
+      <c r="L21" s="94" t="n">
         <v>94.42</v>
       </c>
-      <c r="K21" s="94" t="n">
+      <c r="M21" s="94" t="n">
         <v>93.58</v>
       </c>
-      <c r="L21" s="94" t="n">
+      <c r="N21" s="94" t="n">
         <v>62.65</v>
       </c>
-      <c r="M21" s="94" t="n">
+      <c r="O21" s="94" t="n">
         <v>62.65</v>
       </c>
-      <c r="N21" s="94" t="n">
+      <c r="P21" s="94" t="n">
         <v>57.92</v>
       </c>
-      <c r="O21" s="94" t="n">
+      <c r="Q21" s="94" t="n">
         <v>69.63</v>
       </c>
-      <c r="P21" s="94" t="n">
+      <c r="R21" s="94" t="n">
         <v>39.94</v>
       </c>
-      <c r="Q21" s="94" t="n">
+      <c r="S21" s="94" t="n">
         <v>77.94</v>
       </c>
-      <c r="R21" s="94" t="n">
+      <c r="T21" s="94" t="n">
         <v>69.16</v>
       </c>
-      <c r="S21" s="94" t="n">
+      <c r="U21" s="94" t="n">
         <v>69.16</v>
       </c>
-      <c r="T21" s="94" t="n">
+      <c r="V21" s="94" t="n">
         <v>13.01</v>
       </c>
-      <c r="U21" s="94" t="n">
+      <c r="W21" s="94" t="n">
         <v>32.79</v>
       </c>
-      <c r="V21" s="94" t="n">
+      <c r="X21" s="94" t="n">
         <v>8.44</v>
       </c>
-      <c r="W21" s="94" t="n">
+      <c r="Y21" s="94" t="n">
         <v>11.76</v>
       </c>
-      <c r="X21" s="94" t="n">
+      <c r="Z21" s="94" t="n">
         <v>42.26</v>
       </c>
-      <c r="Y21" s="94" t="n">
+      <c r="AA21" s="94" t="n">
         <v>42.26</v>
       </c>
-      <c r="Z21" s="94" t="n">
+      <c r="AB21" s="94" t="n">
         <v>21.55</v>
       </c>
-      <c r="AA21" s="94" t="n">
+      <c r="AC21" s="94" t="n">
         <v>52.46</v>
       </c>
-      <c r="AB21" s="94" t="n">
+      <c r="AD21" s="94" t="n">
         <v>14.46</v>
       </c>
-      <c r="AC21" s="94" t="n">
+      <c r="AE21" s="94" t="n">
         <v>25.99</v>
-      </c>
-      <c r="AD21" s="94" t="n">
-        <v>62.38</v>
-      </c>
-      <c r="AE21" s="94" t="n">
-        <v>62.38</v>
       </c>
     </row>
     <row r="22">
@@ -8737,154 +8736,154 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="92" t="inlineStr">
+      <c r="B22" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C22" s="92" t="inlineStr">
+      <c r="C22" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D22" s="93" t="inlineStr">
+      <c r="D22" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E22" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F22" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E22" s="92" t="inlineStr">
+      <c r="G22" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F22" s="92" t="inlineStr">
+      <c r="H22" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G22" s="92" t="inlineStr">
+      <c r="I22" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H22" s="91" t="inlineStr">
+      <c r="J22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I22" s="93" t="inlineStr">
+      <c r="K22" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J22" s="93" t="inlineStr">
+      <c r="L22" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K22" s="93" t="inlineStr">
+      <c r="M22" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L22" s="91" t="inlineStr">
+      <c r="N22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M22" s="91" t="inlineStr">
+      <c r="O22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N22" s="91" t="inlineStr">
+      <c r="P22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O22" s="91" t="inlineStr">
+      <c r="Q22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P22" s="91" t="inlineStr">
+      <c r="R22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q22" s="91" t="inlineStr">
+      <c r="S22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R22" s="91" t="inlineStr">
+      <c r="T22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S22" s="91" t="inlineStr">
+      <c r="U22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T22" s="92" t="inlineStr">
+      <c r="V22" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U22" s="92" t="inlineStr">
+      <c r="W22" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V22" s="92" t="inlineStr">
+      <c r="X22" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W22" s="92" t="inlineStr">
+      <c r="Y22" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X22" s="91" t="inlineStr">
+      <c r="Z22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y22" s="91" t="inlineStr">
+      <c r="AA22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z22" s="92" t="inlineStr">
+      <c r="AB22" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA22" s="91" t="inlineStr">
+      <c r="AC22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB22" s="92" t="inlineStr">
+      <c r="AD22" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC22" s="92" t="inlineStr">
+      <c r="AE22" s="91" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AD22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -8898,91 +8897,91 @@
         <v>-9.91</v>
       </c>
       <c r="C23" s="94" t="n">
+        <v>-9.91</v>
+      </c>
+      <c r="D23" s="94" t="n">
+        <v>-9.91</v>
+      </c>
+      <c r="E23" s="94" t="n">
         <v>-5.06</v>
       </c>
-      <c r="D23" s="94" t="n">
+      <c r="F23" s="94" t="n">
         <v>-1.19</v>
       </c>
-      <c r="E23" s="94" t="n">
+      <c r="G23" s="94" t="n">
         <v>-0.95</v>
       </c>
-      <c r="F23" s="94" t="n">
+      <c r="H23" s="94" t="n">
         <v>-1.28</v>
       </c>
-      <c r="G23" s="94" t="n">
+      <c r="I23" s="94" t="n">
         <v>-2.32</v>
       </c>
-      <c r="H23" s="94" t="n">
+      <c r="J23" s="94" t="n">
         <v>-1.61</v>
       </c>
-      <c r="I23" s="94" t="n">
+      <c r="K23" s="94" t="n">
         <v>-2.01</v>
       </c>
-      <c r="J23" s="94" t="n">
+      <c r="L23" s="94" t="n">
         <v>-1.64</v>
       </c>
-      <c r="K23" s="94" t="n">
+      <c r="M23" s="94" t="n">
         <v>-0.75</v>
       </c>
-      <c r="L23" s="94" t="n">
+      <c r="N23" s="94" t="n">
         <v>-2</v>
       </c>
-      <c r="M23" s="94" t="n">
+      <c r="O23" s="94" t="n">
         <v>-2</v>
       </c>
-      <c r="N23" s="94" t="n">
+      <c r="P23" s="94" t="n">
         <v>-0.92</v>
       </c>
-      <c r="O23" s="94" t="n">
+      <c r="Q23" s="94" t="n">
         <v>-0.86</v>
       </c>
-      <c r="P23" s="94" t="n">
+      <c r="R23" s="94" t="n">
         <v>-4.3</v>
       </c>
-      <c r="Q23" s="94" t="n">
+      <c r="S23" s="94" t="n">
         <v>-4.29</v>
       </c>
-      <c r="R23" s="94" t="n">
+      <c r="T23" s="94" t="n">
         <v>-5.34</v>
       </c>
-      <c r="S23" s="94" t="n">
+      <c r="U23" s="94" t="n">
         <v>-5.34</v>
       </c>
-      <c r="T23" s="94" t="n">
+      <c r="V23" s="94" t="n">
         <v>-7.06</v>
       </c>
-      <c r="U23" s="94" t="n">
+      <c r="W23" s="94" t="n">
         <v>-6.34</v>
       </c>
-      <c r="V23" s="94" t="n">
+      <c r="X23" s="94" t="n">
         <v>-6.36</v>
       </c>
-      <c r="W23" s="94" t="n">
+      <c r="Y23" s="94" t="n">
         <v>-5.61</v>
       </c>
-      <c r="X23" s="94" t="n">
+      <c r="Z23" s="94" t="n">
         <v>-4.12</v>
       </c>
-      <c r="Y23" s="94" t="n">
+      <c r="AA23" s="94" t="n">
         <v>-4.12</v>
       </c>
-      <c r="Z23" s="94" t="n">
+      <c r="AB23" s="94" t="n">
         <v>-4.88</v>
       </c>
-      <c r="AA23" s="94" t="n">
+      <c r="AC23" s="94" t="n">
         <v>-4.46</v>
       </c>
-      <c r="AB23" s="94" t="n">
+      <c r="AD23" s="94" t="n">
         <v>-4.89</v>
       </c>
-      <c r="AC23" s="94" t="n">
+      <c r="AE23" s="94" t="n">
         <v>-3.55</v>
-      </c>
-      <c r="AD23" s="94" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="AE23" s="94" t="n">
-        <v>-2.38</v>
       </c>
     </row>
     <row r="24">
@@ -8995,95 +8994,95 @@
         <v>-9.75</v>
       </c>
       <c r="C24" s="94" t="n">
+        <v>-9.75</v>
+      </c>
+      <c r="D24" s="94" t="n">
+        <v>-9.75</v>
+      </c>
+      <c r="E24" s="94" t="n">
         <v>-4.62</v>
       </c>
-      <c r="D24" s="94" t="n">
+      <c r="F24" s="94" t="n">
         <v>0.34</v>
       </c>
-      <c r="E24" s="94" t="n">
+      <c r="G24" s="94" t="n">
         <v>0.09</v>
       </c>
-      <c r="F24" s="94" t="n">
+      <c r="H24" s="94" t="n">
         <v>-0.83</v>
       </c>
-      <c r="G24" s="94" t="n">
+      <c r="I24" s="94" t="n">
         <v>-1.02</v>
       </c>
-      <c r="H24" s="94" t="n">
+      <c r="J24" s="94" t="n">
         <v>0.24</v>
       </c>
-      <c r="I24" s="94" t="n">
+      <c r="K24" s="94" t="n">
         <v>0.71</v>
       </c>
-      <c r="J24" s="94" t="n">
+      <c r="L24" s="94" t="n">
         <v>0.61</v>
       </c>
-      <c r="K24" s="94" t="n">
+      <c r="M24" s="94" t="n">
         <v>0.64</v>
       </c>
-      <c r="L24" s="94" t="n">
+      <c r="N24" s="94" t="n">
         <v>-0.45</v>
       </c>
-      <c r="M24" s="94" t="n">
+      <c r="O24" s="94" t="n">
         <v>-0.45</v>
       </c>
-      <c r="N24" s="94" t="n">
+      <c r="P24" s="94" t="n">
         <v>0.09</v>
       </c>
-      <c r="O24" s="94" t="n">
+      <c r="Q24" s="94" t="n">
         <v>-0.58</v>
       </c>
-      <c r="P24" s="94" t="n">
+      <c r="R24" s="94" t="n">
         <v>-1.29</v>
       </c>
-      <c r="Q24" s="94" t="n">
+      <c r="S24" s="94" t="n">
         <v>-0.53</v>
       </c>
-      <c r="R24" s="94" t="n">
+      <c r="T24" s="94" t="n">
         <v>-1.28</v>
       </c>
-      <c r="S24" s="94" t="n">
+      <c r="U24" s="94" t="n">
         <v>-1.28</v>
       </c>
-      <c r="T24" s="94" t="n">
+      <c r="V24" s="94" t="n">
         <v>-1.66</v>
       </c>
-      <c r="U24" s="94" t="n">
+      <c r="W24" s="94" t="n">
         <v>-0.61</v>
       </c>
-      <c r="V24" s="94" t="n">
+      <c r="X24" s="94" t="n">
         <v>-0.45</v>
       </c>
-      <c r="W24" s="94" t="n">
+      <c r="Y24" s="94" t="n">
         <v>1.25</v>
       </c>
-      <c r="X24" s="94" t="n">
+      <c r="Z24" s="94" t="n">
         <v>4.15</v>
       </c>
-      <c r="Y24" s="94" t="n">
+      <c r="AA24" s="94" t="n">
         <v>4.15</v>
       </c>
-      <c r="Z24" s="94" t="n">
+      <c r="AB24" s="94" t="n">
         <v>4.2</v>
       </c>
-      <c r="AA24" s="94" t="n">
+      <c r="AC24" s="94" t="n">
         <v>5.57</v>
       </c>
-      <c r="AB24" s="94" t="n">
+      <c r="AD24" s="94" t="n">
         <v>4.14</v>
       </c>
-      <c r="AC24" s="94" t="n">
+      <c r="AE24" s="94" t="n">
         <v>7.05</v>
       </c>
-      <c r="AD24" s="94" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="AE24" s="94" t="n">
-        <v>7.57</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="96" t="inlineStr">
+      <c r="A25" s="95" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
@@ -9092,91 +9091,91 @@
         <v>5.68</v>
       </c>
       <c r="C25" s="94" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="D25" s="94" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="E25" s="94" t="n">
         <v>14.42</v>
       </c>
-      <c r="D25" s="94" t="n">
+      <c r="F25" s="94" t="n">
         <v>63.09</v>
       </c>
-      <c r="E25" s="94" t="n">
+      <c r="G25" s="94" t="n">
         <v>46.09</v>
       </c>
-      <c r="F25" s="94" t="n">
+      <c r="H25" s="94" t="n">
         <v>46.81</v>
       </c>
-      <c r="G25" s="94" t="n">
+      <c r="I25" s="94" t="n">
         <v>15.69</v>
       </c>
-      <c r="H25" s="94" t="n">
+      <c r="J25" s="94" t="n">
         <v>47.29</v>
       </c>
-      <c r="I25" s="94" t="n">
+      <c r="K25" s="94" t="n">
         <v>66.68000000000001</v>
       </c>
-      <c r="J25" s="94" t="n">
+      <c r="L25" s="94" t="n">
         <v>87.05</v>
       </c>
-      <c r="K25" s="94" t="n">
+      <c r="M25" s="94" t="n">
         <v>86.95999999999999</v>
       </c>
-      <c r="L25" s="94" t="n">
+      <c r="N25" s="94" t="n">
         <v>66.09</v>
       </c>
-      <c r="M25" s="94" t="n">
+      <c r="O25" s="94" t="n">
         <v>66.09</v>
       </c>
-      <c r="N25" s="94" t="n">
+      <c r="P25" s="94" t="n">
         <v>64.04000000000001</v>
       </c>
-      <c r="O25" s="94" t="n">
+      <c r="Q25" s="94" t="n">
         <v>64.95999999999999</v>
       </c>
-      <c r="P25" s="94" t="n">
+      <c r="R25" s="94" t="n">
         <v>47.92</v>
       </c>
-      <c r="Q25" s="94" t="n">
+      <c r="S25" s="94" t="n">
         <v>61.45</v>
       </c>
-      <c r="R25" s="94" t="n">
+      <c r="T25" s="94" t="n">
         <v>48.21</v>
       </c>
-      <c r="S25" s="94" t="n">
+      <c r="U25" s="94" t="n">
         <v>48.21</v>
       </c>
-      <c r="T25" s="94" t="n">
+      <c r="V25" s="94" t="n">
         <v>7.98</v>
       </c>
-      <c r="U25" s="94" t="n">
+      <c r="W25" s="94" t="n">
         <v>13.58</v>
       </c>
-      <c r="V25" s="94" t="n">
+      <c r="X25" s="94" t="n">
         <v>14.64</v>
       </c>
-      <c r="W25" s="94" t="n">
+      <c r="Y25" s="94" t="n">
         <v>20.89</v>
       </c>
-      <c r="X25" s="94" t="n">
+      <c r="Z25" s="94" t="n">
         <v>44.4</v>
       </c>
-      <c r="Y25" s="94" t="n">
+      <c r="AA25" s="94" t="n">
         <v>44.4</v>
       </c>
-      <c r="Z25" s="94" t="n">
+      <c r="AB25" s="94" t="n">
         <v>31.55</v>
       </c>
-      <c r="AA25" s="94" t="n">
+      <c r="AC25" s="94" t="n">
         <v>44.8</v>
       </c>
-      <c r="AB25" s="94" t="n">
+      <c r="AD25" s="94" t="n">
         <v>19.04</v>
       </c>
-      <c r="AC25" s="94" t="n">
+      <c r="AE25" s="94" t="n">
         <v>33.38</v>
-      </c>
-      <c r="AD25" s="94" t="n">
-        <v>65.01000000000001</v>
-      </c>
-      <c r="AE25" s="94" t="n">
-        <v>65.01000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -9185,159 +9184,159 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
+      <c r="B26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C26" s="92" t="inlineStr">
+      <c r="C26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
       <c r="D26" s="91" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E26" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F26" s="92" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E26" s="92" t="inlineStr">
+      <c r="G26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F26" s="92" t="inlineStr">
+      <c r="H26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G26" s="92" t="inlineStr">
+      <c r="I26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H26" s="92" t="inlineStr">
+      <c r="J26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I26" s="92" t="inlineStr">
+      <c r="K26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J26" s="93" t="inlineStr">
+      <c r="L26" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K26" s="93" t="inlineStr">
+      <c r="M26" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L26" s="91" t="inlineStr">
+      <c r="N26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M26" s="91" t="inlineStr">
+      <c r="O26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N26" s="91" t="inlineStr">
+      <c r="P26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O26" s="91" t="inlineStr">
+      <c r="Q26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P26" s="91" t="inlineStr">
+      <c r="R26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q26" s="91" t="inlineStr">
+      <c r="S26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R26" s="91" t="inlineStr">
+      <c r="T26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S26" s="91" t="inlineStr">
+      <c r="U26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T26" s="91" t="inlineStr">
+      <c r="V26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U26" s="91" t="inlineStr">
+      <c r="W26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V26" s="92" t="inlineStr">
+      <c r="X26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W26" s="92" t="inlineStr">
+      <c r="Y26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X26" s="91" t="inlineStr">
+      <c r="Z26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y26" s="91" t="inlineStr">
+      <c r="AA26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z26" s="92" t="inlineStr">
+      <c r="AB26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA26" s="91" t="inlineStr">
+      <c r="AC26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB26" s="92" t="inlineStr">
+      <c r="AD26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC26" s="92" t="inlineStr">
+      <c r="AE26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" s="96" t="inlineStr">
+      <c r="A27" s="95" t="inlineStr">
         <is>
           <t>ixic:RNG60</t>
         </is>
@@ -9346,91 +9345,91 @@
         <v>-20.02</v>
       </c>
       <c r="C27" s="94" t="n">
+        <v>-20.02</v>
+      </c>
+      <c r="D27" s="94" t="n">
+        <v>-20.02</v>
+      </c>
+      <c r="E27" s="94" t="n">
         <v>-16.68</v>
       </c>
-      <c r="D27" s="94" t="n">
+      <c r="F27" s="94" t="n">
         <v>-10.3</v>
       </c>
-      <c r="E27" s="94" t="n">
+      <c r="G27" s="94" t="n">
         <v>-9.5</v>
       </c>
-      <c r="F27" s="94" t="n">
+      <c r="H27" s="94" t="n">
         <v>-10.42</v>
       </c>
-      <c r="G27" s="94" t="n">
+      <c r="I27" s="94" t="n">
         <v>-11.1</v>
       </c>
-      <c r="H27" s="94" t="n">
+      <c r="J27" s="94" t="n">
         <v>-9.73</v>
       </c>
-      <c r="I27" s="94" t="n">
+      <c r="K27" s="94" t="n">
         <v>-10.6</v>
       </c>
-      <c r="J27" s="94" t="n">
+      <c r="L27" s="94" t="n">
         <v>-8.779999999999999</v>
       </c>
-      <c r="K27" s="94" t="n">
+      <c r="M27" s="94" t="n">
         <v>-7.98</v>
       </c>
-      <c r="L27" s="94" t="n">
+      <c r="N27" s="94" t="n">
         <v>-9.140000000000001</v>
       </c>
-      <c r="M27" s="94" t="n">
+      <c r="O27" s="94" t="n">
         <v>-9.140000000000001</v>
       </c>
-      <c r="N27" s="94" t="n">
+      <c r="P27" s="94" t="n">
         <v>-8.68</v>
       </c>
-      <c r="O27" s="94" t="n">
+      <c r="Q27" s="94" t="n">
         <v>-8.470000000000001</v>
       </c>
-      <c r="P27" s="94" t="n">
+      <c r="R27" s="94" t="n">
         <v>-12.95</v>
       </c>
-      <c r="Q27" s="94" t="n">
+      <c r="S27" s="94" t="n">
         <v>-11.72</v>
       </c>
-      <c r="R27" s="94" t="n">
+      <c r="T27" s="94" t="n">
         <v>-10.9</v>
       </c>
-      <c r="S27" s="94" t="n">
+      <c r="U27" s="94" t="n">
         <v>-10.9</v>
       </c>
-      <c r="T27" s="94" t="n">
+      <c r="V27" s="94" t="n">
         <v>-13.06</v>
       </c>
-      <c r="U27" s="94" t="n">
+      <c r="W27" s="94" t="n">
         <v>-11.91</v>
       </c>
-      <c r="V27" s="94" t="n">
+      <c r="X27" s="94" t="n">
         <v>-11.43</v>
       </c>
-      <c r="W27" s="94" t="n">
+      <c r="Y27" s="94" t="n">
         <v>-11.49</v>
       </c>
-      <c r="X27" s="94" t="n">
+      <c r="Z27" s="94" t="n">
         <v>-8.380000000000001</v>
       </c>
-      <c r="Y27" s="94" t="n">
+      <c r="AA27" s="94" t="n">
         <v>-8.380000000000001</v>
       </c>
-      <c r="Z27" s="94" t="n">
+      <c r="AB27" s="94" t="n">
         <v>-8.279999999999999</v>
       </c>
-      <c r="AA27" s="94" t="n">
+      <c r="AC27" s="94" t="n">
         <v>-5.99</v>
       </c>
-      <c r="AB27" s="94" t="n">
+      <c r="AD27" s="94" t="n">
         <v>-6.14</v>
       </c>
-      <c r="AC27" s="94" t="n">
+      <c r="AE27" s="94" t="n">
         <v>-5.43</v>
-      </c>
-      <c r="AD27" s="94" t="n">
-        <v>-1.93</v>
-      </c>
-      <c r="AE27" s="94" t="n">
-        <v>-1.93</v>
       </c>
     </row>
     <row r="28">
@@ -9443,95 +9442,95 @@
         <v>-14.74</v>
       </c>
       <c r="C28" s="94" t="n">
+        <v>-14.74</v>
+      </c>
+      <c r="D28" s="94" t="n">
+        <v>-14.74</v>
+      </c>
+      <c r="E28" s="94" t="n">
         <v>-9.52</v>
       </c>
-      <c r="D28" s="94" t="n">
+      <c r="F28" s="94" t="n">
         <v>-3.2</v>
       </c>
-      <c r="E28" s="94" t="n">
+      <c r="G28" s="94" t="n">
         <v>-2.64</v>
       </c>
-      <c r="F28" s="94" t="n">
+      <c r="H28" s="94" t="n">
         <v>-4.62</v>
       </c>
-      <c r="G28" s="94" t="n">
+      <c r="I28" s="94" t="n">
         <v>-3.32</v>
       </c>
-      <c r="H28" s="94" t="n">
+      <c r="J28" s="94" t="n">
         <v>-0.68</v>
       </c>
-      <c r="I28" s="94" t="n">
+      <c r="K28" s="94" t="n">
         <v>-0.06</v>
       </c>
-      <c r="J28" s="94" t="n">
+      <c r="L28" s="94" t="n">
         <v>0.45</v>
       </c>
-      <c r="K28" s="94" t="n">
+      <c r="M28" s="94" t="n">
         <v>0.38</v>
       </c>
-      <c r="L28" s="94" t="n">
+      <c r="N28" s="94" t="n">
         <v>-2.23</v>
       </c>
-      <c r="M28" s="94" t="n">
+      <c r="O28" s="94" t="n">
         <v>-2.23</v>
       </c>
-      <c r="N28" s="94" t="n">
+      <c r="P28" s="94" t="n">
         <v>-2.16</v>
       </c>
-      <c r="O28" s="94" t="n">
+      <c r="Q28" s="94" t="n">
         <v>-1.79</v>
       </c>
-      <c r="P28" s="94" t="n">
+      <c r="R28" s="94" t="n">
         <v>-2.62</v>
       </c>
-      <c r="Q28" s="94" t="n">
+      <c r="S28" s="94" t="n">
         <v>-0.78</v>
       </c>
-      <c r="R28" s="94" t="n">
+      <c r="T28" s="94" t="n">
         <v>-1.44</v>
       </c>
-      <c r="S28" s="94" t="n">
+      <c r="U28" s="94" t="n">
         <v>-1.44</v>
       </c>
-      <c r="T28" s="94" t="n">
+      <c r="V28" s="94" t="n">
         <v>-1.54</v>
       </c>
-      <c r="U28" s="94" t="n">
+      <c r="W28" s="94" t="n">
         <v>0.12</v>
       </c>
-      <c r="V28" s="94" t="n">
+      <c r="X28" s="94" t="n">
         <v>-0.89</v>
       </c>
-      <c r="W28" s="94" t="n">
+      <c r="Y28" s="94" t="n">
         <v>-1.22</v>
       </c>
-      <c r="X28" s="94" t="n">
+      <c r="Z28" s="94" t="n">
         <v>3.57</v>
       </c>
-      <c r="Y28" s="94" t="n">
+      <c r="AA28" s="94" t="n">
         <v>3.57</v>
       </c>
-      <c r="Z28" s="94" t="n">
+      <c r="AB28" s="94" t="n">
         <v>3.87</v>
       </c>
-      <c r="AA28" s="94" t="n">
+      <c r="AC28" s="94" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="AB28" s="94" t="n">
+      <c r="AD28" s="94" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="AC28" s="94" t="n">
+      <c r="AE28" s="94" t="n">
         <v>9.94</v>
       </c>
-      <c r="AD28" s="94" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="AE28" s="94" t="n">
-        <v>10.04</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" s="96" t="inlineStr">
+      <c r="A29" s="95" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
@@ -9540,91 +9539,91 @@
         <v>3.7</v>
       </c>
       <c r="C29" s="94" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D29" s="94" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E29" s="94" t="n">
         <v>9.58</v>
       </c>
-      <c r="D29" s="94" t="n">
+      <c r="F29" s="94" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="E29" s="94" t="n">
+      <c r="G29" s="94" t="n">
         <v>48.94</v>
       </c>
-      <c r="F29" s="94" t="n">
+      <c r="H29" s="94" t="n">
         <v>5.77</v>
       </c>
-      <c r="G29" s="94" t="n">
+      <c r="I29" s="94" t="n">
         <v>6.18</v>
       </c>
-      <c r="H29" s="94" t="n">
+      <c r="J29" s="94" t="n">
         <v>22.32</v>
       </c>
-      <c r="I29" s="94" t="n">
+      <c r="K29" s="94" t="n">
         <v>30.08</v>
       </c>
-      <c r="J29" s="94" t="n">
+      <c r="L29" s="94" t="n">
         <v>94.62</v>
       </c>
-      <c r="K29" s="94" t="n">
+      <c r="M29" s="94" t="n">
         <v>92.92</v>
       </c>
-      <c r="L29" s="94" t="n">
+      <c r="N29" s="94" t="n">
         <v>69.84999999999999</v>
       </c>
-      <c r="M29" s="94" t="n">
+      <c r="O29" s="94" t="n">
         <v>69.84999999999999</v>
       </c>
-      <c r="N29" s="94" t="n">
+      <c r="P29" s="94" t="n">
         <v>51.97</v>
       </c>
-      <c r="O29" s="94" t="n">
+      <c r="Q29" s="94" t="n">
         <v>64.14</v>
       </c>
-      <c r="P29" s="94" t="n">
+      <c r="R29" s="94" t="n">
         <v>29.95</v>
       </c>
-      <c r="Q29" s="94" t="n">
+      <c r="S29" s="94" t="n">
         <v>72.81999999999999</v>
       </c>
-      <c r="R29" s="94" t="n">
+      <c r="T29" s="94" t="n">
         <v>68.81999999999999</v>
       </c>
-      <c r="S29" s="94" t="n">
+      <c r="U29" s="94" t="n">
         <v>68.81999999999999</v>
       </c>
-      <c r="T29" s="94" t="n">
+      <c r="V29" s="94" t="n">
         <v>20.44</v>
       </c>
-      <c r="U29" s="94" t="n">
+      <c r="W29" s="94" t="n">
         <v>50.35</v>
       </c>
-      <c r="V29" s="94" t="n">
+      <c r="X29" s="94" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="W29" s="94" t="n">
+      <c r="Y29" s="94" t="n">
         <v>10.44</v>
       </c>
-      <c r="X29" s="94" t="n">
+      <c r="Z29" s="94" t="n">
         <v>41.16</v>
       </c>
-      <c r="Y29" s="94" t="n">
+      <c r="AA29" s="94" t="n">
         <v>41.16</v>
       </c>
-      <c r="Z29" s="94" t="n">
+      <c r="AB29" s="94" t="n">
         <v>20.86</v>
       </c>
-      <c r="AA29" s="94" t="n">
+      <c r="AC29" s="94" t="n">
         <v>60.82</v>
       </c>
-      <c r="AB29" s="94" t="n">
+      <c r="AD29" s="94" t="n">
         <v>16.64</v>
       </c>
-      <c r="AC29" s="94" t="n">
+      <c r="AE29" s="94" t="n">
         <v>19.28</v>
-      </c>
-      <c r="AD29" s="94" t="n">
-        <v>49.05</v>
-      </c>
-      <c r="AE29" s="94" t="n">
-        <v>49.05</v>
       </c>
     </row>
     <row r="30">
@@ -9633,159 +9632,159 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B30" s="92" t="inlineStr">
+      <c r="B30" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C30" s="92" t="inlineStr">
+      <c r="C30" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D30" s="92" t="inlineStr">
+      <c r="D30" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E30" s="92" t="inlineStr">
+      <c r="E30" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F30" s="92" t="inlineStr">
+      <c r="F30" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G30" s="92" t="inlineStr">
+      <c r="G30" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
       <c r="H30" s="91" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I30" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J30" s="92" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I30" s="93" t="inlineStr">
+      <c r="K30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J30" s="93" t="inlineStr">
+      <c r="L30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K30" s="91" t="inlineStr">
+      <c r="M30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L30" s="93" t="inlineStr">
+      <c r="N30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M30" s="93" t="inlineStr">
+      <c r="O30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N30" s="93" t="inlineStr">
+      <c r="P30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O30" s="93" t="inlineStr">
+      <c r="Q30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P30" s="93" t="inlineStr">
+      <c r="R30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q30" s="93" t="inlineStr">
+      <c r="S30" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R30" s="91" t="inlineStr">
+      <c r="T30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S30" s="91" t="inlineStr">
+      <c r="U30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T30" s="91" t="inlineStr">
+      <c r="V30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U30" s="91" t="inlineStr">
+      <c r="W30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V30" s="91" t="inlineStr">
+      <c r="X30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W30" s="91" t="inlineStr">
+      <c r="Y30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X30" s="92" t="inlineStr">
+      <c r="Z30" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y30" s="92" t="inlineStr">
+      <c r="AA30" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z30" s="91" t="inlineStr">
+      <c r="AB30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA30" s="91" t="inlineStr">
+      <c r="AC30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB30" s="92" t="inlineStr">
+      <c r="AD30" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC30" s="91" t="inlineStr">
+      <c r="AE30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD30" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE30" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" s="96" t="inlineStr">
+      <c r="A31" s="95" t="inlineStr">
         <is>
           <t>jp225:RNG60</t>
         </is>
@@ -9794,91 +9793,91 @@
         <v>-15.51</v>
       </c>
       <c r="C31" s="94" t="n">
+        <v>-15.51</v>
+      </c>
+      <c r="D31" s="94" t="n">
+        <v>-15.51</v>
+      </c>
+      <c r="E31" s="94" t="n">
         <v>-13.34</v>
       </c>
-      <c r="D31" s="94" t="n">
+      <c r="F31" s="94" t="n">
         <v>-9.109999999999999</v>
       </c>
-      <c r="E31" s="94" t="n">
+      <c r="G31" s="94" t="n">
         <v>-10.7</v>
       </c>
-      <c r="F31" s="94" t="n">
+      <c r="H31" s="94" t="n">
         <v>-11.58</v>
       </c>
-      <c r="G31" s="94" t="n">
+      <c r="I31" s="94" t="n">
         <v>-6.19</v>
       </c>
-      <c r="H31" s="94" t="n">
+      <c r="J31" s="94" t="n">
         <v>-3.4</v>
       </c>
-      <c r="I31" s="94" t="n">
+      <c r="K31" s="94" t="n">
         <v>-2.59</v>
       </c>
-      <c r="J31" s="94" t="n">
+      <c r="L31" s="94" t="n">
         <v>-3.53</v>
       </c>
-      <c r="K31" s="94" t="n">
+      <c r="M31" s="94" t="n">
         <v>-2.83</v>
       </c>
-      <c r="L31" s="94" t="n">
+      <c r="N31" s="94" t="n">
         <v>-2.93</v>
       </c>
-      <c r="M31" s="94" t="n">
+      <c r="O31" s="94" t="n">
         <v>-2.93</v>
       </c>
-      <c r="N31" s="94" t="n">
+      <c r="P31" s="94" t="n">
         <v>-3.09</v>
       </c>
-      <c r="O31" s="94" t="n">
+      <c r="Q31" s="94" t="n">
         <v>-4.1</v>
       </c>
-      <c r="P31" s="94" t="n">
+      <c r="R31" s="94" t="n">
         <v>-4.09</v>
       </c>
-      <c r="Q31" s="94" t="n">
+      <c r="S31" s="94" t="n">
         <v>-5.25</v>
       </c>
-      <c r="R31" s="94" t="n">
+      <c r="T31" s="94" t="n">
         <v>-7.02</v>
       </c>
-      <c r="S31" s="94" t="n">
+      <c r="U31" s="94" t="n">
         <v>-7.02</v>
       </c>
-      <c r="T31" s="94" t="n">
+      <c r="V31" s="94" t="n">
         <v>-6.56</v>
       </c>
-      <c r="U31" s="94" t="n">
+      <c r="W31" s="94" t="n">
         <v>-6.47</v>
       </c>
-      <c r="V31" s="94" t="n">
+      <c r="X31" s="94" t="n">
         <v>-6.05</v>
       </c>
-      <c r="W31" s="94" t="n">
+      <c r="Y31" s="94" t="n">
         <v>-5.28</v>
       </c>
-      <c r="X31" s="94" t="n">
+      <c r="Z31" s="94" t="n">
         <v>-6.37</v>
       </c>
-      <c r="Y31" s="94" t="n">
+      <c r="AA31" s="94" t="n">
         <v>-6.37</v>
       </c>
-      <c r="Z31" s="94" t="n">
+      <c r="AB31" s="94" t="n">
         <v>-4</v>
       </c>
-      <c r="AA31" s="94" t="n">
+      <c r="AC31" s="94" t="n">
         <v>-4.66</v>
       </c>
-      <c r="AB31" s="94" t="n">
+      <c r="AD31" s="94" t="n">
         <v>-3.07</v>
       </c>
-      <c r="AC31" s="94" t="n">
+      <c r="AE31" s="94" t="n">
         <v>-1.11</v>
-      </c>
-      <c r="AD31" s="94" t="n">
-        <v>-3.11</v>
-      </c>
-      <c r="AE31" s="94" t="n">
-        <v>-3.11</v>
       </c>
     </row>
     <row r="32">
@@ -9891,95 +9890,95 @@
         <v>-14</v>
       </c>
       <c r="C32" s="94" t="n">
+        <v>-14</v>
+      </c>
+      <c r="D32" s="94" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E32" s="94" t="n">
         <v>-10.79</v>
       </c>
-      <c r="D32" s="94" t="n">
+      <c r="F32" s="94" t="n">
         <v>-9.17</v>
       </c>
-      <c r="E32" s="94" t="n">
+      <c r="G32" s="94" t="n">
         <v>-7.79</v>
       </c>
-      <c r="F32" s="94" t="n">
+      <c r="H32" s="94" t="n">
         <v>-7.61</v>
       </c>
-      <c r="G32" s="94" t="n">
+      <c r="I32" s="94" t="n">
         <v>-1.82</v>
       </c>
-      <c r="H32" s="94" t="n">
+      <c r="J32" s="94" t="n">
         <v>-2.2</v>
       </c>
-      <c r="I32" s="94" t="n">
+      <c r="K32" s="94" t="n">
         <v>0.28</v>
       </c>
-      <c r="J32" s="94" t="n">
+      <c r="L32" s="94" t="n">
         <v>-5.14</v>
       </c>
-      <c r="K32" s="94" t="n">
+      <c r="M32" s="94" t="n">
         <v>-3.38</v>
       </c>
-      <c r="L32" s="94" t="n">
+      <c r="N32" s="94" t="n">
         <v>-0.51</v>
       </c>
-      <c r="M32" s="94" t="n">
+      <c r="O32" s="94" t="n">
         <v>-0.51</v>
       </c>
-      <c r="N32" s="94" t="n">
+      <c r="P32" s="94" t="n">
         <v>-0.18</v>
       </c>
-      <c r="O32" s="94" t="n">
+      <c r="Q32" s="94" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P32" s="94" t="n">
+      <c r="R32" s="94" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q32" s="94" t="n">
+      <c r="S32" s="94" t="n">
         <v>2.79</v>
       </c>
-      <c r="R32" s="94" t="n">
+      <c r="T32" s="94" t="n">
         <v>2.35</v>
       </c>
-      <c r="S32" s="94" t="n">
+      <c r="U32" s="94" t="n">
         <v>2.35</v>
       </c>
-      <c r="T32" s="94" t="n">
+      <c r="V32" s="94" t="n">
         <v>0.63</v>
       </c>
-      <c r="U32" s="94" t="n">
+      <c r="W32" s="94" t="n">
         <v>0.65</v>
       </c>
-      <c r="V32" s="94" t="n">
+      <c r="X32" s="94" t="n">
         <v>-0.11</v>
       </c>
-      <c r="W32" s="94" t="n">
+      <c r="Y32" s="94" t="n">
         <v>3.95</v>
       </c>
-      <c r="X32" s="94" t="n">
+      <c r="Z32" s="94" t="n">
         <v>2.01</v>
       </c>
-      <c r="Y32" s="94" t="n">
+      <c r="AA32" s="94" t="n">
         <v>2.01</v>
       </c>
-      <c r="Z32" s="94" t="n">
+      <c r="AB32" s="94" t="n">
         <v>4.11</v>
       </c>
-      <c r="AA32" s="94" t="n">
+      <c r="AC32" s="94" t="n">
         <v>2.82</v>
       </c>
-      <c r="AB32" s="94" t="n">
+      <c r="AD32" s="94" t="n">
         <v>1.84</v>
       </c>
-      <c r="AC32" s="94" t="n">
+      <c r="AE32" s="94" t="n">
         <v>1.99</v>
       </c>
-      <c r="AD32" s="94" t="n">
-        <v>-3.96</v>
-      </c>
-      <c r="AE32" s="94" t="n">
-        <v>-3.96</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" s="96" t="inlineStr">
+      <c r="A33" s="95" t="inlineStr">
         <is>
           <t>jp225:RS9</t>
         </is>
@@ -9988,91 +9987,91 @@
         <v>14.64</v>
       </c>
       <c r="C33" s="94" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="D33" s="94" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="E33" s="94" t="n">
         <v>18.88</v>
       </c>
-      <c r="D33" s="94" t="n">
+      <c r="F33" s="94" t="n">
         <v>25.75</v>
       </c>
-      <c r="E33" s="94" t="n">
+      <c r="G33" s="94" t="n">
         <v>23.21</v>
       </c>
-      <c r="F33" s="94" t="n">
+      <c r="H33" s="94" t="n">
         <v>23.05</v>
       </c>
-      <c r="G33" s="94" t="n">
+      <c r="I33" s="94" t="n">
         <v>38.53</v>
       </c>
-      <c r="H33" s="94" t="n">
+      <c r="J33" s="94" t="n">
         <v>52.79</v>
       </c>
-      <c r="I33" s="94" t="n">
+      <c r="K33" s="94" t="n">
         <v>59.31</v>
       </c>
-      <c r="J33" s="94" t="n">
+      <c r="L33" s="94" t="n">
         <v>53.8</v>
       </c>
-      <c r="K33" s="94" t="n">
+      <c r="M33" s="94" t="n">
         <v>49.57</v>
       </c>
-      <c r="L33" s="94" t="n">
+      <c r="N33" s="94" t="n">
         <v>51.23</v>
       </c>
-      <c r="M33" s="94" t="n">
+      <c r="O33" s="94" t="n">
         <v>51.23</v>
       </c>
-      <c r="N33" s="94" t="n">
+      <c r="P33" s="94" t="n">
         <v>55.99</v>
       </c>
-      <c r="O33" s="94" t="n">
+      <c r="Q33" s="94" t="n">
         <v>53.63</v>
       </c>
-      <c r="P33" s="94" t="n">
+      <c r="R33" s="94" t="n">
         <v>55.69</v>
       </c>
-      <c r="Q33" s="94" t="n">
+      <c r="S33" s="94" t="n">
         <v>47</v>
       </c>
-      <c r="R33" s="94" t="n">
+      <c r="T33" s="94" t="n">
         <v>38.84</v>
       </c>
-      <c r="S33" s="94" t="n">
+      <c r="U33" s="94" t="n">
         <v>38.84</v>
       </c>
-      <c r="T33" s="94" t="n">
+      <c r="V33" s="94" t="n">
         <v>31.69</v>
       </c>
-      <c r="U33" s="94" t="n">
+      <c r="W33" s="94" t="n">
         <v>32.06</v>
       </c>
-      <c r="V33" s="94" t="n">
+      <c r="X33" s="94" t="n">
         <v>31.42</v>
       </c>
-      <c r="W33" s="94" t="n">
+      <c r="Y33" s="94" t="n">
         <v>33.97</v>
       </c>
-      <c r="X33" s="94" t="n">
+      <c r="Z33" s="94" t="n">
         <v>30.98</v>
       </c>
-      <c r="Y33" s="94" t="n">
+      <c r="AA33" s="94" t="n">
         <v>30.98</v>
       </c>
-      <c r="Z33" s="94" t="n">
+      <c r="AB33" s="94" t="n">
         <v>40.4</v>
       </c>
-      <c r="AA33" s="94" t="n">
+      <c r="AC33" s="94" t="n">
         <v>34.16</v>
       </c>
-      <c r="AB33" s="94" t="n">
+      <c r="AD33" s="94" t="n">
         <v>32.25</v>
       </c>
-      <c r="AC33" s="94" t="n">
+      <c r="AE33" s="94" t="n">
         <v>37.27</v>
-      </c>
-      <c r="AD33" s="94" t="n">
-        <v>22.38</v>
-      </c>
-      <c r="AE33" s="94" t="n">
-        <v>22.38</v>
       </c>
     </row>
     <row r="34">
@@ -10081,152 +10080,152 @@
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B34" s="92" t="inlineStr">
+      <c r="B34" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C34" s="92" t="inlineStr">
+      <c r="C34" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
       <c r="D34" s="91" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E34" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F34" s="92" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E34" s="91" t="inlineStr">
+      <c r="G34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F34" s="92" t="inlineStr">
+      <c r="H34" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G34" s="92" t="inlineStr">
+      <c r="I34" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H34" s="92" t="inlineStr">
+      <c r="J34" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I34" s="91" t="inlineStr">
+      <c r="K34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J34" s="93" t="inlineStr">
+      <c r="L34" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K34" s="93" t="inlineStr">
+      <c r="M34" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L34" s="92" t="inlineStr">
+      <c r="N34" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M34" s="92" t="inlineStr">
+      <c r="O34" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N34" s="91" t="inlineStr">
+      <c r="P34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O34" s="91" t="inlineStr">
+      <c r="Q34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P34" s="91" t="inlineStr">
+      <c r="R34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q34" s="93" t="inlineStr">
+      <c r="S34" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R34" s="91" t="inlineStr">
+      <c r="T34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S34" s="91" t="inlineStr">
+      <c r="U34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T34" s="91" t="inlineStr">
+      <c r="V34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U34" s="91" t="inlineStr">
+      <c r="W34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V34" s="93" t="inlineStr">
+      <c r="X34" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W34" s="93" t="inlineStr">
+      <c r="Y34" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X34" s="93" t="inlineStr">
+      <c r="Z34" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y34" s="93" t="inlineStr">
+      <c r="AA34" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z34" s="93" t="inlineStr">
+      <c r="AB34" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA34" s="91" t="inlineStr">
+      <c r="AC34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB34" s="91" t="inlineStr">
+      <c r="AD34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE34" s="91" t="inlineStr">
+      <c r="AE34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -10242,91 +10241,91 @@
         <v>-3.5</v>
       </c>
       <c r="C35" s="94" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="D35" s="94" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="E35" s="94" t="n">
         <v>-3.14</v>
       </c>
-      <c r="D35" s="94" t="n">
+      <c r="F35" s="94" t="n">
         <v>4.03</v>
       </c>
-      <c r="E35" s="94" t="n">
+      <c r="G35" s="94" t="n">
         <v>3.56</v>
       </c>
-      <c r="F35" s="94" t="n">
+      <c r="H35" s="94" t="n">
         <v>2.49</v>
       </c>
-      <c r="G35" s="94" t="n">
+      <c r="I35" s="94" t="n">
         <v>3.5</v>
       </c>
-      <c r="H35" s="94" t="n">
+      <c r="J35" s="94" t="n">
         <v>3.91</v>
       </c>
-      <c r="I35" s="94" t="n">
+      <c r="K35" s="94" t="n">
         <v>5.22</v>
       </c>
-      <c r="J35" s="94" t="n">
+      <c r="L35" s="94" t="n">
         <v>5.48</v>
       </c>
-      <c r="K35" s="94" t="n">
+      <c r="M35" s="94" t="n">
         <v>5.79</v>
       </c>
-      <c r="L35" s="94" t="n">
+      <c r="N35" s="94" t="n">
         <v>5.36</v>
       </c>
-      <c r="M35" s="94" t="n">
+      <c r="O35" s="94" t="n">
         <v>5.36</v>
       </c>
-      <c r="N35" s="94" t="n">
+      <c r="P35" s="94" t="n">
         <v>4.58</v>
       </c>
-      <c r="O35" s="94" t="n">
+      <c r="Q35" s="94" t="n">
         <v>4.99</v>
       </c>
-      <c r="P35" s="94" t="n">
+      <c r="R35" s="94" t="n">
         <v>5.32</v>
       </c>
-      <c r="Q35" s="94" t="n">
+      <c r="S35" s="94" t="n">
         <v>5.84</v>
       </c>
-      <c r="R35" s="94" t="n">
+      <c r="T35" s="94" t="n">
         <v>4.64</v>
       </c>
-      <c r="S35" s="94" t="n">
+      <c r="U35" s="94" t="n">
         <v>4.64</v>
       </c>
-      <c r="T35" s="94" t="n">
+      <c r="V35" s="94" t="n">
         <v>4.52</v>
       </c>
-      <c r="U35" s="94" t="n">
+      <c r="W35" s="94" t="n">
         <v>4.9</v>
       </c>
-      <c r="V35" s="94" t="n">
+      <c r="X35" s="94" t="n">
         <v>4.61</v>
       </c>
-      <c r="W35" s="94" t="n">
+      <c r="Y35" s="94" t="n">
         <v>4.73</v>
       </c>
-      <c r="X35" s="94" t="n">
+      <c r="Z35" s="94" t="n">
         <v>4.62</v>
       </c>
-      <c r="Y35" s="94" t="n">
+      <c r="AA35" s="94" t="n">
         <v>4.62</v>
       </c>
-      <c r="Z35" s="94" t="n">
+      <c r="AB35" s="94" t="n">
         <v>6.27</v>
       </c>
-      <c r="AA35" s="94" t="n">
+      <c r="AC35" s="94" t="n">
         <v>4.39</v>
       </c>
-      <c r="AB35" s="94" t="n">
+      <c r="AD35" s="94" t="n">
         <v>4.85</v>
       </c>
-      <c r="AC35" s="94" t="n">
+      <c r="AE35" s="94" t="n">
         <v>4.71</v>
-      </c>
-      <c r="AD35" s="94" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="AE35" s="94" t="n">
-        <v>5.09</v>
       </c>
     </row>
     <row r="36">
@@ -10339,95 +10338,95 @@
         <v>-5.88</v>
       </c>
       <c r="C36" s="94" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="D36" s="94" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="E36" s="94" t="n">
         <v>-4.06</v>
       </c>
-      <c r="D36" s="94" t="n">
+      <c r="F36" s="94" t="n">
         <v>3.6</v>
       </c>
-      <c r="E36" s="94" t="n">
+      <c r="G36" s="94" t="n">
         <v>3.73</v>
       </c>
-      <c r="F36" s="94" t="n">
+      <c r="H36" s="94" t="n">
         <v>2.85</v>
       </c>
-      <c r="G36" s="94" t="n">
+      <c r="I36" s="94" t="n">
         <v>3.08</v>
       </c>
-      <c r="H36" s="94" t="n">
+      <c r="J36" s="94" t="n">
         <v>2.79</v>
       </c>
-      <c r="I36" s="94" t="n">
+      <c r="K36" s="94" t="n">
         <v>2.62</v>
       </c>
-      <c r="J36" s="94" t="n">
+      <c r="L36" s="94" t="n">
         <v>3.41</v>
       </c>
-      <c r="K36" s="94" t="n">
+      <c r="M36" s="94" t="n">
         <v>3.05</v>
       </c>
-      <c r="L36" s="94" t="n">
+      <c r="N36" s="94" t="n">
         <v>2.35</v>
       </c>
-      <c r="M36" s="94" t="n">
+      <c r="O36" s="94" t="n">
         <v>2.35</v>
       </c>
-      <c r="N36" s="94" t="n">
+      <c r="P36" s="94" t="n">
         <v>2.83</v>
       </c>
-      <c r="O36" s="94" t="n">
+      <c r="Q36" s="94" t="n">
         <v>3.73</v>
       </c>
-      <c r="P36" s="94" t="n">
+      <c r="R36" s="94" t="n">
         <v>4.93</v>
       </c>
-      <c r="Q36" s="94" t="n">
+      <c r="S36" s="94" t="n">
         <v>5.05</v>
       </c>
-      <c r="R36" s="94" t="n">
+      <c r="T36" s="94" t="n">
         <v>4.32</v>
       </c>
-      <c r="S36" s="94" t="n">
+      <c r="U36" s="94" t="n">
         <v>4.32</v>
       </c>
-      <c r="T36" s="94" t="n">
+      <c r="V36" s="94" t="n">
         <v>4.85</v>
       </c>
-      <c r="U36" s="94" t="n">
+      <c r="W36" s="94" t="n">
         <v>5.99</v>
       </c>
-      <c r="V36" s="94" t="n">
+      <c r="X36" s="94" t="n">
         <v>7.53</v>
       </c>
-      <c r="W36" s="94" t="n">
+      <c r="Y36" s="94" t="n">
         <v>6.28</v>
       </c>
-      <c r="X36" s="94" t="n">
+      <c r="Z36" s="94" t="n">
         <v>5.55</v>
       </c>
-      <c r="Y36" s="94" t="n">
+      <c r="AA36" s="94" t="n">
         <v>5.55</v>
       </c>
-      <c r="Z36" s="94" t="n">
+      <c r="AB36" s="94" t="n">
         <v>5.18</v>
       </c>
-      <c r="AA36" s="94" t="n">
+      <c r="AC36" s="94" t="n">
         <v>3.94</v>
       </c>
-      <c r="AB36" s="94" t="n">
+      <c r="AD36" s="94" t="n">
         <v>3.48</v>
       </c>
-      <c r="AC36" s="94" t="n">
+      <c r="AE36" s="94" t="n">
         <v>2.78</v>
       </c>
-      <c r="AD36" s="94" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AE36" s="94" t="n">
-        <v>2.93</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" s="96" t="inlineStr">
+      <c r="A37" s="95" t="inlineStr">
         <is>
           <t>vn:RS3</t>
         </is>
@@ -10436,91 +10435,91 @@
         <v>4.29</v>
       </c>
       <c r="C37" s="94" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="D37" s="94" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="E37" s="94" t="n">
         <v>5.54</v>
       </c>
-      <c r="D37" s="94" t="n">
+      <c r="F37" s="94" t="n">
         <v>50.33</v>
       </c>
-      <c r="E37" s="94" t="n">
+      <c r="G37" s="94" t="n">
         <v>48.76</v>
       </c>
-      <c r="F37" s="94" t="n">
+      <c r="H37" s="94" t="n">
         <v>8.33</v>
       </c>
-      <c r="G37" s="94" t="n">
+      <c r="I37" s="94" t="n">
         <v>17.82</v>
       </c>
-      <c r="H37" s="94" t="n">
+      <c r="J37" s="94" t="n">
         <v>32.69</v>
       </c>
-      <c r="I37" s="94" t="n">
+      <c r="K37" s="94" t="n">
         <v>40.84</v>
       </c>
-      <c r="J37" s="94" t="n">
+      <c r="L37" s="94" t="n">
         <v>71.06</v>
       </c>
-      <c r="K37" s="94" t="n">
+      <c r="M37" s="94" t="n">
         <v>66.54000000000001</v>
       </c>
-      <c r="L37" s="94" t="n">
+      <c r="N37" s="94" t="n">
         <v>25.54</v>
       </c>
-      <c r="M37" s="94" t="n">
+      <c r="O37" s="94" t="n">
         <v>25.54</v>
       </c>
-      <c r="N37" s="94" t="n">
+      <c r="P37" s="94" t="n">
         <v>31.86</v>
       </c>
-      <c r="O37" s="94" t="n">
+      <c r="Q37" s="94" t="n">
         <v>33.76</v>
       </c>
-      <c r="P37" s="94" t="n">
+      <c r="R37" s="94" t="n">
         <v>52.78</v>
       </c>
-      <c r="Q37" s="94" t="n">
+      <c r="S37" s="94" t="n">
         <v>76.89</v>
       </c>
-      <c r="R37" s="94" t="n">
+      <c r="T37" s="94" t="n">
         <v>44.73</v>
       </c>
-      <c r="S37" s="94" t="n">
+      <c r="U37" s="94" t="n">
         <v>44.73</v>
       </c>
-      <c r="T37" s="94" t="n">
+      <c r="V37" s="94" t="n">
         <v>45.22</v>
       </c>
-      <c r="U37" s="94" t="n">
+      <c r="W37" s="94" t="n">
         <v>91.12</v>
       </c>
-      <c r="V37" s="94" t="n">
+      <c r="X37" s="94" t="n">
         <v>89.48</v>
       </c>
-      <c r="W37" s="94" t="n">
+      <c r="Y37" s="94" t="n">
         <v>87.65000000000001</v>
       </c>
-      <c r="X37" s="94" t="n">
+      <c r="Z37" s="94" t="n">
         <v>84.23</v>
       </c>
-      <c r="Y37" s="94" t="n">
+      <c r="AA37" s="94" t="n">
         <v>84.23</v>
       </c>
-      <c r="Z37" s="94" t="n">
+      <c r="AB37" s="94" t="n">
         <v>76.01000000000001</v>
       </c>
-      <c r="AA37" s="94" t="n">
+      <c r="AC37" s="94" t="n">
         <v>40.18</v>
       </c>
-      <c r="AB37" s="94" t="n">
+      <c r="AD37" s="94" t="n">
         <v>85.62</v>
       </c>
-      <c r="AC37" s="94" t="n">
+      <c r="AE37" s="94" t="n">
         <v>80.41</v>
-      </c>
-      <c r="AD37" s="94" t="n">
-        <v>68.34</v>
-      </c>
-      <c r="AE37" s="94" t="n">
-        <v>68.34</v>
       </c>
     </row>
     <row r="38">
@@ -10529,152 +10528,152 @@
           <t>sensex:EIDE</t>
         </is>
       </c>
-      <c r="B38" s="92" t="inlineStr">
+      <c r="B38" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C38" s="92" t="inlineStr">
+      <c r="C38" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
       <c r="D38" s="91" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E38" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F38" s="92" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E38" s="92" t="inlineStr">
+      <c r="G38" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F38" s="91" t="inlineStr">
+      <c r="H38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G38" s="91" t="inlineStr">
+      <c r="I38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H38" s="91" t="inlineStr">
+      <c r="J38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I38" s="91" t="inlineStr">
+      <c r="K38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J38" s="93" t="inlineStr">
+      <c r="L38" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K38" s="93" t="inlineStr">
+      <c r="M38" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L38" s="93" t="inlineStr">
+      <c r="N38" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M38" s="93" t="inlineStr">
+      <c r="O38" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N38" s="93" t="inlineStr">
+      <c r="P38" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O38" s="93" t="inlineStr">
+      <c r="Q38" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P38" s="93" t="inlineStr">
+      <c r="R38" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q38" s="91" t="inlineStr">
+      <c r="S38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R38" s="91" t="inlineStr">
+      <c r="T38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S38" s="91" t="inlineStr">
+      <c r="U38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T38" s="91" t="inlineStr">
+      <c r="V38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U38" s="91" t="inlineStr">
+      <c r="W38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V38" s="91" t="inlineStr">
+      <c r="X38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W38" s="91" t="inlineStr">
+      <c r="Y38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X38" s="91" t="inlineStr">
+      <c r="Z38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y38" s="91" t="inlineStr">
+      <c r="AA38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z38" s="91" t="inlineStr">
+      <c r="AB38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA38" s="91" t="inlineStr">
+      <c r="AC38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB38" s="92" t="inlineStr">
+      <c r="AD38" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC38" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD38" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE38" s="92" t="inlineStr">
+      <c r="AE38" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -10690,91 +10689,91 @@
         <v>-3.56</v>
       </c>
       <c r="C39" s="94" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="D39" s="94" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="E39" s="94" t="n">
         <v>-2.43</v>
       </c>
-      <c r="D39" s="94" t="n">
+      <c r="F39" s="94" t="n">
         <v>-1.73</v>
       </c>
-      <c r="E39" s="94" t="n">
+      <c r="G39" s="94" t="n">
         <v>-4.04</v>
       </c>
-      <c r="F39" s="94" t="n">
+      <c r="H39" s="94" t="n">
         <v>-3.16</v>
       </c>
-      <c r="G39" s="94" t="n">
+      <c r="I39" s="94" t="n">
         <v>-3.16</v>
       </c>
-      <c r="H39" s="94" t="n">
+      <c r="J39" s="94" t="n">
         <v>-1.15</v>
       </c>
-      <c r="I39" s="94" t="n">
+      <c r="K39" s="94" t="n">
         <v>-1.09</v>
       </c>
-      <c r="J39" s="94" t="n">
+      <c r="L39" s="94" t="n">
         <v>-0.3</v>
       </c>
-      <c r="K39" s="94" t="n">
+      <c r="M39" s="94" t="n">
         <v>-0.91</v>
       </c>
-      <c r="L39" s="94" t="n">
+      <c r="N39" s="94" t="n">
         <v>-2</v>
       </c>
-      <c r="M39" s="94" t="n">
+      <c r="O39" s="94" t="n">
         <v>-2</v>
       </c>
-      <c r="N39" s="94" t="n">
+      <c r="P39" s="94" t="n">
         <v>-2.71</v>
       </c>
-      <c r="O39" s="94" t="n">
+      <c r="Q39" s="94" t="n">
         <v>-3.94</v>
       </c>
-      <c r="P39" s="94" t="n">
+      <c r="R39" s="94" t="n">
         <v>-3.51</v>
       </c>
-      <c r="Q39" s="94" t="n">
+      <c r="S39" s="94" t="n">
         <v>-6.37</v>
-      </c>
-      <c r="R39" s="94" t="n">
-        <v>-7.92</v>
-      </c>
-      <c r="S39" s="94" t="n">
-        <v>-7.92</v>
       </c>
       <c r="T39" s="94" t="n">
         <v>-7.92</v>
       </c>
       <c r="U39" s="94" t="n">
+        <v>-7.92</v>
+      </c>
+      <c r="V39" s="94" t="n">
+        <v>-7.92</v>
+      </c>
+      <c r="W39" s="94" t="n">
         <v>-8.25</v>
       </c>
-      <c r="V39" s="94" t="n">
+      <c r="X39" s="94" t="n">
         <v>-9.35</v>
       </c>
-      <c r="W39" s="94" t="n">
+      <c r="Y39" s="94" t="n">
         <v>-9.76</v>
       </c>
-      <c r="X39" s="94" t="n">
+      <c r="Z39" s="94" t="n">
         <v>-8.56</v>
       </c>
-      <c r="Y39" s="94" t="n">
+      <c r="AA39" s="94" t="n">
         <v>-8.56</v>
       </c>
-      <c r="Z39" s="94" t="n">
+      <c r="AB39" s="94" t="n">
         <v>-8.81</v>
       </c>
-      <c r="AA39" s="94" t="n">
+      <c r="AC39" s="94" t="n">
         <v>-9.539999999999999</v>
       </c>
-      <c r="AB39" s="94" t="n">
+      <c r="AD39" s="94" t="n">
         <v>-10.45</v>
       </c>
-      <c r="AC39" s="94" t="n">
+      <c r="AE39" s="94" t="n">
         <v>-10.55</v>
-      </c>
-      <c r="AD39" s="94" t="n">
-        <v>-10.48</v>
-      </c>
-      <c r="AE39" s="94" t="n">
-        <v>-10.48</v>
       </c>
     </row>
     <row r="40">
@@ -10787,52 +10786,52 @@
         <v>-7.39</v>
       </c>
       <c r="C40" s="94" t="n">
+        <v>-7.39</v>
+      </c>
+      <c r="D40" s="94" t="n">
+        <v>-7.39</v>
+      </c>
+      <c r="E40" s="94" t="n">
         <v>-6.51</v>
       </c>
-      <c r="D40" s="94" t="n">
+      <c r="F40" s="94" t="n">
         <v>-5.95</v>
       </c>
-      <c r="E40" s="94" t="n">
+      <c r="G40" s="94" t="n">
         <v>-6.87</v>
       </c>
-      <c r="F40" s="94" t="n">
+      <c r="H40" s="94" t="n">
         <v>-4.48</v>
       </c>
-      <c r="G40" s="94" t="n">
+      <c r="I40" s="94" t="n">
         <v>-4.48</v>
       </c>
-      <c r="H40" s="94" t="n">
+      <c r="J40" s="94" t="n">
         <v>-5</v>
       </c>
-      <c r="I40" s="94" t="n">
+      <c r="K40" s="94" t="n">
         <v>-6.31</v>
       </c>
-      <c r="J40" s="94" t="n">
+      <c r="L40" s="94" t="n">
         <v>-7.42</v>
       </c>
-      <c r="K40" s="94" t="n">
+      <c r="M40" s="94" t="n">
         <v>-7.49</v>
       </c>
-      <c r="L40" s="94" t="n">
+      <c r="N40" s="94" t="n">
         <v>-10.13</v>
       </c>
-      <c r="M40" s="94" t="n">
+      <c r="O40" s="94" t="n">
         <v>-10.13</v>
       </c>
-      <c r="N40" s="94" t="n">
+      <c r="P40" s="94" t="n">
         <v>-11.05</v>
       </c>
-      <c r="O40" s="94" t="n">
+      <c r="Q40" s="94" t="n">
         <v>-11.41</v>
       </c>
-      <c r="P40" s="94" t="n">
+      <c r="R40" s="94" t="n">
         <v>-11.32</v>
-      </c>
-      <c r="Q40" s="94" t="n">
-        <v>-12.67</v>
-      </c>
-      <c r="R40" s="94" t="n">
-        <v>-12.67</v>
       </c>
       <c r="S40" s="94" t="n">
         <v>-12.67</v>
@@ -10841,37 +10840,37 @@
         <v>-12.67</v>
       </c>
       <c r="U40" s="94" t="n">
+        <v>-12.67</v>
+      </c>
+      <c r="V40" s="94" t="n">
+        <v>-12.67</v>
+      </c>
+      <c r="W40" s="94" t="n">
         <v>-11.01</v>
       </c>
-      <c r="V40" s="94" t="n">
+      <c r="X40" s="94" t="n">
         <v>-10.66</v>
       </c>
-      <c r="W40" s="94" t="n">
+      <c r="Y40" s="94" t="n">
         <v>-10.79</v>
       </c>
-      <c r="X40" s="94" t="n">
+      <c r="Z40" s="94" t="n">
         <v>-10.43</v>
       </c>
-      <c r="Y40" s="94" t="n">
+      <c r="AA40" s="94" t="n">
         <v>-10.43</v>
       </c>
-      <c r="Z40" s="94" t="n">
+      <c r="AB40" s="94" t="n">
         <v>-10.32</v>
       </c>
-      <c r="AA40" s="94" t="n">
+      <c r="AC40" s="94" t="n">
         <v>-11.13</v>
       </c>
-      <c r="AB40" s="94" t="n">
+      <c r="AD40" s="94" t="n">
         <v>-10.47</v>
       </c>
-      <c r="AC40" s="94" t="n">
+      <c r="AE40" s="94" t="n">
         <v>-10.79</v>
-      </c>
-      <c r="AD40" s="94" t="n">
-        <v>-10.25</v>
-      </c>
-      <c r="AE40" s="94" t="n">
-        <v>-10.25</v>
       </c>
     </row>
     <row r="41">
@@ -10884,91 +10883,91 @@
         <v>42.69</v>
       </c>
       <c r="C41" s="94" t="n">
+        <v>42.69</v>
+      </c>
+      <c r="D41" s="94" t="n">
+        <v>42.69</v>
+      </c>
+      <c r="E41" s="94" t="n">
         <v>51.3</v>
       </c>
-      <c r="D41" s="94" t="n">
+      <c r="F41" s="94" t="n">
         <v>54.73</v>
       </c>
-      <c r="E41" s="94" t="n">
+      <c r="G41" s="94" t="n">
         <v>49.08</v>
       </c>
-      <c r="F41" s="94" t="n">
+      <c r="H41" s="94" t="n">
         <v>66.64</v>
       </c>
-      <c r="G41" s="94" t="n">
+      <c r="I41" s="94" t="n">
         <v>66.64</v>
       </c>
-      <c r="H41" s="94" t="n">
+      <c r="J41" s="94" t="n">
         <v>69.73</v>
       </c>
-      <c r="I41" s="94" t="n">
+      <c r="K41" s="94" t="n">
         <v>67.48</v>
       </c>
-      <c r="J41" s="94" t="n">
+      <c r="L41" s="94" t="n">
         <v>79.73</v>
       </c>
-      <c r="K41" s="94" t="n">
+      <c r="M41" s="94" t="n">
         <v>79.58</v>
       </c>
-      <c r="L41" s="94" t="n">
+      <c r="N41" s="94" t="n">
         <v>73.84</v>
       </c>
-      <c r="M41" s="94" t="n">
+      <c r="O41" s="94" t="n">
         <v>73.84</v>
       </c>
-      <c r="N41" s="94" t="n">
+      <c r="P41" s="94" t="n">
         <v>69.91</v>
       </c>
-      <c r="O41" s="94" t="n">
+      <c r="Q41" s="94" t="n">
         <v>61.51</v>
       </c>
-      <c r="P41" s="94" t="n">
+      <c r="R41" s="94" t="n">
         <v>59.85</v>
       </c>
-      <c r="Q41" s="94" t="n">
+      <c r="S41" s="94" t="n">
         <v>42.91</v>
-      </c>
-      <c r="R41" s="94" t="n">
-        <v>35.52</v>
-      </c>
-      <c r="S41" s="94" t="n">
-        <v>35.52</v>
       </c>
       <c r="T41" s="94" t="n">
         <v>35.52</v>
       </c>
       <c r="U41" s="94" t="n">
+        <v>35.52</v>
+      </c>
+      <c r="V41" s="94" t="n">
+        <v>35.52</v>
+      </c>
+      <c r="W41" s="94" t="n">
         <v>38.14</v>
       </c>
-      <c r="V41" s="94" t="n">
+      <c r="X41" s="94" t="n">
         <v>39.07</v>
       </c>
-      <c r="W41" s="94" t="n">
+      <c r="Y41" s="94" t="n">
         <v>39.23</v>
       </c>
-      <c r="X41" s="94" t="n">
+      <c r="Z41" s="94" t="n">
         <v>41.72</v>
       </c>
-      <c r="Y41" s="94" t="n">
+      <c r="AA41" s="94" t="n">
         <v>41.72</v>
       </c>
-      <c r="Z41" s="94" t="n">
+      <c r="AB41" s="94" t="n">
         <v>41.8</v>
       </c>
-      <c r="AA41" s="94" t="n">
+      <c r="AC41" s="94" t="n">
         <v>31.96</v>
       </c>
-      <c r="AB41" s="94" t="n">
+      <c r="AD41" s="94" t="n">
         <v>16.55</v>
       </c>
-      <c r="AC41" s="94" t="n">
+      <c r="AE41" s="94" t="n">
         <v>17</v>
-      </c>
-      <c r="AD41" s="94" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE41" s="94" t="n">
-        <v>17.5</v>
       </c>
     </row>
     <row r="42">
@@ -10977,154 +10976,154 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="92" t="inlineStr">
+      <c r="B42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C42" s="92" t="inlineStr">
+      <c r="C42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
       <c r="D42" s="91" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E42" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F42" s="92" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E42" s="91" t="inlineStr">
+      <c r="G42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F42" s="92" t="inlineStr">
+      <c r="H42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G42" s="92" t="inlineStr">
+      <c r="I42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H42" s="92" t="inlineStr">
+      <c r="J42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I42" s="92" t="inlineStr">
+      <c r="K42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J42" s="93" t="inlineStr">
+      <c r="L42" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K42" s="92" t="inlineStr">
+      <c r="M42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L42" s="92" t="inlineStr">
+      <c r="N42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M42" s="92" t="inlineStr">
+      <c r="O42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N42" s="93" t="inlineStr">
+      <c r="P42" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O42" s="93" t="inlineStr">
+      <c r="Q42" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P42" s="93" t="inlineStr">
+      <c r="R42" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q42" s="93" t="inlineStr">
+      <c r="S42" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R42" s="91" t="inlineStr">
+      <c r="T42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S42" s="91" t="inlineStr">
+      <c r="U42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T42" s="92" t="inlineStr">
+      <c r="V42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U42" s="92" t="inlineStr">
+      <c r="W42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V42" s="92" t="inlineStr">
+      <c r="X42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W42" s="92" t="inlineStr">
+      <c r="Y42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X42" s="92" t="inlineStr">
+      <c r="Z42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y42" s="92" t="inlineStr">
+      <c r="AA42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z42" s="93" t="inlineStr">
+      <c r="AB42" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA42" s="93" t="inlineStr">
+      <c r="AC42" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB42" s="92" t="inlineStr">
+      <c r="AD42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC42" s="93" t="inlineStr">
+      <c r="AE42" s="93" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AD42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -11138,91 +11137,91 @@
         <v>-2.1</v>
       </c>
       <c r="C43" s="94" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="D43" s="94" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="E43" s="94" t="n">
         <v>1.45</v>
       </c>
-      <c r="D43" s="94" t="n">
+      <c r="F43" s="94" t="n">
         <v>5.45</v>
       </c>
-      <c r="E43" s="94" t="n">
+      <c r="G43" s="94" t="n">
         <v>5.17</v>
       </c>
-      <c r="F43" s="94" t="n">
+      <c r="H43" s="94" t="n">
         <v>4.63</v>
       </c>
-      <c r="G43" s="94" t="n">
+      <c r="I43" s="94" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="H43" s="94" t="n">
+      <c r="J43" s="94" t="n">
         <v>8.07</v>
       </c>
-      <c r="I43" s="94" t="n">
+      <c r="K43" s="94" t="n">
         <v>8.81</v>
       </c>
-      <c r="J43" s="94" t="n">
+      <c r="L43" s="94" t="n">
         <v>10.87</v>
       </c>
-      <c r="K43" s="94" t="n">
+      <c r="M43" s="94" t="n">
         <v>9.07</v>
       </c>
-      <c r="L43" s="94" t="n">
+      <c r="N43" s="94" t="n">
         <v>10.44</v>
       </c>
-      <c r="M43" s="94" t="n">
+      <c r="O43" s="94" t="n">
         <v>10.44</v>
       </c>
-      <c r="N43" s="94" t="n">
+      <c r="P43" s="94" t="n">
         <v>11.3</v>
       </c>
-      <c r="O43" s="94" t="n">
+      <c r="Q43" s="94" t="n">
         <v>12.33</v>
       </c>
-      <c r="P43" s="94" t="n">
+      <c r="R43" s="94" t="n">
         <v>11.24</v>
       </c>
-      <c r="Q43" s="94" t="n">
+      <c r="S43" s="94" t="n">
         <v>9.34</v>
       </c>
-      <c r="R43" s="94" t="n">
+      <c r="T43" s="94" t="n">
         <v>9</v>
       </c>
-      <c r="S43" s="94" t="n">
+      <c r="U43" s="94" t="n">
         <v>9</v>
       </c>
-      <c r="T43" s="94" t="n">
+      <c r="V43" s="94" t="n">
         <v>7.9</v>
       </c>
-      <c r="U43" s="94" t="n">
+      <c r="W43" s="94" t="n">
         <v>7.82</v>
       </c>
-      <c r="V43" s="94" t="n">
+      <c r="X43" s="94" t="n">
         <v>7.02</v>
       </c>
-      <c r="W43" s="94" t="n">
+      <c r="Y43" s="94" t="n">
         <v>8.41</v>
       </c>
-      <c r="X43" s="94" t="n">
+      <c r="Z43" s="94" t="n">
         <v>9.82</v>
       </c>
-      <c r="Y43" s="94" t="n">
+      <c r="AA43" s="94" t="n">
         <v>9.82</v>
       </c>
-      <c r="Z43" s="94" t="n">
+      <c r="AB43" s="94" t="n">
         <v>9.59</v>
       </c>
-      <c r="AA43" s="94" t="n">
+      <c r="AC43" s="94" t="n">
         <v>10.06</v>
       </c>
-      <c r="AB43" s="94" t="n">
+      <c r="AD43" s="94" t="n">
         <v>9.789999999999999</v>
       </c>
-      <c r="AC43" s="94" t="n">
+      <c r="AE43" s="94" t="n">
         <v>12.27</v>
-      </c>
-      <c r="AD43" s="94" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="AE43" s="94" t="n">
-        <v>11.8</v>
       </c>
     </row>
     <row r="44">
@@ -11235,95 +11234,95 @@
         <v>-3.28</v>
       </c>
       <c r="C44" s="94" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="D44" s="94" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="E44" s="94" t="n">
         <v>-0.04</v>
       </c>
-      <c r="D44" s="94" t="n">
+      <c r="F44" s="94" t="n">
         <v>3.71</v>
       </c>
-      <c r="E44" s="94" t="n">
+      <c r="G44" s="94" t="n">
         <v>4.44</v>
       </c>
-      <c r="F44" s="94" t="n">
+      <c r="H44" s="94" t="n">
         <v>3.05</v>
       </c>
-      <c r="G44" s="94" t="n">
+      <c r="I44" s="94" t="n">
         <v>5.25</v>
       </c>
-      <c r="H44" s="94" t="n">
+      <c r="J44" s="94" t="n">
         <v>5.47</v>
       </c>
-      <c r="I44" s="94" t="n">
+      <c r="K44" s="94" t="n">
         <v>6.49</v>
       </c>
-      <c r="J44" s="94" t="n">
+      <c r="L44" s="94" t="n">
         <v>8.44</v>
       </c>
-      <c r="K44" s="94" t="n">
+      <c r="M44" s="94" t="n">
         <v>5.87</v>
       </c>
-      <c r="L44" s="94" t="n">
+      <c r="N44" s="94" t="n">
         <v>6.19</v>
       </c>
-      <c r="M44" s="94" t="n">
+      <c r="O44" s="94" t="n">
         <v>6.19</v>
       </c>
-      <c r="N44" s="94" t="n">
+      <c r="P44" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="O44" s="94" t="n">
+      <c r="Q44" s="94" t="n">
         <v>4.87</v>
       </c>
-      <c r="P44" s="94" t="n">
+      <c r="R44" s="94" t="n">
         <v>4.81</v>
       </c>
-      <c r="Q44" s="94" t="n">
+      <c r="S44" s="94" t="n">
         <v>6.72</v>
       </c>
-      <c r="R44" s="94" t="n">
+      <c r="T44" s="94" t="n">
         <v>5.58</v>
       </c>
-      <c r="S44" s="94" t="n">
+      <c r="U44" s="94" t="n">
         <v>5.58</v>
       </c>
-      <c r="T44" s="94" t="n">
+      <c r="V44" s="94" t="n">
         <v>5.73</v>
       </c>
-      <c r="U44" s="94" t="n">
+      <c r="W44" s="94" t="n">
         <v>6.52</v>
       </c>
-      <c r="V44" s="94" t="n">
+      <c r="X44" s="94" t="n">
         <v>4.29</v>
       </c>
-      <c r="W44" s="94" t="n">
+      <c r="Y44" s="94" t="n">
         <v>8.1</v>
       </c>
-      <c r="X44" s="94" t="n">
+      <c r="Z44" s="94" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="Y44" s="94" t="n">
+      <c r="AA44" s="94" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="Z44" s="94" t="n">
+      <c r="AB44" s="94" t="n">
         <v>10.04</v>
       </c>
-      <c r="AA44" s="94" t="n">
+      <c r="AC44" s="94" t="n">
         <v>9.49</v>
       </c>
-      <c r="AB44" s="94" t="n">
+      <c r="AD44" s="94" t="n">
         <v>8.24</v>
       </c>
-      <c r="AC44" s="94" t="n">
+      <c r="AE44" s="94" t="n">
         <v>10.85</v>
       </c>
-      <c r="AD44" s="94" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE44" s="94" t="n">
-        <v>9.5</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" s="96" t="inlineStr">
+      <c r="A45" s="95" t="inlineStr">
         <is>
           <t>fr40:RS5</t>
         </is>
@@ -11332,91 +11331,91 @@
         <v>9.82</v>
       </c>
       <c r="C45" s="94" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="D45" s="94" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="E45" s="94" t="n">
         <v>17.48</v>
       </c>
-      <c r="D45" s="94" t="n">
+      <c r="F45" s="94" t="n">
         <v>34.95</v>
       </c>
-      <c r="E45" s="94" t="n">
+      <c r="G45" s="94" t="n">
         <v>36.94</v>
       </c>
-      <c r="F45" s="94" t="n">
+      <c r="H45" s="94" t="n">
         <v>18.86</v>
       </c>
-      <c r="G45" s="94" t="n">
+      <c r="I45" s="94" t="n">
         <v>28.39</v>
       </c>
-      <c r="H45" s="94" t="n">
+      <c r="J45" s="94" t="n">
         <v>37.31</v>
       </c>
-      <c r="I45" s="94" t="n">
+      <c r="K45" s="94" t="n">
         <v>43.26</v>
       </c>
-      <c r="J45" s="94" t="n">
+      <c r="L45" s="94" t="n">
         <v>57.32</v>
       </c>
-      <c r="K45" s="94" t="n">
+      <c r="M45" s="94" t="n">
         <v>40.07</v>
       </c>
-      <c r="L45" s="94" t="n">
+      <c r="N45" s="94" t="n">
         <v>43.42</v>
       </c>
-      <c r="M45" s="94" t="n">
+      <c r="O45" s="94" t="n">
         <v>43.42</v>
       </c>
-      <c r="N45" s="94" t="n">
+      <c r="P45" s="94" t="n">
         <v>52.1</v>
       </c>
-      <c r="O45" s="94" t="n">
+      <c r="Q45" s="94" t="n">
         <v>68.64</v>
       </c>
-      <c r="P45" s="94" t="n">
+      <c r="R45" s="94" t="n">
         <v>61.42</v>
       </c>
-      <c r="Q45" s="94" t="n">
+      <c r="S45" s="94" t="n">
         <v>55.59</v>
       </c>
-      <c r="R45" s="94" t="n">
+      <c r="T45" s="94" t="n">
         <v>48.6</v>
       </c>
-      <c r="S45" s="94" t="n">
+      <c r="U45" s="94" t="n">
         <v>48.6</v>
       </c>
-      <c r="T45" s="94" t="n">
+      <c r="V45" s="94" t="n">
         <v>31.62</v>
       </c>
-      <c r="U45" s="94" t="n">
+      <c r="W45" s="94" t="n">
         <v>37.15</v>
       </c>
-      <c r="V45" s="94" t="n">
+      <c r="X45" s="94" t="n">
         <v>27.78</v>
       </c>
-      <c r="W45" s="94" t="n">
+      <c r="Y45" s="94" t="n">
         <v>37.95</v>
       </c>
-      <c r="X45" s="94" t="n">
+      <c r="Z45" s="94" t="n">
         <v>47.6</v>
       </c>
-      <c r="Y45" s="94" t="n">
+      <c r="AA45" s="94" t="n">
         <v>47.6</v>
       </c>
-      <c r="Z45" s="94" t="n">
+      <c r="AB45" s="94" t="n">
         <v>60.55</v>
       </c>
-      <c r="AA45" s="94" t="n">
+      <c r="AC45" s="94" t="n">
         <v>57.69</v>
       </c>
-      <c r="AB45" s="94" t="n">
+      <c r="AD45" s="94" t="n">
         <v>39.06</v>
       </c>
-      <c r="AC45" s="94" t="n">
+      <c r="AE45" s="94" t="n">
         <v>67.92</v>
-      </c>
-      <c r="AD45" s="94" t="n">
-        <v>51.18</v>
-      </c>
-      <c r="AE45" s="94" t="n">
-        <v>51.18</v>
       </c>
     </row>
     <row r="46">
@@ -11425,154 +11424,154 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="92" t="inlineStr">
+      <c r="B46" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C46" s="92" t="inlineStr">
+      <c r="C46" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
       <c r="D46" s="91" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E46" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F46" s="92" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E46" s="91" t="inlineStr">
+      <c r="G46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F46" s="92" t="inlineStr">
+      <c r="H46" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G46" s="92" t="inlineStr">
+      <c r="I46" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H46" s="92" t="inlineStr">
+      <c r="J46" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I46" s="92" t="inlineStr">
+      <c r="K46" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J46" s="93" t="inlineStr">
+      <c r="L46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K46" s="92" t="inlineStr">
+      <c r="M46" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L46" s="92" t="inlineStr">
+      <c r="N46" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M46" s="92" t="inlineStr">
+      <c r="O46" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N46" s="91" t="inlineStr">
+      <c r="P46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O46" s="93" t="inlineStr">
+      <c r="Q46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P46" s="93" t="inlineStr">
+      <c r="R46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q46" s="93" t="inlineStr">
+      <c r="S46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R46" s="93" t="inlineStr">
+      <c r="T46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S46" s="93" t="inlineStr">
+      <c r="U46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T46" s="92" t="inlineStr">
+      <c r="V46" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U46" s="91" t="inlineStr">
+      <c r="W46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V46" s="92" t="inlineStr">
+      <c r="X46" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W46" s="92" t="inlineStr">
+      <c r="Y46" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X46" s="91" t="inlineStr">
+      <c r="Z46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y46" s="91" t="inlineStr">
+      <c r="AA46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z46" s="93" t="inlineStr">
+      <c r="AB46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA46" s="93" t="inlineStr">
+      <c r="AC46" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB46" s="92" t="inlineStr">
+      <c r="AD46" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC46" s="93" t="inlineStr">
+      <c r="AE46" s="93" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AD46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -11586,91 +11585,91 @@
         <v>2.11</v>
       </c>
       <c r="C47" s="94" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="D47" s="94" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E47" s="94" t="n">
         <v>6.89</v>
       </c>
-      <c r="D47" s="94" t="n">
+      <c r="F47" s="94" t="n">
         <v>10.14</v>
       </c>
-      <c r="E47" s="94" t="n">
+      <c r="G47" s="94" t="n">
         <v>10.81</v>
       </c>
-      <c r="F47" s="94" t="n">
+      <c r="H47" s="94" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="G47" s="94" t="n">
+      <c r="I47" s="94" t="n">
         <v>12.84</v>
       </c>
-      <c r="H47" s="94" t="n">
+      <c r="J47" s="94" t="n">
         <v>13.25</v>
       </c>
-      <c r="I47" s="94" t="n">
+      <c r="K47" s="94" t="n">
         <v>14.72</v>
       </c>
-      <c r="J47" s="94" t="n">
+      <c r="L47" s="94" t="n">
         <v>15.64</v>
       </c>
-      <c r="K47" s="94" t="n">
+      <c r="M47" s="94" t="n">
         <v>15.13</v>
       </c>
-      <c r="L47" s="94" t="n">
+      <c r="N47" s="94" t="n">
         <v>15.12</v>
       </c>
-      <c r="M47" s="94" t="n">
+      <c r="O47" s="94" t="n">
         <v>15.12</v>
       </c>
-      <c r="N47" s="94" t="n">
+      <c r="P47" s="94" t="n">
         <v>15.17</v>
       </c>
-      <c r="O47" s="94" t="n">
+      <c r="Q47" s="94" t="n">
         <v>15.04</v>
       </c>
-      <c r="P47" s="94" t="n">
+      <c r="R47" s="94" t="n">
         <v>15.48</v>
       </c>
-      <c r="Q47" s="94" t="n">
+      <c r="S47" s="94" t="n">
         <v>13.98</v>
       </c>
-      <c r="R47" s="94" t="n">
+      <c r="T47" s="94" t="n">
         <v>12.65</v>
       </c>
-      <c r="S47" s="94" t="n">
+      <c r="U47" s="94" t="n">
         <v>12.65</v>
       </c>
-      <c r="T47" s="94" t="n">
+      <c r="V47" s="94" t="n">
         <v>10.48</v>
       </c>
-      <c r="U47" s="94" t="n">
+      <c r="W47" s="94" t="n">
         <v>11.16</v>
       </c>
-      <c r="V47" s="94" t="n">
+      <c r="X47" s="94" t="n">
         <v>9.84</v>
       </c>
-      <c r="W47" s="94" t="n">
+      <c r="Y47" s="94" t="n">
         <v>11.18</v>
       </c>
-      <c r="X47" s="94" t="n">
+      <c r="Z47" s="94" t="n">
         <v>12.87</v>
       </c>
-      <c r="Y47" s="94" t="n">
+      <c r="AA47" s="94" t="n">
         <v>12.87</v>
       </c>
-      <c r="Z47" s="94" t="n">
+      <c r="AB47" s="94" t="n">
         <v>15.03</v>
       </c>
-      <c r="AA47" s="94" t="n">
+      <c r="AC47" s="94" t="n">
         <v>14.08</v>
       </c>
-      <c r="AB47" s="94" t="n">
+      <c r="AD47" s="94" t="n">
         <v>11.54</v>
       </c>
-      <c r="AC47" s="94" t="n">
+      <c r="AE47" s="94" t="n">
         <v>16.12</v>
-      </c>
-      <c r="AD47" s="94" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="AE47" s="94" t="n">
-        <v>14.9</v>
       </c>
     </row>
     <row r="48">
@@ -11683,91 +11682,91 @@
         <v>6.54</v>
       </c>
       <c r="C48" s="94" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="D48" s="94" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="E48" s="94" t="n">
         <v>13.05</v>
       </c>
-      <c r="D48" s="94" t="n">
+      <c r="F48" s="94" t="n">
         <v>16.29</v>
       </c>
-      <c r="E48" s="94" t="n">
+      <c r="G48" s="94" t="n">
         <v>18.22</v>
       </c>
-      <c r="F48" s="94" t="n">
+      <c r="H48" s="94" t="n">
         <v>16.01</v>
       </c>
-      <c r="G48" s="94" t="n">
+      <c r="I48" s="94" t="n">
         <v>17.47</v>
       </c>
-      <c r="H48" s="94" t="n">
+      <c r="J48" s="94" t="n">
         <v>19.27</v>
       </c>
-      <c r="I48" s="94" t="n">
+      <c r="K48" s="94" t="n">
         <v>19.17</v>
       </c>
-      <c r="J48" s="94" t="n">
+      <c r="L48" s="94" t="n">
         <v>20.28</v>
       </c>
-      <c r="K48" s="94" t="n">
+      <c r="M48" s="94" t="n">
         <v>18.25</v>
       </c>
-      <c r="L48" s="94" t="n">
+      <c r="N48" s="94" t="n">
         <v>17.55</v>
       </c>
-      <c r="M48" s="94" t="n">
+      <c r="O48" s="94" t="n">
         <v>17.55</v>
       </c>
-      <c r="N48" s="94" t="n">
+      <c r="P48" s="94" t="n">
         <v>19.55</v>
       </c>
-      <c r="O48" s="94" t="n">
+      <c r="Q48" s="94" t="n">
         <v>23.1</v>
       </c>
-      <c r="P48" s="94" t="n">
+      <c r="R48" s="94" t="n">
         <v>23.08</v>
       </c>
-      <c r="Q48" s="94" t="n">
+      <c r="S48" s="94" t="n">
         <v>22.86</v>
       </c>
-      <c r="R48" s="94" t="n">
+      <c r="T48" s="94" t="n">
         <v>22.79</v>
       </c>
-      <c r="S48" s="94" t="n">
+      <c r="U48" s="94" t="n">
         <v>22.79</v>
       </c>
-      <c r="T48" s="94" t="n">
+      <c r="V48" s="94" t="n">
         <v>18.76</v>
       </c>
-      <c r="U48" s="94" t="n">
+      <c r="W48" s="94" t="n">
         <v>21.19</v>
       </c>
-      <c r="V48" s="94" t="n">
+      <c r="X48" s="94" t="n">
         <v>19.24</v>
       </c>
-      <c r="W48" s="94" t="n">
+      <c r="Y48" s="94" t="n">
         <v>21.4</v>
       </c>
-      <c r="X48" s="94" t="n">
+      <c r="Z48" s="94" t="n">
         <v>23.05</v>
       </c>
-      <c r="Y48" s="94" t="n">
+      <c r="AA48" s="94" t="n">
         <v>23.05</v>
       </c>
-      <c r="Z48" s="94" t="n">
+      <c r="AB48" s="94" t="n">
         <v>26.47</v>
       </c>
-      <c r="AA48" s="94" t="n">
+      <c r="AC48" s="94" t="n">
         <v>25.92</v>
       </c>
-      <c r="AB48" s="94" t="n">
+      <c r="AD48" s="94" t="n">
         <v>22.23</v>
       </c>
-      <c r="AC48" s="94" t="n">
+      <c r="AE48" s="94" t="n">
         <v>25.5</v>
-      </c>
-      <c r="AD48" s="94" t="n">
-        <v>23.22</v>
-      </c>
-      <c r="AE48" s="94" t="n">
-        <v>23.22</v>
       </c>
     </row>
     <row r="49">
@@ -11780,104 +11779,104 @@
         <v>14.84</v>
       </c>
       <c r="C49" s="94" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="D49" s="94" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="E49" s="94" t="n">
         <v>25.18</v>
       </c>
-      <c r="D49" s="94" t="n">
+      <c r="F49" s="94" t="n">
         <v>39.55</v>
       </c>
-      <c r="E49" s="94" t="n">
+      <c r="G49" s="94" t="n">
         <v>44.2</v>
       </c>
-      <c r="F49" s="94" t="n">
+      <c r="H49" s="94" t="n">
         <v>25.84</v>
       </c>
-      <c r="G49" s="94" t="n">
+      <c r="I49" s="94" t="n">
         <v>33</v>
       </c>
-      <c r="H49" s="94" t="n">
+      <c r="J49" s="94" t="n">
         <v>39.69</v>
       </c>
-      <c r="I49" s="94" t="n">
+      <c r="K49" s="94" t="n">
         <v>45.34</v>
       </c>
-      <c r="J49" s="94" t="n">
+      <c r="L49" s="94" t="n">
         <v>56.7</v>
       </c>
-      <c r="K49" s="94" t="n">
+      <c r="M49" s="94" t="n">
         <v>45.99</v>
       </c>
-      <c r="L49" s="94" t="n">
+      <c r="N49" s="94" t="n">
         <v>47.47</v>
       </c>
-      <c r="M49" s="94" t="n">
+      <c r="O49" s="94" t="n">
         <v>47.47</v>
       </c>
-      <c r="N49" s="94" t="n">
+      <c r="P49" s="94" t="n">
         <v>51.27</v>
       </c>
-      <c r="O49" s="94" t="n">
+      <c r="Q49" s="94" t="n">
         <v>62.47</v>
       </c>
-      <c r="P49" s="94" t="n">
+      <c r="R49" s="94" t="n">
         <v>66.34</v>
       </c>
-      <c r="Q49" s="94" t="n">
+      <c r="S49" s="94" t="n">
         <v>61.48</v>
       </c>
-      <c r="R49" s="94" t="n">
+      <c r="T49" s="94" t="n">
         <v>57.71</v>
       </c>
-      <c r="S49" s="94" t="n">
+      <c r="U49" s="94" t="n">
         <v>57.71</v>
       </c>
-      <c r="T49" s="94" t="n">
+      <c r="V49" s="94" t="n">
         <v>46.87</v>
       </c>
-      <c r="U49" s="94" t="n">
+      <c r="W49" s="94" t="n">
         <v>49.63</v>
       </c>
-      <c r="V49" s="94" t="n">
+      <c r="X49" s="94" t="n">
         <v>40.3</v>
       </c>
-      <c r="W49" s="94" t="n">
+      <c r="Y49" s="94" t="n">
         <v>46.31</v>
       </c>
-      <c r="X49" s="94" t="n">
+      <c r="Z49" s="94" t="n">
         <v>55.45</v>
       </c>
-      <c r="Y49" s="94" t="n">
+      <c r="AA49" s="94" t="n">
         <v>55.45</v>
       </c>
-      <c r="Z49" s="94" t="n">
+      <c r="AB49" s="94" t="n">
         <v>67.13</v>
       </c>
-      <c r="AA49" s="94" t="n">
+      <c r="AC49" s="94" t="n">
         <v>61.57</v>
       </c>
-      <c r="AB49" s="94" t="n">
+      <c r="AD49" s="94" t="n">
         <v>43.95</v>
       </c>
-      <c r="AC49" s="94" t="n">
+      <c r="AE49" s="94" t="n">
         <v>75.19</v>
-      </c>
-      <c r="AD49" s="94" t="n">
-        <v>56.46</v>
-      </c>
-      <c r="AE49" s="94" t="n">
-        <v>56.46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RS4:18.53&lt;=22;us500:RS2:2.99&lt;=22;us30:RS3:5.68&lt;=25;ixic:RNG60:-20.02&lt;=-20;ixic:RS2:3.7&lt;=38;jp225:RNG60:-15.51&lt;=-10;jp225:RS9:14.64&lt;=28;vn:RS3:4.29&lt;=25;fr40:RS5:9.82&lt;=20</t>
+          <t>今日买报：sh:RS3:2.16&lt;=8;kc:RS5:6.02&lt;=21;cy:RNG60:-10.01&lt;=-10;cy:RS3:0.77&lt;=4;hk50:RS4:4.01&lt;=22;us500:RS2:2.99&lt;=22;us30:RS3:5.68&lt;=25;ixic:RNG60:-20.02&lt;=-20;ixic:RS2:3.7&lt;=38;jp225:RNG60:-15.51&lt;=-10;jp225:RS9:14.64&lt;=28;vn:RS3:4.29&lt;=25;fr40:RS5:9.82&lt;=20</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：hk50:RNG60:16.06&gt;=15</t>
+          <t>今日卖报：</t>
         </is>
       </c>
     </row>
@@ -15478,13 +15477,13 @@
       <c r="G2" s="36" t="n">
         <v>66</v>
       </c>
-      <c r="H2" s="97" t="n">
+      <c r="H2" s="96" t="n">
         <v>22.3514585</v>
       </c>
       <c r="I2" s="36" t="n">
         <v>7.06</v>
       </c>
-      <c r="J2" s="98">
+      <c r="J2" s="97">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -15516,13 +15515,13 @@
       <c r="G3" s="39" t="n">
         <v>73</v>
       </c>
-      <c r="H3" s="99" t="n">
+      <c r="H3" s="98" t="n">
         <v>35.0298984</v>
       </c>
       <c r="I3" s="39" t="n">
         <v>11.41</v>
       </c>
-      <c r="J3" s="98">
+      <c r="J3" s="97">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -15554,13 +15553,13 @@
       <c r="G4" s="39" t="n">
         <v>85</v>
       </c>
-      <c r="H4" s="99" t="n">
+      <c r="H4" s="98" t="n">
         <v>122.4911655</v>
       </c>
       <c r="I4" s="39" t="n">
         <v>76.98</v>
       </c>
-      <c r="J4" s="100">
+      <c r="J4" s="99">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -15592,13 +15591,13 @@
       <c r="G5" s="39" t="n">
         <v>96</v>
       </c>
-      <c r="H5" s="99" t="n">
+      <c r="H5" s="98" t="n">
         <v>136.13543</v>
       </c>
       <c r="I5" s="39" t="n">
         <v>100.05</v>
       </c>
-      <c r="J5" s="100">
+      <c r="J5" s="99">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -15630,13 +15629,13 @@
       <c r="G6" s="39" t="n">
         <v>95</v>
       </c>
-      <c r="H6" s="99" t="n">
+      <c r="H6" s="98" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I6" s="39" t="n">
         <v>44.37</v>
       </c>
-      <c r="J6" s="100">
+      <c r="J6" s="99">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -15668,13 +15667,13 @@
       <c r="G7" s="39" t="n">
         <v>86</v>
       </c>
-      <c r="H7" s="99" t="n">
+      <c r="H7" s="98" t="n">
         <v>123.8525927</v>
       </c>
       <c r="I7" s="39" t="n">
         <v>63.41</v>
       </c>
-      <c r="J7" s="100">
+      <c r="J7" s="99">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -15706,13 +15705,13 @@
       <c r="G8" s="39" t="n">
         <v>87</v>
       </c>
-      <c r="H8" s="99" t="n">
+      <c r="H8" s="98" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I8" s="39" t="n">
         <v>26.39</v>
       </c>
-      <c r="J8" s="100">
+      <c r="J8" s="99">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -15744,13 +15743,13 @@
       <c r="G9" s="39" t="n">
         <v>83</v>
       </c>
-      <c r="H9" s="99" t="n">
+      <c r="H9" s="98" t="n">
         <v>47.02060524</v>
       </c>
       <c r="I9" s="39" t="n">
         <v>37.82</v>
       </c>
-      <c r="J9" s="100">
+      <c r="J9" s="99">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -15781,13 +15780,13 @@
       <c r="G10" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="H10" s="101" t="n">
+      <c r="H10" s="100" t="n">
         <v>27.8860732</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>-10.97</v>
       </c>
-      <c r="J10" s="102" t="n">
+      <c r="J10" s="101" t="n">
         <v>0.278860732</v>
       </c>
     </row>
@@ -15818,13 +15817,13 @@
       <c r="G11" s="24" t="n">
         <v>93</v>
       </c>
-      <c r="H11" s="101" t="n">
+      <c r="H11" s="100" t="n">
         <v>17.4948656</v>
       </c>
       <c r="I11" s="24" t="n">
         <v>-7.7</v>
       </c>
-      <c r="J11" s="102">
+      <c r="J11" s="101">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>

--- a/report_2504.xlsx
+++ b/report_2504.xlsx
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="B25" s="88" t="n">
-        <v>7.32</v>
+        <v>7.35</v>
       </c>
       <c r="C25" s="88" t="n">
         <v>7.28</v>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="B26" s="89" t="n">
-        <v>0.53</v>
+        <v>0.89</v>
       </c>
       <c r="C26" s="89" t="n">
         <v>-0.22</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="B27" s="89" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="C27" s="89" t="n">
         <v>0.5</v>
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>-14.13</v>
+        <v>-14.46</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>-14.13</v>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>-12.21</v>
+        <v>-12.95</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>-12.21</v>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>2.99</v>
@@ -8888,13 +8888,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="76" t="inlineStr">
+      <c r="A23" s="86" t="inlineStr">
         <is>
           <t>us30:RNG60</t>
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>-9.91</v>
+        <v>-10.95</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>-9.91</v>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>-9.75</v>
+        <v>-11.43</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>-9.75</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>5.68</v>
+        <v>4.97</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>5.68</v>
@@ -9336,13 +9336,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="86" t="inlineStr">
+      <c r="A27" s="76" t="inlineStr">
         <is>
           <t>ixic:RNG60</t>
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>-20.02</v>
+        <v>-19.9</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>-20.02</v>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>-14.74</v>
+        <v>-14.94</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>-14.74</v>
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>3.7</v>
+        <v>5.56</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>3.7</v>
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-7.72</v>
+        <v>-6.5</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-2.1</v>
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-8.75</v>
+        <v>-7.54</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-3.28</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>5.64</v>
+        <v>6.19</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>9.82</v>
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>-2.21</v>
+        <v>-1.7</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>2.11</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>0.92</v>
+        <v>1.44</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>6.54</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>10.33</v>
+        <v>10.68</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>14.84</v>
@@ -11869,7 +11869,7 @@
     <row r="51">
       <c r="A51" s="91" t="inlineStr">
         <is>
-          <t>今日买报：sh:RS3:2.01&lt;=8;kc:RS5:4.98&lt;=21;cy:RNG60:-12.29&lt;=-10;cy:RNG120:-20.74&lt;=-20;cy:RS3:0.64&lt;=4;hk50:RS4:3.21&lt;=22;us500:RS2:2.99&lt;=22;us30:RS3:5.68&lt;=25;ixic:RNG60:-20.02&lt;=-20;ixic:RS2:3.7&lt;=38;jp225:RNG60:-21.38&lt;=-10;jp225:RNG120:-20.93&lt;=-20;jp225:RS9:8.62&lt;=28;vn:RS3:4.29&lt;=25;sensex:RS10:29.52&lt;=39;fr40:RS5:5.64&lt;=20</t>
+          <t>今日买报：sh:RS3:2.01&lt;=8;kc:RS5:4.98&lt;=21;cy:RNG60:-12.29&lt;=-10;cy:RNG120:-20.74&lt;=-20;cy:RS3:0.64&lt;=4;hk50:RS4:3.21&lt;=22;us500:RS2:2.85&lt;=22;us30:RNG60:-10.95&lt;=-10;us30:RS3:4.97&lt;=25;ixic:RS2:5.56&lt;=38;jp225:RNG60:-21.38&lt;=-10;jp225:RNG120:-20.93&lt;=-20;jp225:RS9:8.62&lt;=28;vn:RS3:4.29&lt;=25;sensex:RS10:29.52&lt;=39;fr40:RS5:6.19&lt;=20</t>
         </is>
       </c>
     </row>

--- a/report_2504.xlsx
+++ b/report_2504.xlsx
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.36</v>
+        <v>7.43</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.35</v>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.89</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.33</v>
+        <v>2.24</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.4</v>
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>-14.46</v>
+        <v>-14.49</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>-14.46</v>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>-12.95</v>
+        <v>-14.97</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>-12.95</v>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>2.85</v>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>-10.95</v>
+        <v>-10.24</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>-10.95</v>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>-11.43</v>
+        <v>-12.58</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>-11.43</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>4.97</v>
+        <v>4.25</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>4.97</v>
@@ -9336,13 +9336,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="76" t="inlineStr">
+      <c r="A27" s="95" t="inlineStr">
         <is>
           <t>ixic:RNG60</t>
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>-19.9</v>
+        <v>-20.32</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>-19.9</v>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>-14.94</v>
+        <v>-17.48</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>-14.94</v>
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>5.56</v>
+        <v>3.02</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>5.56</v>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="B35" s="94" t="n">
-        <v>-8.07</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="C35" s="94" t="n">
         <v>-3.5</v>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="B36" s="94" t="n">
-        <v>-11.07</v>
+        <v>-12.08</v>
       </c>
       <c r="C36" s="94" t="n">
         <v>-5.88</v>
@@ -10432,7 +10432,7 @@
         </is>
       </c>
       <c r="B37" s="94" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="C37" s="94" t="n">
         <v>4.29</v>
@@ -10686,7 +10686,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-3.69</v>
+        <v>-4.07</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-5.77</v>
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-8.92</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-10.78</v>
@@ -10880,7 +10880,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>41.9</v>
+        <v>39.64</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>29.52</v>
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>-6.5</v>
+        <v>-4.35</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-6.5</v>
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-7.54</v>
+        <v>-6.37</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-7.54</v>
@@ -11322,13 +11322,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="95" t="inlineStr">
+      <c r="A45" s="76" t="inlineStr">
         <is>
           <t>fr40:RS5</t>
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>6.19</v>
+        <v>23.76</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>6.19</v>
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>-1.7</v>
+        <v>-0.08</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>-1.7</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>1.44</v>
+        <v>3.95</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>1.44</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>10.68</v>
+        <v>24.58</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>10.68</v>
@@ -11869,7 +11869,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：kc:RS5:18.5&lt;=21;hk50:RS4:12.74&lt;=22;us500:RS2:2.85&lt;=22;us30:RNG60:-10.95&lt;=-10;us30:RS3:4.97&lt;=25;ixic:RS2:5.56&lt;=38;jp225:RNG60:-15.76&lt;=-10;vn:RS3:2.0&lt;=25;fr40:RS5:6.19&lt;=20</t>
+          <t>今日买报：kc:RS5:18.5&lt;=21;hk50:RS4:12.74&lt;=22;us500:RS2:1.75&lt;=22;us30:RNG60:-10.24&lt;=-10;us30:RS3:4.25&lt;=25;ixic:RNG60:-20.32&lt;=-20;ixic:RS2:3.02&lt;=38;jp225:RNG60:-15.76&lt;=-10;vn:RS3:1.81&lt;=25</t>
         </is>
       </c>
     </row>

--- a/report_2504.xlsx
+++ b/report_2504.xlsx
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.38</v>
+        <v>7.35</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.43</v>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.64</v>
+        <v>-1.04</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>1.1</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>2.11</v>
+        <v>1.69</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>2.24</v>
@@ -8288,9 +8288,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B18" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C18" s="92" t="inlineStr">
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>-14.49</v>
+        <v>-6.5</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>-14.49</v>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>-14.97</v>
+        <v>-6.16</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>-14.97</v>
@@ -8634,13 +8634,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="95" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>1.75</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>1.75</v>
@@ -8736,165 +8736,165 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="92" t="inlineStr">
+      <c r="B22" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C22" s="92" t="inlineStr">
+      <c r="D22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D22" s="92" t="inlineStr">
+      <c r="E22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E22" s="92" t="inlineStr">
+      <c r="F22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F22" s="92" t="inlineStr">
+      <c r="G22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G22" s="92" t="inlineStr">
+      <c r="H22" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H22" s="93" t="inlineStr">
+      <c r="J22" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K22" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M22" s="93" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I22" s="92" t="inlineStr">
+      <c r="N22" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O22" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J22" s="92" t="inlineStr">
+      <c r="Y22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K22" s="92" t="inlineStr">
+      <c r="Z22" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L22" s="91" t="inlineStr">
+      <c r="AA22" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P22" s="91" t="inlineStr">
+      <c r="AC22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q22" s="91" t="inlineStr">
+      <c r="AD22" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X22" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y22" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z22" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA22" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD22" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" s="95" t="inlineStr">
+      <c r="A23" s="76" t="inlineStr">
         <is>
           <t>us30:RNG60</t>
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>-10.24</v>
+        <v>-3.99</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>-10.24</v>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>-12.58</v>
+        <v>-4.99</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>-12.58</v>
@@ -9082,13 +9082,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="95" t="inlineStr">
+      <c r="A25" s="76" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>4.25</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>4.25</v>
@@ -9184,165 +9184,165 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
+      <c r="B26" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C26" s="92" t="inlineStr">
+      <c r="D26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D26" s="92" t="inlineStr">
+      <c r="E26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E26" s="92" t="inlineStr">
+      <c r="F26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F26" s="92" t="inlineStr">
+      <c r="G26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G26" s="92" t="inlineStr">
+      <c r="H26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H26" s="91" t="inlineStr">
+      <c r="J26" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K26" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L26" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M26" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N26" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O26" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I26" s="92" t="inlineStr">
+      <c r="Q26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J26" s="92" t="inlineStr">
+      <c r="AA26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K26" s="92" t="inlineStr">
+      <c r="AB26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AD26" s="92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L26" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="M26" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N26" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O26" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P26" s="91" t="inlineStr">
+      <c r="AE26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z26" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA26" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD26" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" s="95" t="inlineStr">
+      <c r="A27" s="76" t="inlineStr">
         <is>
           <t>ixic:RNG60</t>
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>-20.32</v>
+        <v>-10.28</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>-20.32</v>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>-17.48</v>
+        <v>-6.5</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>-17.48</v>
@@ -9530,13 +9530,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="95" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>3.02</v>
+        <v>83.98</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>3.02</v>
@@ -10880,7 +10880,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>37.57</v>
+        <v>37.55</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>39.64</v>
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>-4.35</v>
+        <v>-8.18</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-4.35</v>
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-6.37</v>
+        <v>-9.85</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-6.37</v>
@@ -11322,13 +11322,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="76" t="inlineStr">
+      <c r="A45" s="95" t="inlineStr">
         <is>
           <t>fr40:RS5</t>
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>23.76</v>
+        <v>17.99</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>23.76</v>
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>-4.54</v>
+        <v>-4.39</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>0.04</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>4.08</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>20.08</v>
+        <v>20.28</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>25.19</v>
@@ -11869,7 +11869,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RS4:17.68&lt;=22;us500:RS2:1.75&lt;=22;us30:RNG60:-10.24&lt;=-10;us30:RS3:4.25&lt;=25;ixic:RNG60:-20.32&lt;=-20;ixic:RS2:3.02&lt;=38;jp225:RNG60:-17.57&lt;=-10;jp225:RNG120:-20.54&lt;=-20;jp225:RS9:26.17&lt;=28;vn:RNG60:-12.24&lt;=-10;vn:RS3:1.27&lt;=25;sensex:RS10:37.57&lt;=39</t>
+          <t>今日买报：hk50:RS4:17.68&lt;=22;jp225:RNG60:-17.57&lt;=-10;jp225:RNG120:-20.54&lt;=-20;jp225:RS9:26.17&lt;=28;vn:RNG60:-12.24&lt;=-10;vn:RS3:1.27&lt;=25;sensex:RS10:37.55&lt;=39;fr40:RS5:17.99&lt;=20</t>
         </is>
       </c>
     </row>

--- a/report_2504.xlsx
+++ b/report_2504.xlsx
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.35</v>
+        <v>7.31</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.35</v>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.06</v>
+        <v>-0.54</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-1.04</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.69</v>
@@ -8288,9 +8288,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C18" s="93" t="inlineStr">
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>-6.5</v>
+        <v>-9.84</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>-6.5</v>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>-6.16</v>
+        <v>-9.83</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>-6.16</v>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>82.54000000000001</v>
+        <v>49.87</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>82.54000000000001</v>
@@ -8736,9 +8736,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C22" s="93" t="inlineStr">
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>-3.99</v>
+        <v>-6.88</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>-3.99</v>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>-4.99</v>
+        <v>-8.09</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>-4.99</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>68.40000000000001</v>
+        <v>50.88</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>68.40000000000001</v>
@@ -9184,9 +9184,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C26" s="93" t="inlineStr">
@@ -9342,7 +9342,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>-10.28</v>
+        <v>-13.95</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>-10.28</v>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>-6.5</v>
+        <v>-10.78</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>-6.5</v>
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>83.98</v>
+        <v>50.49</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>83.98</v>
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>-5.22</v>
+        <v>-6.66</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-8.18</v>
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-3.98</v>
+        <v>-5.44</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-9.85</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>44.49</v>
+        <v>38.63</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>17.99</v>
@@ -11424,9 +11424,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C46" s="92" t="inlineStr">
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>-4.39</v>
+        <v>-0.45</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>-4.39</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>1.23</v>
+        <v>5</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>1.23</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>20.28</v>
+        <v>40.61</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>20.28</v>
